--- a/data/entrada/nóminas/cargos.xlsx
+++ b/data/entrada/nóminas/cargos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amarzal/_Activo/eco/CoAna/data/entrada/nóminas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2ED64A8-DFF3-B142-BDE0-91C28C3D257B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C02DDD55-E00A-154C-980F-F46785264788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1608,9 +1608,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0"/>
-  </numFmts>
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -1687,7 +1684,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -1696,13 +1693,13 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="0.0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -1742,11 +1739,11 @@
     <sortCondition ref="A1:A465"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{3203C3A6-50D8-DD4C-80B4-06BC4BEB47B2}" name="cargo" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{3203C3A6-50D8-DD4C-80B4-06BC4BEB47B2}" name="cargo" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{33160495-9720-6A40-B7C2-1BBB379EE15A}" name="nombre"/>
     <tableColumn id="5" xr3:uid="{20D9C665-014D-D942-9492-5BC018045525}" name="cargo_asimilado" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{14317EFC-DF48-B644-824E-F5949347DC2C}" name="dedicación" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{72E047F7-BB5D-8541-8732-5A76D9C0CD02}" name="actividad" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{14317EFC-DF48-B644-824E-F5949347DC2C}" name="dedicación" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{72E047F7-BB5D-8541-8732-5A76D9C0CD02}" name="actividad" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{B2F1B344-4C3C-DA4A-AC1E-7332BD2A3B7D}" name="centro"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2406,7 +2403,7 @@
         <v>0.375</v>
       </c>
       <c r="E19" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="F19" t="s">
         <v>493</v>

--- a/data/entrada/nóminas/cargos.xlsx
+++ b/data/entrada/nóminas/cargos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amarzal/_Activo/eco/CoAna/data/entrada/nóminas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C02DDD55-E00A-154C-980F-F46785264788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BB8514-DA1E-7247-8802-2C98BC2613A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="523">
   <si>
     <t>cargo</t>
   </si>
@@ -1397,9 +1397,6 @@
     <t>cargo_asimilado</t>
   </si>
   <si>
-    <t>dedicación</t>
-  </si>
-  <si>
     <t>actividad</t>
   </si>
   <si>
@@ -1598,10 +1595,13 @@
     <t>unidad-divulgación-científica</t>
   </si>
   <si>
-    <t>opaq</t>
-  </si>
-  <si>
     <t>inspección-servicios</t>
+  </si>
+  <si>
+    <t>dedicación_porcentual</t>
+  </si>
+  <si>
+    <t>dedicación_horaria</t>
   </si>
 </sst>
 </file>
@@ -1678,23 +1678,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1719,6 +1719,9 @@
       </font>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1733,17 +1736,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9D2F6B4F-52C3-6B46-B201-F77B94AF0593}" name="Table1" displayName="Table1" ref="A1:F465" totalsRowShown="0">
-  <autoFilter ref="A1:F465" xr:uid="{9D2F6B4F-52C3-6B46-B201-F77B94AF0593}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C465">
-    <sortCondition ref="A1:A465"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9D2F6B4F-52C3-6B46-B201-F77B94AF0593}" name="Table1" displayName="Table1" ref="A1:G465" totalsRowShown="0">
+  <autoFilter ref="A1:G465" xr:uid="{9D2F6B4F-52C3-6B46-B201-F77B94AF0593}">
+    <filterColumn colId="3">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G464">
+    <sortCondition ref="B1:B465"/>
   </sortState>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{3203C3A6-50D8-DD4C-80B4-06BC4BEB47B2}" name="cargo" dataDxfId="0"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{3203C3A6-50D8-DD4C-80B4-06BC4BEB47B2}" name="cargo" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{33160495-9720-6A40-B7C2-1BBB379EE15A}" name="nombre"/>
-    <tableColumn id="5" xr3:uid="{20D9C665-014D-D942-9492-5BC018045525}" name="cargo_asimilado" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{14317EFC-DF48-B644-824E-F5949347DC2C}" name="dedicación" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{72E047F7-BB5D-8541-8732-5A76D9C0CD02}" name="actividad" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{20D9C665-014D-D942-9492-5BC018045525}" name="cargo_asimilado" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{14317EFC-DF48-B644-824E-F5949347DC2C}" name="dedicación_porcentual" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{A017F2E9-BB07-534B-9232-D1F6356DE37A}" name="dedicación_horaria"/>
+    <tableColumn id="7" xr3:uid="{72E047F7-BB5D-8541-8732-5A76D9C0CD02}" name="actividad" dataDxfId="0"/>
     <tableColumn id="8" xr3:uid="{B2F1B344-4C3C-DA4A-AC1E-7332BD2A3B7D}" name="centro"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2067,16 +2077,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F465"/>
+  <dimension ref="A1:G465"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="73.6640625" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2087,36 +2097,39 @@
         <v>453</v>
       </c>
       <c r="D1" t="s">
+        <v>521</v>
+      </c>
+      <c r="E1" t="s">
+        <v>522</v>
+      </c>
+      <c r="F1" t="s">
         <v>454</v>
       </c>
-      <c r="E1" t="s">
-        <v>455</v>
-      </c>
-      <c r="F1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="3">
-        <v>1</v>
+        <v>490</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>388</v>
       </c>
       <c r="C2" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="F2" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>0.375</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="G2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" hidden="1">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2129,11 +2142,11 @@
       <c r="D3" t="s">
         <v>63</v>
       </c>
-      <c r="E3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="F3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" hidden="1">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2146,11 +2159,11 @@
       <c r="D4" t="s">
         <v>63</v>
       </c>
-      <c r="E4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="F4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" hidden="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2163,11 +2176,11 @@
       <c r="D5" t="s">
         <v>63</v>
       </c>
-      <c r="E5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="F5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" hidden="1">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2180,11 +2193,11 @@
       <c r="D6" t="s">
         <v>63</v>
       </c>
-      <c r="E6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="F6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" hidden="1">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2197,11 +2210,11 @@
       <c r="D7" t="s">
         <v>63</v>
       </c>
-      <c r="E7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" hidden="1">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2214,11 +2227,11 @@
       <c r="D8" t="s">
         <v>63</v>
       </c>
-      <c r="E8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="F8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" hidden="1">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2231,11 +2244,11 @@
       <c r="D9" t="s">
         <v>63</v>
       </c>
-      <c r="E9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="F9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" hidden="1">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2248,12 +2261,12 @@
       <c r="D10" t="s">
         <v>63</v>
       </c>
-      <c r="E10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" hidden="1">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2266,11 +2279,11 @@
       <c r="D11" t="s">
         <v>63</v>
       </c>
-      <c r="E11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" hidden="1">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -2283,11 +2296,11 @@
       <c r="D12" t="s">
         <v>63</v>
       </c>
-      <c r="E12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" hidden="1">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2300,11 +2313,11 @@
       <c r="D13" t="s">
         <v>63</v>
       </c>
-      <c r="E13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="F13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" hidden="1">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -2317,11 +2330,11 @@
       <c r="D14" t="s">
         <v>63</v>
       </c>
-      <c r="E14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="F14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" hidden="1">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -2334,11 +2347,11 @@
       <c r="D15" t="s">
         <v>63</v>
       </c>
-      <c r="E15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="F15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" hidden="1">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -2351,11 +2364,11 @@
       <c r="D16" t="s">
         <v>63</v>
       </c>
-      <c r="E16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="F16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" hidden="1">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -2368,11 +2381,11 @@
       <c r="D17" t="s">
         <v>63</v>
       </c>
-      <c r="E17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="F17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" hidden="1">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -2385,31 +2398,34 @@
       <c r="D18" t="s">
         <v>63</v>
       </c>
-      <c r="E18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="F18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="3">
-        <v>18</v>
+        <v>421</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>328</v>
       </c>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19">
-        <v>0.375</v>
-      </c>
-      <c r="E19" t="s">
-        <v>496</v>
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>400</v>
       </c>
       <c r="F19" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>487</v>
+      </c>
+      <c r="G19" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" hidden="1">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -2422,11 +2438,11 @@
       <c r="D20" t="s">
         <v>63</v>
       </c>
-      <c r="E20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="F20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" hidden="1">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -2437,31 +2453,34 @@
       <c r="D21" t="s">
         <v>63</v>
       </c>
-      <c r="E21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="F21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="C22" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D22">
-        <v>0.375</v>
-      </c>
-      <c r="E22" t="s">
-        <v>457</v>
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>250</v>
       </c>
       <c r="F22" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>495</v>
+      </c>
+      <c r="G22" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" hidden="1">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -2472,11 +2491,11 @@
       <c r="D23" t="s">
         <v>63</v>
       </c>
-      <c r="E23" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="F23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" hidden="1">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -2489,11 +2508,11 @@
       <c r="D24" t="s">
         <v>63</v>
       </c>
-      <c r="E24" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="F24" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" hidden="1">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -2506,11 +2525,11 @@
       <c r="D25" t="s">
         <v>63</v>
       </c>
-      <c r="E25" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="F25" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" hidden="1">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -2523,11 +2542,11 @@
       <c r="D26" t="s">
         <v>63</v>
       </c>
-      <c r="E26" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="F26" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" hidden="1">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -2540,11 +2559,11 @@
       <c r="D27" t="s">
         <v>63</v>
       </c>
-      <c r="E27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="F27" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" hidden="1">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -2557,11 +2576,11 @@
       <c r="D28" t="s">
         <v>63</v>
       </c>
-      <c r="E28" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="F28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" hidden="1">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -2574,11 +2593,11 @@
       <c r="D29" t="s">
         <v>63</v>
       </c>
-      <c r="E29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="F29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" hidden="1">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -2591,31 +2610,34 @@
       <c r="D30" t="s">
         <v>63</v>
       </c>
-      <c r="E30" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="F30" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="3">
-        <v>30</v>
+        <v>198</v>
       </c>
       <c r="B31" t="s">
-        <v>212</v>
+        <v>108</v>
       </c>
       <c r="C31" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D31">
-        <v>0.375</v>
-      </c>
-      <c r="E31" t="s">
-        <v>458</v>
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>250</v>
       </c>
       <c r="F31" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>487</v>
+      </c>
+      <c r="G31" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" hidden="1">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -2628,11 +2650,11 @@
       <c r="D32" t="s">
         <v>63</v>
       </c>
-      <c r="E32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="F32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" hidden="1">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -2645,31 +2667,34 @@
       <c r="D33" t="s">
         <v>63</v>
       </c>
-      <c r="E33" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="F33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="3">
-        <v>33</v>
+        <v>360</v>
       </c>
       <c r="B34" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="C34" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D34">
-        <v>0.625</v>
-      </c>
-      <c r="E34" t="s">
-        <v>458</v>
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>250</v>
       </c>
       <c r="F34" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>487</v>
+      </c>
+      <c r="G34" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -2682,11 +2707,11 @@
       <c r="D35" t="s">
         <v>63</v>
       </c>
-      <c r="E35" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="F35" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -2699,11 +2724,11 @@
       <c r="D36" t="s">
         <v>63</v>
       </c>
-      <c r="E36" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="F36" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -2716,11 +2741,11 @@
       <c r="D37" t="s">
         <v>63</v>
       </c>
-      <c r="E37" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="F37" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -2733,11 +2758,11 @@
       <c r="D38" t="s">
         <v>63</v>
       </c>
-      <c r="E38" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="F38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -2750,11 +2775,11 @@
       <c r="D39" t="s">
         <v>63</v>
       </c>
-      <c r="E39" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="F39" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -2767,11 +2792,11 @@
       <c r="D40" t="s">
         <v>63</v>
       </c>
-      <c r="E40" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="F40" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -2784,11 +2809,11 @@
       <c r="D41" t="s">
         <v>63</v>
       </c>
-      <c r="E41" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="F41" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -2801,11 +2826,11 @@
       <c r="D42" t="s">
         <v>63</v>
       </c>
-      <c r="E42" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="F42" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -2818,11 +2843,11 @@
       <c r="D43" t="s">
         <v>63</v>
       </c>
-      <c r="E43" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="F43" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -2835,11 +2860,11 @@
       <c r="D44" t="s">
         <v>63</v>
       </c>
-      <c r="E44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="F44" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -2852,11 +2877,11 @@
       <c r="D45" t="s">
         <v>63</v>
       </c>
-      <c r="E45" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="F45" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -2869,11 +2894,11 @@
       <c r="D46" t="s">
         <v>63</v>
       </c>
-      <c r="E46" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+      <c r="F46" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -2886,11 +2911,11 @@
       <c r="D47" t="s">
         <v>63</v>
       </c>
-      <c r="E47" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="F47" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" hidden="1">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -2903,11 +2928,11 @@
       <c r="D48" t="s">
         <v>63</v>
       </c>
-      <c r="E48" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="F48" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" hidden="1">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -2920,11 +2945,11 @@
       <c r="D49" t="s">
         <v>63</v>
       </c>
-      <c r="E49" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="F49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" hidden="1">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -2937,11 +2962,11 @@
       <c r="D50" t="s">
         <v>63</v>
       </c>
-      <c r="E50" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="F50" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" hidden="1">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -2954,11 +2979,11 @@
       <c r="D51" t="s">
         <v>63</v>
       </c>
-      <c r="E51" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="F51" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" hidden="1">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -2971,11 +2996,11 @@
       <c r="D52" t="s">
         <v>63</v>
       </c>
-      <c r="E52" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="F52" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" hidden="1">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -2988,11 +3013,11 @@
       <c r="D53" t="s">
         <v>63</v>
       </c>
-      <c r="E53" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="F53" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" hidden="1">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -3005,11 +3030,11 @@
       <c r="D54" t="s">
         <v>63</v>
       </c>
-      <c r="E54" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="F54" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" hidden="1">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -3022,11 +3047,11 @@
       <c r="D55" t="s">
         <v>63</v>
       </c>
-      <c r="E55" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+      <c r="F55" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" hidden="1">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -3039,11 +3064,11 @@
       <c r="D56" t="s">
         <v>63</v>
       </c>
-      <c r="E56" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+      <c r="F56" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" hidden="1">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -3056,11 +3081,11 @@
       <c r="D57" t="s">
         <v>63</v>
       </c>
-      <c r="E57" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+      <c r="F57" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" hidden="1">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -3073,11 +3098,11 @@
       <c r="D58" t="s">
         <v>63</v>
       </c>
-      <c r="E58" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+      <c r="F58" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" hidden="1">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -3090,11 +3115,11 @@
       <c r="D59" t="s">
         <v>63</v>
       </c>
-      <c r="E59" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+      <c r="F59" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" hidden="1">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -3107,11 +3132,11 @@
       <c r="D60" t="s">
         <v>63</v>
       </c>
-      <c r="E60" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+      <c r="F60" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" hidden="1">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -3124,11 +3149,11 @@
       <c r="D61" t="s">
         <v>63</v>
       </c>
-      <c r="E61" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+      <c r="F61" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" hidden="1">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -3141,11 +3166,11 @@
       <c r="D62" t="s">
         <v>63</v>
       </c>
-      <c r="E62" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+      <c r="F62" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" hidden="1">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -3158,11 +3183,11 @@
       <c r="D63" t="s">
         <v>63</v>
       </c>
-      <c r="E63" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+      <c r="F63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" hidden="1">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -3175,11 +3200,11 @@
       <c r="D64" t="s">
         <v>63</v>
       </c>
-      <c r="E64" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="F64" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" hidden="1">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -3192,31 +3217,34 @@
       <c r="D65" t="s">
         <v>63</v>
       </c>
-      <c r="E65" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="F65" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" s="3">
-        <v>65</v>
+        <v>361</v>
       </c>
       <c r="B66" t="s">
-        <v>417</v>
+        <v>268</v>
       </c>
       <c r="C66" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66" t="s">
-        <v>459</v>
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>250</v>
       </c>
       <c r="F66" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+        <v>487</v>
+      </c>
+      <c r="G66" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" hidden="1">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -3229,31 +3257,31 @@
       <c r="D67" t="s">
         <v>63</v>
       </c>
-      <c r="E67" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="F67" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" s="3">
-        <v>67</v>
+        <v>397</v>
       </c>
       <c r="B68" t="s">
-        <v>419</v>
+        <v>303</v>
       </c>
       <c r="C68" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D68">
-        <v>0.375</v>
-      </c>
-      <c r="E68" t="s">
-        <v>460</v>
+        <v>0.25</v>
       </c>
       <c r="F68" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+        <v>466</v>
+      </c>
+      <c r="G68" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" hidden="1">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -3266,11 +3294,11 @@
       <c r="D69" t="s">
         <v>63</v>
       </c>
-      <c r="E69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+      <c r="F69" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" hidden="1">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -3283,11 +3311,11 @@
       <c r="D70" t="s">
         <v>63</v>
       </c>
-      <c r="E70" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+      <c r="F70" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" hidden="1">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -3300,11 +3328,11 @@
       <c r="D71" t="s">
         <v>63</v>
       </c>
-      <c r="E71" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+      <c r="F71" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" hidden="1">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -3317,11 +3345,11 @@
       <c r="D72" t="s">
         <v>63</v>
       </c>
-      <c r="E72" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+      <c r="F72" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" hidden="1">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -3334,11 +3362,11 @@
       <c r="D73" t="s">
         <v>63</v>
       </c>
-      <c r="E73" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="F73" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" hidden="1">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -3351,11 +3379,11 @@
       <c r="D74" t="s">
         <v>63</v>
       </c>
-      <c r="E74" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+      <c r="F74" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" hidden="1">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -3368,11 +3396,11 @@
       <c r="D75" t="s">
         <v>63</v>
       </c>
-      <c r="E75" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="F75" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" hidden="1">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -3385,11 +3413,11 @@
       <c r="D76" t="s">
         <v>63</v>
       </c>
-      <c r="E76" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+      <c r="F76" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" hidden="1">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -3402,11 +3430,11 @@
       <c r="D77" t="s">
         <v>63</v>
       </c>
-      <c r="E77" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="F77" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" hidden="1">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -3419,11 +3447,11 @@
       <c r="D78" t="s">
         <v>63</v>
       </c>
-      <c r="E78" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
+      <c r="F78" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" hidden="1">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -3436,11 +3464,11 @@
       <c r="D79" t="s">
         <v>63</v>
       </c>
-      <c r="E79" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
+      <c r="F79" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" hidden="1">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -3453,11 +3481,11 @@
       <c r="D80" t="s">
         <v>63</v>
       </c>
-      <c r="E80" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+      <c r="F80" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" hidden="1">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -3470,11 +3498,11 @@
       <c r="D81" t="s">
         <v>63</v>
       </c>
-      <c r="E81" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
+      <c r="F81" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" hidden="1">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -3487,11 +3515,11 @@
       <c r="D82" t="s">
         <v>63</v>
       </c>
-      <c r="E82" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="F82" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" hidden="1">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -3504,31 +3532,34 @@
       <c r="D83" t="s">
         <v>63</v>
       </c>
-      <c r="E83" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
+      <c r="F83" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84" s="3">
-        <v>83</v>
+        <v>307</v>
       </c>
       <c r="B84" t="s">
-        <v>437</v>
+        <v>219</v>
       </c>
       <c r="C84" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D84">
-        <v>1</v>
-      </c>
-      <c r="E84" t="s">
-        <v>461</v>
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>250</v>
       </c>
       <c r="F84" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
+        <v>489</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" hidden="1">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -3541,11 +3572,11 @@
       <c r="D85" t="s">
         <v>63</v>
       </c>
-      <c r="E85" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
+      <c r="F85" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" hidden="1">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -3558,11 +3589,11 @@
       <c r="D86" t="s">
         <v>63</v>
       </c>
-      <c r="E86" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
+      <c r="F86" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" hidden="1">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -3575,11 +3606,11 @@
       <c r="D87" t="s">
         <v>63</v>
       </c>
-      <c r="E87" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
+      <c r="F87" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" hidden="1">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -3592,11 +3623,11 @@
       <c r="D88" t="s">
         <v>63</v>
       </c>
-      <c r="E88" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
+      <c r="F88" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" hidden="1">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -3609,11 +3640,11 @@
       <c r="D89" t="s">
         <v>63</v>
       </c>
-      <c r="E89" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
+      <c r="F89" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" hidden="1">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -3626,11 +3657,11 @@
       <c r="D90" t="s">
         <v>63</v>
       </c>
-      <c r="E90" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
+      <c r="F90" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" hidden="1">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -3643,11 +3674,11 @@
       <c r="D91" t="s">
         <v>63</v>
       </c>
-      <c r="E91" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="F91" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" hidden="1">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -3660,11 +3691,11 @@
       <c r="D92" t="s">
         <v>63</v>
       </c>
-      <c r="E92" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
+      <c r="F92" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" hidden="1">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -3677,11 +3708,11 @@
       <c r="D93" t="s">
         <v>63</v>
       </c>
-      <c r="E93" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
+      <c r="F93" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" hidden="1">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -3694,11 +3725,11 @@
       <c r="D94" t="s">
         <v>63</v>
       </c>
-      <c r="E94" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
+      <c r="F94" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" hidden="1">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -3711,11 +3742,11 @@
       <c r="D95" t="s">
         <v>63</v>
       </c>
-      <c r="E95" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
+      <c r="F95" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" hidden="1">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -3728,11 +3759,11 @@
       <c r="D96" t="s">
         <v>63</v>
       </c>
-      <c r="E96" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+      <c r="F96" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" hidden="1">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -3745,11 +3776,11 @@
       <c r="D97" t="s">
         <v>63</v>
       </c>
-      <c r="E97" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+      <c r="F97" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" hidden="1">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -3762,11 +3793,11 @@
       <c r="D98" t="s">
         <v>63</v>
       </c>
-      <c r="E98" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+      <c r="F98" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" hidden="1">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -3779,11 +3810,11 @@
       <c r="D99" t="s">
         <v>63</v>
       </c>
-      <c r="E99" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+      <c r="F99" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" hidden="1">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -3796,11 +3827,11 @@
       <c r="D100" t="s">
         <v>63</v>
       </c>
-      <c r="E100" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+      <c r="F100" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" hidden="1">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -3813,11 +3844,11 @@
       <c r="D101" t="s">
         <v>63</v>
       </c>
-      <c r="E101" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+      <c r="F101" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" hidden="1">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -3830,11 +3861,11 @@
       <c r="D102" t="s">
         <v>63</v>
       </c>
-      <c r="E102" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
+      <c r="F102" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" hidden="1">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -3847,11 +3878,11 @@
       <c r="D103" t="s">
         <v>63</v>
       </c>
-      <c r="E103" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
+      <c r="F103" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" hidden="1">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -3864,11 +3895,11 @@
       <c r="D104" t="s">
         <v>63</v>
       </c>
-      <c r="E104" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
+      <c r="F104" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" hidden="1">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -3881,11 +3912,11 @@
       <c r="D105" t="s">
         <v>63</v>
       </c>
-      <c r="E105" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
+      <c r="F105" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" hidden="1">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -3898,11 +3929,11 @@
       <c r="D106" t="s">
         <v>63</v>
       </c>
-      <c r="E106" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
+      <c r="F106" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" hidden="1">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -3915,11 +3946,11 @@
       <c r="D107" t="s">
         <v>63</v>
       </c>
-      <c r="E107" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
+      <c r="F107" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" hidden="1">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -3932,11 +3963,11 @@
       <c r="D108" t="s">
         <v>63</v>
       </c>
-      <c r="E108" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
+      <c r="F108" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" hidden="1">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -3949,11 +3980,11 @@
       <c r="D109" t="s">
         <v>63</v>
       </c>
-      <c r="E109" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
+      <c r="F109" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" hidden="1">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -3966,11 +3997,11 @@
       <c r="D110" t="s">
         <v>63</v>
       </c>
-      <c r="E110" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
+      <c r="F110" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" hidden="1">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -3983,11 +4014,11 @@
       <c r="D111" t="s">
         <v>63</v>
       </c>
-      <c r="E111" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
+      <c r="F111" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" hidden="1">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -4000,11 +4031,11 @@
       <c r="D112" t="s">
         <v>63</v>
       </c>
-      <c r="E112" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
+      <c r="F112" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" hidden="1">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -4017,11 +4048,11 @@
       <c r="D113" t="s">
         <v>63</v>
       </c>
-      <c r="E113" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
+      <c r="F113" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" hidden="1">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -4034,31 +4065,34 @@
       <c r="D114" t="s">
         <v>63</v>
       </c>
-      <c r="E114" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="F114" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" s="3">
-        <v>114</v>
+        <v>292</v>
       </c>
       <c r="B115" t="s">
-        <v>19</v>
+        <v>203</v>
       </c>
       <c r="C115" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D115">
-        <v>0.375</v>
-      </c>
-      <c r="E115" t="s">
-        <v>462</v>
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>400</v>
       </c>
       <c r="F115" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
+        <v>487</v>
+      </c>
+      <c r="G115" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" hidden="1">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -4069,11 +4103,11 @@
       <c r="D116" t="s">
         <v>63</v>
       </c>
-      <c r="E116" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
+      <c r="F116" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" hidden="1">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -4084,11 +4118,11 @@
       <c r="D117" t="s">
         <v>63</v>
       </c>
-      <c r="E117" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="F117" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" hidden="1">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -4101,11 +4135,11 @@
       <c r="D118" t="s">
         <v>63</v>
       </c>
-      <c r="E118" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
+      <c r="F118" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" hidden="1">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -4118,11 +4152,11 @@
       <c r="D119" t="s">
         <v>63</v>
       </c>
-      <c r="E119" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
+      <c r="F119" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" hidden="1">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -4133,11 +4167,11 @@
       <c r="D120" t="s">
         <v>63</v>
       </c>
-      <c r="E120" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+      <c r="F120" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" hidden="1">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -4150,11 +4184,11 @@
       <c r="D121" t="s">
         <v>63</v>
       </c>
-      <c r="E121" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="F121" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" hidden="1">
       <c r="A122" s="3">
         <v>121</v>
       </c>
@@ -4167,11 +4201,11 @@
       <c r="D122" t="s">
         <v>63</v>
       </c>
-      <c r="E122" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
+      <c r="F122" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" hidden="1">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -4184,11 +4218,11 @@
       <c r="D123" t="s">
         <v>63</v>
       </c>
-      <c r="E123" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+      <c r="F123" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" hidden="1">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -4201,11 +4235,11 @@
       <c r="D124" t="s">
         <v>63</v>
       </c>
-      <c r="E124" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
+      <c r="F124" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" hidden="1">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -4218,11 +4252,11 @@
       <c r="D125" t="s">
         <v>63</v>
       </c>
-      <c r="E125" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
+      <c r="F125" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" hidden="1">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -4235,11 +4269,11 @@
       <c r="D126" t="s">
         <v>63</v>
       </c>
-      <c r="E126" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
+      <c r="F126" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" hidden="1">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -4252,11 +4286,11 @@
       <c r="D127" t="s">
         <v>63</v>
       </c>
-      <c r="E127" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
+      <c r="F127" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" hidden="1">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -4269,11 +4303,11 @@
       <c r="D128" t="s">
         <v>63</v>
       </c>
-      <c r="E128" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
+      <c r="F128" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" hidden="1">
       <c r="A129" s="3">
         <v>128</v>
       </c>
@@ -4286,11 +4320,11 @@
       <c r="D129" t="s">
         <v>63</v>
       </c>
-      <c r="E129" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
+      <c r="F129" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" hidden="1">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -4303,11 +4337,11 @@
       <c r="D130" t="s">
         <v>63</v>
       </c>
-      <c r="E130" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
+      <c r="F130" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" hidden="1">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -4320,11 +4354,11 @@
       <c r="D131" t="s">
         <v>63</v>
       </c>
-      <c r="E131" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
+      <c r="F131" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" hidden="1">
       <c r="A132" s="3">
         <v>131</v>
       </c>
@@ -4335,11 +4369,11 @@
       <c r="D132" t="s">
         <v>63</v>
       </c>
-      <c r="E132" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
+      <c r="F132" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" hidden="1">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -4352,11 +4386,11 @@
       <c r="D133" t="s">
         <v>63</v>
       </c>
-      <c r="E133" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
+      <c r="F133" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" hidden="1">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -4369,11 +4403,11 @@
       <c r="D134" t="s">
         <v>63</v>
       </c>
-      <c r="E134" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
+      <c r="F134" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" hidden="1">
       <c r="A135" s="3">
         <v>134</v>
       </c>
@@ -4386,11 +4420,11 @@
       <c r="D135" t="s">
         <v>63</v>
       </c>
-      <c r="E135" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
+      <c r="F135" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" hidden="1">
       <c r="A136" s="3">
         <v>135</v>
       </c>
@@ -4403,11 +4437,11 @@
       <c r="D136" t="s">
         <v>63</v>
       </c>
-      <c r="E136" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
+      <c r="F136" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" hidden="1">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -4418,11 +4452,11 @@
       <c r="D137" t="s">
         <v>63</v>
       </c>
-      <c r="E137" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
+      <c r="F137" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" hidden="1">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -4433,11 +4467,11 @@
       <c r="D138" t="s">
         <v>63</v>
       </c>
-      <c r="E138" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
+      <c r="F138" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" hidden="1">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -4450,11 +4484,11 @@
       <c r="D139" t="s">
         <v>63</v>
       </c>
-      <c r="E139" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
+      <c r="F139" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" hidden="1">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -4467,11 +4501,11 @@
       <c r="D140" t="s">
         <v>63</v>
       </c>
-      <c r="E140" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
+      <c r="F140" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" hidden="1">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -4484,11 +4518,11 @@
       <c r="D141" t="s">
         <v>63</v>
       </c>
-      <c r="E141" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
+      <c r="F141" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" hidden="1">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -4501,11 +4535,11 @@
       <c r="D142" t="s">
         <v>63</v>
       </c>
-      <c r="E142" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
+      <c r="F142" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" hidden="1">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -4518,11 +4552,11 @@
       <c r="D143" t="s">
         <v>63</v>
       </c>
-      <c r="E143" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
+      <c r="F143" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" hidden="1">
       <c r="A144" s="3">
         <v>143</v>
       </c>
@@ -4535,11 +4569,11 @@
       <c r="D144" t="s">
         <v>63</v>
       </c>
-      <c r="E144" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
+      <c r="F144" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" hidden="1">
       <c r="A145" s="3">
         <v>144</v>
       </c>
@@ -4552,11 +4586,11 @@
       <c r="D145" t="s">
         <v>63</v>
       </c>
-      <c r="E145" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
+      <c r="F145" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" hidden="1">
       <c r="A146" s="3">
         <v>145</v>
       </c>
@@ -4569,11 +4603,11 @@
       <c r="D146" t="s">
         <v>63</v>
       </c>
-      <c r="E146" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
+      <c r="F146" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" hidden="1">
       <c r="A147" s="3">
         <v>146</v>
       </c>
@@ -4586,11 +4620,11 @@
       <c r="D147" t="s">
         <v>63</v>
       </c>
-      <c r="E147" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
+      <c r="F147" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" hidden="1">
       <c r="A148" s="3">
         <v>147</v>
       </c>
@@ -4603,11 +4637,11 @@
       <c r="D148" t="s">
         <v>63</v>
       </c>
-      <c r="E148" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
+      <c r="F148" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" hidden="1">
       <c r="A149" s="3">
         <v>148</v>
       </c>
@@ -4620,11 +4654,11 @@
       <c r="D149" t="s">
         <v>63</v>
       </c>
-      <c r="E149" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
+      <c r="F149" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" hidden="1">
       <c r="A150" s="3">
         <v>149</v>
       </c>
@@ -4637,11 +4671,11 @@
       <c r="D150" t="s">
         <v>63</v>
       </c>
-      <c r="E150" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
+      <c r="F150" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" hidden="1">
       <c r="A151" s="3">
         <v>150</v>
       </c>
@@ -4654,11 +4688,11 @@
       <c r="D151" t="s">
         <v>63</v>
       </c>
-      <c r="E151" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
+      <c r="F151" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" hidden="1">
       <c r="A152" s="3">
         <v>151</v>
       </c>
@@ -4671,11 +4705,11 @@
       <c r="D152" t="s">
         <v>63</v>
       </c>
-      <c r="E152" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
+      <c r="F152" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" hidden="1">
       <c r="A153" s="3">
         <v>152</v>
       </c>
@@ -4688,11 +4722,11 @@
       <c r="D153" t="s">
         <v>63</v>
       </c>
-      <c r="E153" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
+      <c r="F153" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" hidden="1">
       <c r="A154" s="3">
         <v>153</v>
       </c>
@@ -4705,11 +4739,11 @@
       <c r="D154" t="s">
         <v>63</v>
       </c>
-      <c r="E154" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
+      <c r="F154" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" hidden="1">
       <c r="A155" s="3">
         <v>154</v>
       </c>
@@ -4719,11 +4753,11 @@
       <c r="D155" t="s">
         <v>63</v>
       </c>
-      <c r="E155" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
+      <c r="F155" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" hidden="1">
       <c r="A156" s="3">
         <v>155</v>
       </c>
@@ -4733,11 +4767,11 @@
       <c r="D156" t="s">
         <v>63</v>
       </c>
-      <c r="E156" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5">
+      <c r="F156" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" hidden="1">
       <c r="A157" s="3">
         <v>156</v>
       </c>
@@ -4747,11 +4781,11 @@
       <c r="D157" t="s">
         <v>63</v>
       </c>
-      <c r="E157" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
+      <c r="F157" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" hidden="1">
       <c r="A158" s="3">
         <v>157</v>
       </c>
@@ -4761,11 +4795,11 @@
       <c r="D158" t="s">
         <v>63</v>
       </c>
-      <c r="E158" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5">
+      <c r="F158" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" hidden="1">
       <c r="A159" s="3">
         <v>158</v>
       </c>
@@ -4775,11 +4809,11 @@
       <c r="D159" t="s">
         <v>63</v>
       </c>
-      <c r="E159" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5">
+      <c r="F159" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" hidden="1">
       <c r="A160" s="3">
         <v>159</v>
       </c>
@@ -4789,11 +4823,11 @@
       <c r="D160" t="s">
         <v>63</v>
       </c>
-      <c r="E160" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
+      <c r="F160" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" hidden="1">
       <c r="A161" s="3">
         <v>160</v>
       </c>
@@ -4803,11 +4837,11 @@
       <c r="D161" t="s">
         <v>63</v>
       </c>
-      <c r="E161" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5">
+      <c r="F161" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" hidden="1">
       <c r="A162" s="3">
         <v>161</v>
       </c>
@@ -4817,11 +4851,11 @@
       <c r="D162" t="s">
         <v>63</v>
       </c>
-      <c r="E162" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5">
+      <c r="F162" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" hidden="1">
       <c r="A163" s="3">
         <v>162</v>
       </c>
@@ -4834,11 +4868,11 @@
       <c r="D163" t="s">
         <v>63</v>
       </c>
-      <c r="E163" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5">
+      <c r="F163" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" hidden="1">
       <c r="A164" s="3">
         <v>163</v>
       </c>
@@ -4851,11 +4885,11 @@
       <c r="D164" t="s">
         <v>63</v>
       </c>
-      <c r="E164" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5">
+      <c r="F164" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" hidden="1">
       <c r="A165" s="3">
         <v>164</v>
       </c>
@@ -4866,11 +4900,11 @@
       <c r="D165" t="s">
         <v>63</v>
       </c>
-      <c r="E165" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5">
+      <c r="F165" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" hidden="1">
       <c r="A166" s="3">
         <v>165</v>
       </c>
@@ -4883,11 +4917,11 @@
       <c r="D166" t="s">
         <v>63</v>
       </c>
-      <c r="E166" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5">
+      <c r="F166" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" hidden="1">
       <c r="A167" s="3">
         <v>166</v>
       </c>
@@ -4898,11 +4932,11 @@
       <c r="D167" t="s">
         <v>63</v>
       </c>
-      <c r="E167" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5">
+      <c r="F167" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" hidden="1">
       <c r="A168" s="3">
         <v>167</v>
       </c>
@@ -4913,11 +4947,11 @@
       <c r="D168" t="s">
         <v>63</v>
       </c>
-      <c r="E168" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5">
+      <c r="F168" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" hidden="1">
       <c r="A169" s="3">
         <v>168</v>
       </c>
@@ -4928,11 +4962,11 @@
       <c r="D169" t="s">
         <v>63</v>
       </c>
-      <c r="E169" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
+      <c r="F169" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" hidden="1">
       <c r="A170" s="3">
         <v>169</v>
       </c>
@@ -4942,11 +4976,11 @@
       <c r="D170" t="s">
         <v>63</v>
       </c>
-      <c r="E170" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5">
+      <c r="F170" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" hidden="1">
       <c r="A171" s="3">
         <v>170</v>
       </c>
@@ -4957,11 +4991,11 @@
       <c r="D171" t="s">
         <v>63</v>
       </c>
-      <c r="E171" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5">
+      <c r="F171" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" hidden="1">
       <c r="A172" s="3">
         <v>171</v>
       </c>
@@ -4972,11 +5006,11 @@
       <c r="D172" t="s">
         <v>63</v>
       </c>
-      <c r="E172" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
+      <c r="F172" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" hidden="1">
       <c r="A173" s="3">
         <v>172</v>
       </c>
@@ -4987,11 +5021,11 @@
       <c r="D173" t="s">
         <v>63</v>
       </c>
-      <c r="E173" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
+      <c r="F173" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" hidden="1">
       <c r="A174" s="3">
         <v>173</v>
       </c>
@@ -5002,11 +5036,11 @@
       <c r="D174" t="s">
         <v>63</v>
       </c>
-      <c r="E174" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5">
+      <c r="F174" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" hidden="1">
       <c r="A175" s="3">
         <v>174</v>
       </c>
@@ -5017,11 +5051,11 @@
       <c r="D175" t="s">
         <v>63</v>
       </c>
-      <c r="E175" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
+      <c r="F175" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" hidden="1">
       <c r="A176" s="3">
         <v>176</v>
       </c>
@@ -5032,11 +5066,11 @@
       <c r="D176" t="s">
         <v>63</v>
       </c>
-      <c r="E176" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6">
+      <c r="F176" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" hidden="1">
       <c r="A177" s="3">
         <v>177</v>
       </c>
@@ -5047,51 +5081,57 @@
       <c r="D177" t="s">
         <v>63</v>
       </c>
-      <c r="E177" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6">
+      <c r="F177" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
       <c r="A178" s="3">
-        <v>178</v>
+        <v>293</v>
       </c>
       <c r="B178" t="s">
-        <v>88</v>
+        <v>204</v>
       </c>
       <c r="C178" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D178">
-        <v>0.375</v>
-      </c>
-      <c r="E178" t="s">
+        <v>0</v>
+      </c>
+      <c r="E178">
+        <v>400</v>
+      </c>
+      <c r="F178" t="s">
         <v>487</v>
       </c>
-      <c r="F178" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6">
+      <c r="G178" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
       <c r="A179" s="3">
-        <v>179</v>
+        <v>431</v>
       </c>
       <c r="B179" t="s">
-        <v>89</v>
+        <v>337</v>
       </c>
       <c r="C179" s="1">
         <v>7</v>
       </c>
       <c r="D179">
-        <v>0.375</v>
-      </c>
-      <c r="E179" t="s">
-        <v>487</v>
+        <v>0</v>
+      </c>
+      <c r="E179">
+        <v>250</v>
       </c>
       <c r="F179" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6">
+        <v>489</v>
+      </c>
+      <c r="G179" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" hidden="1">
       <c r="A180" s="3">
         <v>180</v>
       </c>
@@ -5102,11 +5142,11 @@
       <c r="D180" t="s">
         <v>63</v>
       </c>
-      <c r="E180" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="F180" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" hidden="1">
       <c r="A181" s="3">
         <v>182</v>
       </c>
@@ -5117,11 +5157,11 @@
       <c r="D181" t="s">
         <v>63</v>
       </c>
-      <c r="E181" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6">
+      <c r="F181" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" hidden="1">
       <c r="A182" s="3">
         <v>183</v>
       </c>
@@ -5132,11 +5172,11 @@
       <c r="D182" t="s">
         <v>63</v>
       </c>
-      <c r="E182" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6">
+      <c r="F182" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" hidden="1">
       <c r="A183" s="3">
         <v>184</v>
       </c>
@@ -5147,11 +5187,11 @@
       <c r="D183" t="s">
         <v>63</v>
       </c>
-      <c r="E183" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6">
+      <c r="F183" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" hidden="1">
       <c r="A184" s="3">
         <v>185</v>
       </c>
@@ -5162,11 +5202,11 @@
       <c r="D184" t="s">
         <v>63</v>
       </c>
-      <c r="E184" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6">
+      <c r="F184" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" hidden="1">
       <c r="A185" s="3">
         <v>186</v>
       </c>
@@ -5177,11 +5217,11 @@
       <c r="D185" t="s">
         <v>63</v>
       </c>
-      <c r="E185" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6">
+      <c r="F185" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" hidden="1">
       <c r="A186" s="3">
         <v>187</v>
       </c>
@@ -5192,111 +5232,126 @@
       <c r="D186" t="s">
         <v>63</v>
       </c>
-      <c r="E186" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6">
+      <c r="F186" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
       <c r="A187" s="3">
-        <v>188</v>
+        <v>389</v>
       </c>
       <c r="B187" t="s">
-        <v>98</v>
+        <v>295</v>
       </c>
       <c r="C187" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D187">
-        <v>0.375</v>
-      </c>
-      <c r="E187" t="s">
+        <v>0</v>
+      </c>
+      <c r="E187">
+        <v>250</v>
+      </c>
+      <c r="F187" t="s">
         <v>487</v>
       </c>
-      <c r="F187" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6">
+      <c r="G187" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
       <c r="A188" s="3">
-        <v>189</v>
+        <v>314</v>
       </c>
       <c r="B188" t="s">
-        <v>99</v>
+        <v>227</v>
       </c>
       <c r="C188" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D188">
-        <v>0.625</v>
-      </c>
-      <c r="E188" t="s">
+        <v>0</v>
+      </c>
+      <c r="E188">
+        <v>150</v>
+      </c>
+      <c r="F188" t="s">
         <v>487</v>
       </c>
-      <c r="F188" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6">
+      <c r="G188" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
       <c r="A189" s="3">
-        <v>191</v>
+        <v>430</v>
       </c>
       <c r="B189" t="s">
-        <v>101</v>
+        <v>336</v>
       </c>
       <c r="C189" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D189">
-        <v>0.375</v>
-      </c>
-      <c r="E189" t="s">
+        <v>0</v>
+      </c>
+      <c r="E189">
+        <v>100</v>
+      </c>
+      <c r="F189" t="s">
+        <v>488</v>
+      </c>
+      <c r="G189" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" s="3">
+        <v>499</v>
+      </c>
+      <c r="B190" t="s">
+        <v>396</v>
+      </c>
+      <c r="C190" s="1">
+        <v>8</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="E190">
+        <v>100</v>
+      </c>
+      <c r="F190" t="s">
         <v>487</v>
       </c>
-      <c r="F189" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6">
-      <c r="A190" s="3">
-        <v>192</v>
-      </c>
-      <c r="B190" t="s">
-        <v>102</v>
-      </c>
-      <c r="C190" s="1">
-        <v>5</v>
-      </c>
-      <c r="D190">
-        <v>0.375</v>
-      </c>
-      <c r="E190" t="s">
+      <c r="G190" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" s="3">
+        <v>498</v>
+      </c>
+      <c r="B191" t="s">
+        <v>395</v>
+      </c>
+      <c r="C191" s="1">
+        <v>7</v>
+      </c>
+      <c r="D191">
+        <v>0</v>
+      </c>
+      <c r="E191">
+        <v>100</v>
+      </c>
+      <c r="F191" t="s">
         <v>487</v>
       </c>
-      <c r="F190" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6">
-      <c r="A191" s="3">
-        <v>193</v>
-      </c>
-      <c r="B191" t="s">
-        <v>103</v>
-      </c>
-      <c r="C191" s="1">
-        <v>5</v>
-      </c>
-      <c r="D191">
-        <v>0.375</v>
-      </c>
-      <c r="E191" t="s">
-        <v>487</v>
-      </c>
-      <c r="F191" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6">
+      <c r="G191" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" hidden="1">
       <c r="A192" s="3">
         <v>194</v>
       </c>
@@ -5309,11 +5364,11 @@
       <c r="D192" t="s">
         <v>63</v>
       </c>
-      <c r="E192" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6">
+      <c r="F192" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" hidden="1">
       <c r="A193" s="3">
         <v>195</v>
       </c>
@@ -5326,11 +5381,11 @@
       <c r="D193" t="s">
         <v>63</v>
       </c>
-      <c r="E193" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
+      <c r="F193" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" hidden="1">
       <c r="A194" s="3">
         <v>196</v>
       </c>
@@ -5341,11 +5396,11 @@
       <c r="D194" t="s">
         <v>63</v>
       </c>
-      <c r="E194" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6">
+      <c r="F194" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" hidden="1">
       <c r="A195" s="3">
         <v>197</v>
       </c>
@@ -5358,31 +5413,34 @@
       <c r="D195" t="s">
         <v>63</v>
       </c>
-      <c r="E195" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6">
+      <c r="F195" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
       <c r="A196" s="3">
-        <v>198</v>
+        <v>422</v>
       </c>
       <c r="B196" t="s">
-        <v>108</v>
+        <v>329</v>
       </c>
       <c r="C196" s="1">
         <v>7</v>
       </c>
       <c r="D196">
-        <v>0.375</v>
-      </c>
-      <c r="E196" t="s">
-        <v>488</v>
+        <v>0</v>
+      </c>
+      <c r="E196">
+        <v>200</v>
       </c>
       <c r="F196" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6">
+        <v>487</v>
+      </c>
+      <c r="G196" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" hidden="1">
       <c r="A197" s="3">
         <v>199</v>
       </c>
@@ -5395,31 +5453,34 @@
       <c r="D197" t="s">
         <v>63</v>
       </c>
-      <c r="E197" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6">
+      <c r="F197" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
       <c r="A198" s="3">
-        <v>200</v>
+        <v>423</v>
       </c>
       <c r="B198" t="s">
-        <v>112</v>
+        <v>330</v>
       </c>
       <c r="C198" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D198">
-        <v>0.375</v>
-      </c>
-      <c r="E198" t="s">
-        <v>488</v>
+        <v>0</v>
+      </c>
+      <c r="E198">
+        <v>150</v>
       </c>
       <c r="F198" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6">
+        <v>506</v>
+      </c>
+      <c r="G198" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" hidden="1">
       <c r="A199" s="3">
         <v>201</v>
       </c>
@@ -5433,7 +5494,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:7" hidden="1">
       <c r="A200" s="3">
         <v>202</v>
       </c>
@@ -5446,11 +5507,11 @@
       <c r="D200" t="s">
         <v>63</v>
       </c>
-      <c r="E200" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6">
+      <c r="F200" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" hidden="1">
       <c r="A201" s="3">
         <v>203</v>
       </c>
@@ -5463,11 +5524,11 @@
       <c r="D201" t="s">
         <v>63</v>
       </c>
-      <c r="E201" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6">
+      <c r="F201" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" hidden="1">
       <c r="A202" s="3">
         <v>204</v>
       </c>
@@ -5480,31 +5541,31 @@
       <c r="D202" t="s">
         <v>63</v>
       </c>
-      <c r="E202" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
+      <c r="F202" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
       <c r="A203" s="3">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="B203" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C203" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D203">
-        <v>0.375</v>
-      </c>
-      <c r="E203" t="s">
-        <v>463</v>
+        <v>0.625</v>
       </c>
       <c r="F203" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
+        <v>486</v>
+      </c>
+      <c r="G203" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" hidden="1">
       <c r="A204" s="3">
         <v>207</v>
       </c>
@@ -5515,11 +5576,11 @@
       <c r="D204" t="s">
         <v>63</v>
       </c>
-      <c r="E204" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6">
+      <c r="F204" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" hidden="1">
       <c r="A205" s="3">
         <v>208</v>
       </c>
@@ -5530,11 +5591,11 @@
       <c r="D205" t="s">
         <v>63</v>
       </c>
-      <c r="E205" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6">
+      <c r="F205" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" hidden="1">
       <c r="A206" s="3">
         <v>209</v>
       </c>
@@ -5545,11 +5606,11 @@
       <c r="D206" t="s">
         <v>63</v>
       </c>
-      <c r="E206" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6">
+      <c r="F206" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" hidden="1">
       <c r="A207" s="3">
         <v>210</v>
       </c>
@@ -5560,11 +5621,11 @@
       <c r="D207" t="s">
         <v>63</v>
       </c>
-      <c r="E207" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6">
+      <c r="F207" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" hidden="1">
       <c r="A208" s="3">
         <v>211</v>
       </c>
@@ -5575,11 +5636,11 @@
       <c r="D208" t="s">
         <v>63</v>
       </c>
-      <c r="E208" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5">
+      <c r="F208" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" hidden="1">
       <c r="A209" s="3">
         <v>212</v>
       </c>
@@ -5590,11 +5651,11 @@
       <c r="D209" t="s">
         <v>63</v>
       </c>
-      <c r="E209" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5">
+      <c r="F209" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" hidden="1">
       <c r="A210" s="3">
         <v>213</v>
       </c>
@@ -5605,11 +5666,11 @@
       <c r="D210" t="s">
         <v>63</v>
       </c>
-      <c r="E210" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5">
+      <c r="F210" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" hidden="1">
       <c r="A211" s="3">
         <v>214</v>
       </c>
@@ -5620,11 +5681,11 @@
       <c r="D211" t="s">
         <v>63</v>
       </c>
-      <c r="E211" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5">
+      <c r="F211" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" hidden="1">
       <c r="A212" s="3">
         <v>215</v>
       </c>
@@ -5635,11 +5696,11 @@
       <c r="D212" t="s">
         <v>63</v>
       </c>
-      <c r="E212" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5">
+      <c r="F212" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" hidden="1">
       <c r="A213" s="3">
         <v>216</v>
       </c>
@@ -5650,11 +5711,11 @@
       <c r="D213" t="s">
         <v>63</v>
       </c>
-      <c r="E213" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5">
+      <c r="F213" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" hidden="1">
       <c r="A214" s="3">
         <v>217</v>
       </c>
@@ -5665,11 +5726,11 @@
       <c r="D214" t="s">
         <v>63</v>
       </c>
-      <c r="E214" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5">
+      <c r="F214" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" hidden="1">
       <c r="A215" s="3">
         <v>218</v>
       </c>
@@ -5680,11 +5741,11 @@
       <c r="D215" t="s">
         <v>63</v>
       </c>
-      <c r="E215" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5">
+      <c r="F215" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" hidden="1">
       <c r="A216" s="3">
         <v>219</v>
       </c>
@@ -5695,11 +5756,11 @@
       <c r="D216" t="s">
         <v>63</v>
       </c>
-      <c r="E216" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5">
+      <c r="F216" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" hidden="1">
       <c r="A217" s="3">
         <v>220</v>
       </c>
@@ -5710,11 +5771,11 @@
       <c r="D217" t="s">
         <v>63</v>
       </c>
-      <c r="E217" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5">
+      <c r="F217" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" hidden="1">
       <c r="A218" s="3">
         <v>221</v>
       </c>
@@ -5725,11 +5786,11 @@
       <c r="D218" t="s">
         <v>63</v>
       </c>
-      <c r="E218" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5">
+      <c r="F218" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" hidden="1">
       <c r="A219" s="3">
         <v>222</v>
       </c>
@@ -5740,11 +5801,11 @@
       <c r="D219" t="s">
         <v>63</v>
       </c>
-      <c r="E219" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5">
+      <c r="F219" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" hidden="1">
       <c r="A220" s="3">
         <v>223</v>
       </c>
@@ -5755,11 +5816,11 @@
       <c r="D220" t="s">
         <v>63</v>
       </c>
-      <c r="E220" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5">
+      <c r="F220" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" hidden="1">
       <c r="A221" s="3">
         <v>224</v>
       </c>
@@ -5770,11 +5831,11 @@
       <c r="D221" t="s">
         <v>63</v>
       </c>
-      <c r="E221" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5">
+      <c r="F221" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" hidden="1">
       <c r="A222" s="3">
         <v>225</v>
       </c>
@@ -5785,11 +5846,11 @@
       <c r="D222" t="s">
         <v>63</v>
       </c>
-      <c r="E222" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5">
+      <c r="F222" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" hidden="1">
       <c r="A223" s="3">
         <v>226</v>
       </c>
@@ -5800,11 +5861,11 @@
       <c r="D223" t="s">
         <v>63</v>
       </c>
-      <c r="E223" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5">
+      <c r="F223" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" hidden="1">
       <c r="A224" s="3">
         <v>227</v>
       </c>
@@ -5815,11 +5876,11 @@
       <c r="D224" t="s">
         <v>63</v>
       </c>
-      <c r="E224" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5">
+      <c r="F224" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" hidden="1">
       <c r="A225" s="3">
         <v>228</v>
       </c>
@@ -5830,11 +5891,11 @@
       <c r="D225" t="s">
         <v>63</v>
       </c>
-      <c r="E225" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5">
+      <c r="F225" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" hidden="1">
       <c r="A226" s="3">
         <v>229</v>
       </c>
@@ -5845,11 +5906,11 @@
       <c r="D226" t="s">
         <v>63</v>
       </c>
-      <c r="E226" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5">
+      <c r="F226" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" hidden="1">
       <c r="A227" s="3">
         <v>230</v>
       </c>
@@ -5860,11 +5921,11 @@
       <c r="D227" t="s">
         <v>63</v>
       </c>
-      <c r="E227" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5">
+      <c r="F227" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" hidden="1">
       <c r="A228" s="3">
         <v>231</v>
       </c>
@@ -5875,11 +5936,11 @@
       <c r="D228" t="s">
         <v>63</v>
       </c>
-      <c r="E228" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5">
+      <c r="F228" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" hidden="1">
       <c r="A229" s="3">
         <v>232</v>
       </c>
@@ -5890,11 +5951,11 @@
       <c r="D229" t="s">
         <v>63</v>
       </c>
-      <c r="E229" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5">
+      <c r="F229" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" hidden="1">
       <c r="A230" s="3">
         <v>233</v>
       </c>
@@ -5905,11 +5966,11 @@
       <c r="D230" t="s">
         <v>63</v>
       </c>
-      <c r="E230" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5">
+      <c r="F230" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" hidden="1">
       <c r="A231" s="3">
         <v>234</v>
       </c>
@@ -5920,11 +5981,11 @@
       <c r="D231" t="s">
         <v>63</v>
       </c>
-      <c r="E231" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5">
+      <c r="F231" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" hidden="1">
       <c r="A232" s="3">
         <v>237</v>
       </c>
@@ -5937,11 +5998,11 @@
       <c r="D232" t="s">
         <v>63</v>
       </c>
-      <c r="E232" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5">
+      <c r="F232" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" hidden="1">
       <c r="A233" s="3">
         <v>238</v>
       </c>
@@ -5951,11 +6012,11 @@
       <c r="D233" t="s">
         <v>63</v>
       </c>
-      <c r="E233" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5">
+      <c r="F233" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" hidden="1">
       <c r="A234" s="3">
         <v>239</v>
       </c>
@@ -5968,11 +6029,11 @@
       <c r="D234" t="s">
         <v>63</v>
       </c>
-      <c r="E234" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5">
+      <c r="F234" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" hidden="1">
       <c r="A235" s="3">
         <v>240</v>
       </c>
@@ -5982,11 +6043,11 @@
       <c r="D235" t="s">
         <v>63</v>
       </c>
-      <c r="E235" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5">
+      <c r="F235" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" hidden="1">
       <c r="A236" s="3">
         <v>241</v>
       </c>
@@ -5997,11 +6058,11 @@
       <c r="D236" t="s">
         <v>63</v>
       </c>
-      <c r="E236" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5">
+      <c r="F236" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" hidden="1">
       <c r="A237" s="3">
         <v>243</v>
       </c>
@@ -6012,11 +6073,11 @@
       <c r="D237" t="s">
         <v>63</v>
       </c>
-      <c r="E237" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5">
+      <c r="F237" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" hidden="1">
       <c r="A238" s="3">
         <v>244</v>
       </c>
@@ -6027,11 +6088,11 @@
       <c r="D238" t="s">
         <v>63</v>
       </c>
-      <c r="E238" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5">
+      <c r="F238" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" hidden="1">
       <c r="A239" s="3">
         <v>245</v>
       </c>
@@ -6044,11 +6105,11 @@
       <c r="D239" t="s">
         <v>63</v>
       </c>
-      <c r="E239" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5">
+      <c r="F239" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" hidden="1">
       <c r="A240" s="3">
         <v>246</v>
       </c>
@@ -6061,11 +6122,11 @@
       <c r="D240" t="s">
         <v>63</v>
       </c>
-      <c r="E240" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5">
+      <c r="F240" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" hidden="1">
       <c r="A241" s="3">
         <v>248</v>
       </c>
@@ -6075,11 +6136,11 @@
       <c r="D241" t="s">
         <v>63</v>
       </c>
-      <c r="E241" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5">
+      <c r="F241" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" hidden="1">
       <c r="A242" s="3">
         <v>249</v>
       </c>
@@ -6089,11 +6150,11 @@
       <c r="D242" t="s">
         <v>63</v>
       </c>
-      <c r="E242" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5">
+      <c r="F242" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" hidden="1">
       <c r="A243" s="3">
         <v>250</v>
       </c>
@@ -6103,11 +6164,11 @@
       <c r="D243" t="s">
         <v>63</v>
       </c>
-      <c r="E243" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5">
+      <c r="F243" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" hidden="1">
       <c r="A244" s="3">
         <v>251</v>
       </c>
@@ -6120,11 +6181,11 @@
       <c r="D244" t="s">
         <v>63</v>
       </c>
-      <c r="E244" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5">
+      <c r="F244" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" hidden="1">
       <c r="A245" s="3">
         <v>252</v>
       </c>
@@ -6137,11 +6198,11 @@
       <c r="D245" t="s">
         <v>63</v>
       </c>
-      <c r="E245" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5">
+      <c r="F245" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" hidden="1">
       <c r="A246" s="3">
         <v>253</v>
       </c>
@@ -6154,11 +6215,11 @@
       <c r="D246" t="s">
         <v>63</v>
       </c>
-      <c r="E246" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5">
+      <c r="F246" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" hidden="1">
       <c r="A247" s="3">
         <v>254</v>
       </c>
@@ -6171,11 +6232,11 @@
       <c r="D247" t="s">
         <v>63</v>
       </c>
-      <c r="E247" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5">
+      <c r="F247" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" hidden="1">
       <c r="A248" s="3">
         <v>255</v>
       </c>
@@ -6188,11 +6249,11 @@
       <c r="D248" t="s">
         <v>63</v>
       </c>
-      <c r="E248" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5">
+      <c r="F248" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" hidden="1">
       <c r="A249" s="3">
         <v>256</v>
       </c>
@@ -6202,11 +6263,11 @@
       <c r="D249" t="s">
         <v>63</v>
       </c>
-      <c r="E249" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5">
+      <c r="F249" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" hidden="1">
       <c r="A250" s="3">
         <v>257</v>
       </c>
@@ -6219,11 +6280,11 @@
       <c r="D250" t="s">
         <v>63</v>
       </c>
-      <c r="E250" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5">
+      <c r="F250" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" hidden="1">
       <c r="A251" s="3">
         <v>258</v>
       </c>
@@ -6236,11 +6297,11 @@
       <c r="D251" t="s">
         <v>63</v>
       </c>
-      <c r="E251" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5">
+      <c r="F251" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" hidden="1">
       <c r="A252" s="3">
         <v>259</v>
       </c>
@@ -6253,11 +6314,11 @@
       <c r="D252" t="s">
         <v>63</v>
       </c>
-      <c r="E252" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5">
+      <c r="F252" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" hidden="1">
       <c r="A253" s="3">
         <v>260</v>
       </c>
@@ -6267,11 +6328,11 @@
       <c r="D253" t="s">
         <v>63</v>
       </c>
-      <c r="E253" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5">
+      <c r="F253" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" hidden="1">
       <c r="A254" s="3">
         <v>261</v>
       </c>
@@ -6282,11 +6343,11 @@
       <c r="D254" t="s">
         <v>63</v>
       </c>
-      <c r="E254" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5">
+      <c r="F254" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" hidden="1">
       <c r="A255" s="3">
         <v>262</v>
       </c>
@@ -6299,11 +6360,11 @@
       <c r="D255" t="s">
         <v>63</v>
       </c>
-      <c r="E255" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5">
+      <c r="F255" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" hidden="1">
       <c r="A256" s="3">
         <v>263</v>
       </c>
@@ -6313,11 +6374,11 @@
       <c r="D256" t="s">
         <v>63</v>
       </c>
-      <c r="E256" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5">
+      <c r="F256" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" hidden="1">
       <c r="A257" s="3">
         <v>264</v>
       </c>
@@ -6328,11 +6389,11 @@
       <c r="D257" t="s">
         <v>63</v>
       </c>
-      <c r="E257" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5">
+      <c r="F257" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" hidden="1">
       <c r="A258" s="3">
         <v>265</v>
       </c>
@@ -6342,11 +6403,11 @@
       <c r="D258" t="s">
         <v>63</v>
       </c>
-      <c r="E258" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5">
+      <c r="F258" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" hidden="1">
       <c r="A259" s="3">
         <v>266</v>
       </c>
@@ -6359,11 +6420,11 @@
       <c r="D259" t="s">
         <v>63</v>
       </c>
-      <c r="E259" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5">
+      <c r="F259" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" hidden="1">
       <c r="A260" s="3">
         <v>267</v>
       </c>
@@ -6376,11 +6437,11 @@
       <c r="D260" t="s">
         <v>63</v>
       </c>
-      <c r="E260" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5">
+      <c r="F260" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" hidden="1">
       <c r="A261" s="3">
         <v>268</v>
       </c>
@@ -6393,11 +6454,11 @@
       <c r="D261" t="s">
         <v>63</v>
       </c>
-      <c r="E261" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5">
+      <c r="F261" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" hidden="1">
       <c r="A262" s="3">
         <v>269</v>
       </c>
@@ -6410,11 +6471,11 @@
       <c r="D262" t="s">
         <v>63</v>
       </c>
-      <c r="E262" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5">
+      <c r="F262" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" hidden="1">
       <c r="A263" s="3">
         <v>270</v>
       </c>
@@ -6427,11 +6488,11 @@
       <c r="D263" t="s">
         <v>63</v>
       </c>
-      <c r="E263" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5">
+      <c r="F263" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" hidden="1">
       <c r="A264" s="3">
         <v>272</v>
       </c>
@@ -6444,11 +6505,11 @@
       <c r="D264" t="s">
         <v>63</v>
       </c>
-      <c r="E264" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5">
+      <c r="F264" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" hidden="1">
       <c r="A265" s="3">
         <v>273</v>
       </c>
@@ -6461,11 +6522,11 @@
       <c r="D265" t="s">
         <v>63</v>
       </c>
-      <c r="E265" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5">
+      <c r="F265" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" hidden="1">
       <c r="A266" s="3">
         <v>274</v>
       </c>
@@ -6478,11 +6539,11 @@
       <c r="D266" t="s">
         <v>63</v>
       </c>
-      <c r="E266" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5">
+      <c r="F266" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" hidden="1">
       <c r="A267" s="3">
         <v>275</v>
       </c>
@@ -6495,11 +6556,11 @@
       <c r="D267" t="s">
         <v>63</v>
       </c>
-      <c r="E267" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5">
+      <c r="F267" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" hidden="1">
       <c r="A268" s="3">
         <v>276</v>
       </c>
@@ -6512,11 +6573,11 @@
       <c r="D268" t="s">
         <v>63</v>
       </c>
-      <c r="E268" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5">
+      <c r="F268" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" hidden="1">
       <c r="A269" s="3">
         <v>277</v>
       </c>
@@ -6529,11 +6590,11 @@
       <c r="D269" t="s">
         <v>63</v>
       </c>
-      <c r="E269" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5">
+      <c r="F269" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" hidden="1">
       <c r="A270" s="3">
         <v>278</v>
       </c>
@@ -6546,11 +6607,11 @@
       <c r="D270" t="s">
         <v>63</v>
       </c>
-      <c r="E270" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5">
+      <c r="F270" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" hidden="1">
       <c r="A271" s="3">
         <v>279</v>
       </c>
@@ -6563,11 +6624,11 @@
       <c r="D271" t="s">
         <v>63</v>
       </c>
-      <c r="E271" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5">
+      <c r="F271" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" hidden="1">
       <c r="A272" s="3">
         <v>280</v>
       </c>
@@ -6577,11 +6638,11 @@
       <c r="D272" t="s">
         <v>63</v>
       </c>
-      <c r="E272" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6">
+      <c r="F272" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" hidden="1">
       <c r="A273" s="3">
         <v>281</v>
       </c>
@@ -6594,11 +6655,11 @@
       <c r="D273" t="s">
         <v>63</v>
       </c>
-      <c r="E273" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6">
+      <c r="F273" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" hidden="1">
       <c r="A274" s="3">
         <v>282</v>
       </c>
@@ -6611,31 +6672,31 @@
       <c r="D274" t="s">
         <v>63</v>
       </c>
-      <c r="E274" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6">
+      <c r="F274" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
       <c r="A275" s="3">
-        <v>283</v>
+        <v>482</v>
       </c>
       <c r="B275" t="s">
-        <v>194</v>
+        <v>381</v>
       </c>
       <c r="C275" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D275">
-        <v>0.375</v>
-      </c>
-      <c r="E275" t="s">
-        <v>464</v>
+        <v>0.75</v>
       </c>
       <c r="F275" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6">
+        <v>479</v>
+      </c>
+      <c r="G275" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" hidden="1">
       <c r="A276" s="3">
         <v>284</v>
       </c>
@@ -6648,11 +6709,11 @@
       <c r="D276" t="s">
         <v>63</v>
       </c>
-      <c r="E276" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6">
+      <c r="F276" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" hidden="1">
       <c r="A277" s="3">
         <v>285</v>
       </c>
@@ -6662,11 +6723,11 @@
       <c r="D277" t="s">
         <v>63</v>
       </c>
-      <c r="E277" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6">
+      <c r="F277" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" hidden="1">
       <c r="A278" s="3">
         <v>286</v>
       </c>
@@ -6676,11 +6737,11 @@
       <c r="D278" t="s">
         <v>63</v>
       </c>
-      <c r="E278" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6">
+      <c r="F278" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" hidden="1">
       <c r="A279" s="3">
         <v>287</v>
       </c>
@@ -6693,11 +6754,11 @@
       <c r="D279" t="s">
         <v>63</v>
       </c>
-      <c r="E279" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6">
+      <c r="F279" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" hidden="1">
       <c r="A280" s="3">
         <v>288</v>
       </c>
@@ -6710,11 +6771,11 @@
       <c r="D280" t="s">
         <v>63</v>
       </c>
-      <c r="E280" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6">
+      <c r="F280" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" hidden="1">
       <c r="A281" s="3">
         <v>289</v>
       </c>
@@ -6725,11 +6786,11 @@
       <c r="D281" t="s">
         <v>63</v>
       </c>
-      <c r="E281" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6">
+      <c r="F281" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" hidden="1">
       <c r="A282" s="3">
         <v>291</v>
       </c>
@@ -6740,51 +6801,51 @@
       <c r="D282" t="s">
         <v>63</v>
       </c>
-      <c r="E282" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6">
+      <c r="F282" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
       <c r="A283" s="3">
-        <v>292</v>
+        <v>455</v>
       </c>
       <c r="B283" t="s">
-        <v>203</v>
+        <v>357</v>
       </c>
       <c r="C283" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D283">
-        <v>0.375</v>
-      </c>
-      <c r="E283" t="s">
-        <v>488</v>
+        <v>0.625</v>
       </c>
       <c r="F283" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6">
+        <v>455</v>
+      </c>
+      <c r="G283" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
       <c r="A284" s="3">
-        <v>293</v>
+        <v>471</v>
       </c>
       <c r="B284" t="s">
-        <v>204</v>
+        <v>373</v>
       </c>
       <c r="C284" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D284">
-        <v>0.375</v>
-      </c>
-      <c r="E284" t="s">
-        <v>488</v>
+        <v>0.625</v>
       </c>
       <c r="F284" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6">
+        <v>478</v>
+      </c>
+      <c r="G284" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" hidden="1">
       <c r="A285" s="3">
         <v>294</v>
       </c>
@@ -6797,11 +6858,11 @@
       <c r="D285" t="s">
         <v>63</v>
       </c>
-      <c r="E285" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6">
+      <c r="F285" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" hidden="1">
       <c r="A286" s="3">
         <v>295</v>
       </c>
@@ -6814,11 +6875,11 @@
       <c r="D286" t="s">
         <v>63</v>
       </c>
-      <c r="E286" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6">
+      <c r="F286" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" hidden="1">
       <c r="A287" s="3">
         <v>296</v>
       </c>
@@ -6828,11 +6889,11 @@
       <c r="D287" t="s">
         <v>63</v>
       </c>
-      <c r="E287" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6">
+      <c r="F287" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" hidden="1">
       <c r="A288" s="3">
         <v>297</v>
       </c>
@@ -6845,11 +6906,11 @@
       <c r="D288" t="s">
         <v>63</v>
       </c>
-      <c r="E288" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6">
+      <c r="F288" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" hidden="1">
       <c r="A289" s="3">
         <v>298</v>
       </c>
@@ -6862,11 +6923,11 @@
       <c r="D289" t="s">
         <v>63</v>
       </c>
-      <c r="E289" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6">
+      <c r="F289" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" hidden="1">
       <c r="A290" s="3">
         <v>299</v>
       </c>
@@ -6879,11 +6940,11 @@
       <c r="D290" t="s">
         <v>63</v>
       </c>
-      <c r="E290" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6">
+      <c r="F290" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" hidden="1">
       <c r="A291" s="3">
         <v>300</v>
       </c>
@@ -6893,11 +6954,11 @@
       <c r="D291" t="s">
         <v>63</v>
       </c>
-      <c r="E291" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6">
+      <c r="F291" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" hidden="1">
       <c r="A292" s="3">
         <v>301</v>
       </c>
@@ -6907,11 +6968,11 @@
       <c r="D292" t="s">
         <v>63</v>
       </c>
-      <c r="E292" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6">
+      <c r="F292" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
       <c r="A293" s="3">
         <v>302</v>
       </c>
@@ -6924,14 +6985,14 @@
       <c r="D293">
         <v>0.375</v>
       </c>
-      <c r="E293" t="s">
-        <v>487</v>
-      </c>
       <c r="F293" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6">
+        <v>486</v>
+      </c>
+      <c r="G293" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" hidden="1">
       <c r="A294" s="3">
         <v>303</v>
       </c>
@@ -6944,11 +7005,11 @@
       <c r="D294" t="s">
         <v>63</v>
       </c>
-      <c r="E294" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6">
+      <c r="F294" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" hidden="1">
       <c r="A295" s="3">
         <v>304</v>
       </c>
@@ -6958,11 +7019,11 @@
       <c r="D295" t="s">
         <v>63</v>
       </c>
-      <c r="E295" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6">
+      <c r="F295" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" hidden="1">
       <c r="A296" s="3">
         <v>305</v>
       </c>
@@ -6975,51 +7036,51 @@
       <c r="D296" t="s">
         <v>63</v>
       </c>
-      <c r="E296" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6">
+      <c r="F296" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
       <c r="A297" s="3">
-        <v>307</v>
+        <v>191</v>
       </c>
       <c r="B297" t="s">
-        <v>219</v>
+        <v>101</v>
       </c>
       <c r="C297" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D297">
         <v>0.375</v>
       </c>
-      <c r="E297" t="s">
-        <v>490</v>
-      </c>
-      <c r="F297" s="5" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6">
+      <c r="F297" t="s">
+        <v>486</v>
+      </c>
+      <c r="G297" s="7" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
       <c r="A298" s="3">
-        <v>308</v>
+        <v>178</v>
       </c>
       <c r="B298" t="s">
-        <v>220</v>
+        <v>88</v>
       </c>
       <c r="C298" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D298">
-        <v>0.25</v>
-      </c>
-      <c r="E298" t="s">
-        <v>487</v>
+        <v>0.375</v>
       </c>
       <c r="F298" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6">
+        <v>486</v>
+      </c>
+      <c r="G298" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" hidden="1">
       <c r="A299" s="3">
         <v>309</v>
       </c>
@@ -7029,11 +7090,11 @@
       <c r="D299" t="s">
         <v>63</v>
       </c>
-      <c r="E299" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6">
+      <c r="F299" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" hidden="1">
       <c r="A300" s="3">
         <v>310</v>
       </c>
@@ -7043,11 +7104,11 @@
       <c r="D300" t="s">
         <v>63</v>
       </c>
-      <c r="E300" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6">
+      <c r="F300" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" hidden="1">
       <c r="A301" s="3">
         <v>311</v>
       </c>
@@ -7057,11 +7118,11 @@
       <c r="D301" t="s">
         <v>63</v>
       </c>
-      <c r="E301" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6">
+      <c r="F301" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" hidden="1">
       <c r="A302" s="3">
         <v>312</v>
       </c>
@@ -7071,11 +7132,11 @@
       <c r="D302" t="s">
         <v>63</v>
       </c>
-      <c r="E302" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6">
+      <c r="F302" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" hidden="1">
       <c r="A303" s="3">
         <v>313</v>
       </c>
@@ -7086,31 +7147,31 @@
       <c r="D303" t="s">
         <v>63</v>
       </c>
-      <c r="E303" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6">
+      <c r="F303" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
       <c r="A304" s="3">
-        <v>314</v>
+        <v>364</v>
       </c>
       <c r="B304" t="s">
-        <v>227</v>
+        <v>271</v>
       </c>
       <c r="C304" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D304">
-        <v>0.375</v>
-      </c>
-      <c r="E304" t="s">
-        <v>488</v>
+        <v>0.625</v>
       </c>
       <c r="F304" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6">
+        <v>465</v>
+      </c>
+      <c r="G304" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" hidden="1">
       <c r="A305" s="3">
         <v>315</v>
       </c>
@@ -7123,11 +7184,11 @@
       <c r="D305" t="s">
         <v>63</v>
       </c>
-      <c r="E305" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6">
+      <c r="F305" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" hidden="1">
       <c r="A306" s="3">
         <v>316</v>
       </c>
@@ -7140,11 +7201,11 @@
       <c r="D306" t="s">
         <v>63</v>
       </c>
-      <c r="E306" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6">
+      <c r="F306" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" hidden="1">
       <c r="A307" s="3">
         <v>317</v>
       </c>
@@ -7157,11 +7218,11 @@
       <c r="D307" t="s">
         <v>63</v>
       </c>
-      <c r="E307" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6">
+      <c r="F307" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" hidden="1">
       <c r="A308" s="3">
         <v>318</v>
       </c>
@@ -7174,11 +7235,11 @@
       <c r="D308" t="s">
         <v>63</v>
       </c>
-      <c r="E308" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="309" spans="1:6">
+      <c r="F308" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" hidden="1">
       <c r="A309" s="3">
         <v>319</v>
       </c>
@@ -7191,11 +7252,11 @@
       <c r="D309" t="s">
         <v>63</v>
       </c>
-      <c r="E309" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="310" spans="1:6">
+      <c r="F309" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" hidden="1">
       <c r="A310" s="3">
         <v>320</v>
       </c>
@@ -7208,11 +7269,11 @@
       <c r="D310" t="s">
         <v>63</v>
       </c>
-      <c r="E310" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="311" spans="1:6">
+      <c r="F310" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" hidden="1">
       <c r="A311" s="3">
         <v>321</v>
       </c>
@@ -7225,11 +7286,11 @@
       <c r="D311" t="s">
         <v>63</v>
       </c>
-      <c r="E311" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="312" spans="1:6">
+      <c r="F311" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" hidden="1">
       <c r="A312" s="3">
         <v>322</v>
       </c>
@@ -7242,11 +7303,11 @@
       <c r="D312" t="s">
         <v>63</v>
       </c>
-      <c r="E312" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="313" spans="1:6">
+      <c r="F312" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" hidden="1">
       <c r="A313" s="3">
         <v>323</v>
       </c>
@@ -7259,11 +7320,11 @@
       <c r="D313" t="s">
         <v>63</v>
       </c>
-      <c r="E313" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6">
+      <c r="F313" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" hidden="1">
       <c r="A314" s="3">
         <v>324</v>
       </c>
@@ -7276,11 +7337,11 @@
       <c r="D314" t="s">
         <v>63</v>
       </c>
-      <c r="E314" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6">
+      <c r="F314" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" hidden="1">
       <c r="A315" s="3">
         <v>325</v>
       </c>
@@ -7293,11 +7354,11 @@
       <c r="D315" t="s">
         <v>63</v>
       </c>
-      <c r="E315" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6">
+      <c r="F315" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" hidden="1">
       <c r="A316" s="3">
         <v>326</v>
       </c>
@@ -7310,11 +7371,11 @@
       <c r="D316" t="s">
         <v>63</v>
       </c>
-      <c r="E316" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="317" spans="1:6">
+      <c r="F316" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" hidden="1">
       <c r="A317" s="3">
         <v>327</v>
       </c>
@@ -7327,16 +7388,16 @@
       <c r="D317" t="s">
         <v>63</v>
       </c>
-      <c r="E317" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="318" spans="1:6">
+      <c r="F317" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7">
       <c r="A318" s="3">
-        <v>328</v>
+        <v>33</v>
       </c>
       <c r="B318" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C318" s="1">
         <v>3</v>
@@ -7344,14 +7405,14 @@
       <c r="D318">
         <v>0.625</v>
       </c>
-      <c r="E318" t="s">
-        <v>465</v>
-      </c>
       <c r="F318" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6">
+        <v>457</v>
+      </c>
+      <c r="G318" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" hidden="1">
       <c r="A319" s="3">
         <v>329</v>
       </c>
@@ -7362,11 +7423,11 @@
       <c r="D319" t="s">
         <v>63</v>
       </c>
-      <c r="E319" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6">
+      <c r="F319" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" hidden="1">
       <c r="A320" s="3">
         <v>331</v>
       </c>
@@ -7376,11 +7437,11 @@
       <c r="D320" t="s">
         <v>63</v>
       </c>
-      <c r="E320" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5">
+      <c r="F320" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" hidden="1">
       <c r="A321" s="3">
         <v>332</v>
       </c>
@@ -7393,11 +7454,11 @@
       <c r="D321" t="s">
         <v>63</v>
       </c>
-      <c r="E321" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5">
+      <c r="F321" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" hidden="1">
       <c r="A322" s="3">
         <v>333</v>
       </c>
@@ -7410,11 +7471,11 @@
       <c r="D322" t="s">
         <v>63</v>
       </c>
-      <c r="E322" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5">
+      <c r="F322" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" hidden="1">
       <c r="A323" s="3">
         <v>334</v>
       </c>
@@ -7424,11 +7485,11 @@
       <c r="D323" t="s">
         <v>63</v>
       </c>
-      <c r="E323" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="324" spans="1:5">
+      <c r="F323" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" hidden="1">
       <c r="A324" s="3">
         <v>336</v>
       </c>
@@ -7438,11 +7499,11 @@
       <c r="D324" t="s">
         <v>63</v>
       </c>
-      <c r="E324" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="325" spans="1:5">
+      <c r="F324" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" hidden="1">
       <c r="A325" s="3">
         <v>338</v>
       </c>
@@ -7455,11 +7516,11 @@
       <c r="D325" t="s">
         <v>63</v>
       </c>
-      <c r="E325" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5">
+      <c r="F325" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" hidden="1">
       <c r="A326" s="3">
         <v>339</v>
       </c>
@@ -7472,11 +7533,11 @@
       <c r="D326" t="s">
         <v>63</v>
       </c>
-      <c r="E326" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="327" spans="1:5">
+      <c r="F326" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" hidden="1">
       <c r="A327" s="3">
         <v>340</v>
       </c>
@@ -7487,11 +7548,11 @@
       <c r="D327" t="s">
         <v>63</v>
       </c>
-      <c r="E327" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5">
+      <c r="F327" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" hidden="1">
       <c r="A328" s="3">
         <v>341</v>
       </c>
@@ -7504,11 +7565,11 @@
       <c r="D328" t="s">
         <v>63</v>
       </c>
-      <c r="E328" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5">
+      <c r="F328" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" hidden="1">
       <c r="A329" s="3">
         <v>342</v>
       </c>
@@ -7521,11 +7582,11 @@
       <c r="D329" t="s">
         <v>63</v>
       </c>
-      <c r="E329" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5">
+      <c r="F329" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" hidden="1">
       <c r="A330" s="3">
         <v>344</v>
       </c>
@@ -7535,11 +7596,11 @@
       <c r="D330" t="s">
         <v>63</v>
       </c>
-      <c r="E330" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5">
+      <c r="F330" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" hidden="1">
       <c r="A331" s="3">
         <v>345</v>
       </c>
@@ -7552,11 +7613,11 @@
       <c r="D331" t="s">
         <v>63</v>
       </c>
-      <c r="E331" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5">
+      <c r="F331" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" hidden="1">
       <c r="A332" s="3">
         <v>347</v>
       </c>
@@ -7569,11 +7630,11 @@
       <c r="D332" t="s">
         <v>63</v>
       </c>
-      <c r="E332" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5">
+      <c r="F332" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" hidden="1">
       <c r="A333" s="3">
         <v>348</v>
       </c>
@@ -7586,11 +7647,11 @@
       <c r="D333" t="s">
         <v>63</v>
       </c>
-      <c r="E333" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="334" spans="1:5">
+      <c r="F333" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" hidden="1">
       <c r="A334" s="3">
         <v>349</v>
       </c>
@@ -7603,11 +7664,11 @@
       <c r="D334" t="s">
         <v>63</v>
       </c>
-      <c r="E334" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="335" spans="1:5">
+      <c r="F334" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" hidden="1">
       <c r="A335" s="3">
         <v>350</v>
       </c>
@@ -7620,11 +7681,11 @@
       <c r="D335" t="s">
         <v>63</v>
       </c>
-      <c r="E335" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="336" spans="1:5">
+      <c r="F335" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" hidden="1">
       <c r="A336" s="3">
         <v>351</v>
       </c>
@@ -7637,11 +7698,11 @@
       <c r="D336" t="s">
         <v>63</v>
       </c>
-      <c r="E336" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="337" spans="1:6">
+      <c r="F336" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" hidden="1">
       <c r="A337" s="3">
         <v>353</v>
       </c>
@@ -7651,11 +7712,11 @@
       <c r="D337" t="s">
         <v>63</v>
       </c>
-      <c r="E337" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="338" spans="1:6">
+      <c r="F337" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" hidden="1">
       <c r="A338" s="3">
         <v>354</v>
       </c>
@@ -7668,11 +7729,11 @@
       <c r="D338" t="s">
         <v>63</v>
       </c>
-      <c r="E338" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="339" spans="1:6">
+      <c r="F338" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" hidden="1">
       <c r="A339" s="3">
         <v>355</v>
       </c>
@@ -7685,11 +7746,11 @@
       <c r="D339" t="s">
         <v>63</v>
       </c>
-      <c r="E339" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="340" spans="1:6">
+      <c r="F339" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" hidden="1">
       <c r="A340" s="3">
         <v>357</v>
       </c>
@@ -7702,11 +7763,11 @@
       <c r="D340" t="s">
         <v>63</v>
       </c>
-      <c r="E340" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="341" spans="1:6">
+      <c r="F340" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" hidden="1">
       <c r="A341" s="3">
         <v>358</v>
       </c>
@@ -7716,11 +7777,11 @@
       <c r="D341" t="s">
         <v>63</v>
       </c>
-      <c r="E341" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="342" spans="1:6">
+      <c r="F341" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" hidden="1">
       <c r="A342" s="3">
         <v>359</v>
       </c>
@@ -7733,51 +7794,54 @@
       <c r="D342" t="s">
         <v>63</v>
       </c>
-      <c r="E342" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="343" spans="1:6">
+      <c r="F342" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7">
       <c r="A343" s="3">
-        <v>360</v>
+        <v>485</v>
       </c>
       <c r="B343" t="s">
-        <v>267</v>
+        <v>382</v>
       </c>
       <c r="C343" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D343">
-        <v>0.375</v>
-      </c>
-      <c r="E343" t="s">
-        <v>488</v>
+        <v>0.625</v>
       </c>
       <c r="F343" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="344" spans="1:6">
+        <v>480</v>
+      </c>
+      <c r="G343" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7">
       <c r="A344" s="3">
-        <v>361</v>
+        <v>493</v>
       </c>
       <c r="B344" t="s">
-        <v>268</v>
+        <v>390</v>
       </c>
       <c r="C344" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D344">
-        <v>0.375</v>
-      </c>
-      <c r="E344" t="s">
-        <v>488</v>
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>0</v>
       </c>
       <c r="F344" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="345" spans="1:6">
+        <v>484</v>
+      </c>
+      <c r="G344" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" hidden="1">
       <c r="A345" s="3">
         <v>362</v>
       </c>
@@ -7790,11 +7854,11 @@
       <c r="D345" t="s">
         <v>63</v>
       </c>
-      <c r="E345" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="346" spans="1:6">
+      <c r="F345" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" hidden="1">
       <c r="A346" s="3">
         <v>363</v>
       </c>
@@ -7804,16 +7868,16 @@
       <c r="D346" t="s">
         <v>63</v>
       </c>
-      <c r="E346" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="347" spans="1:6">
+      <c r="F346" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7">
       <c r="A347" s="3">
-        <v>364</v>
+        <v>328</v>
       </c>
       <c r="B347" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="C347" s="1">
         <v>3</v>
@@ -7821,14 +7885,14 @@
       <c r="D347">
         <v>0.625</v>
       </c>
-      <c r="E347" t="s">
-        <v>466</v>
-      </c>
       <c r="F347" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="348" spans="1:6">
+        <v>464</v>
+      </c>
+      <c r="G347" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" hidden="1">
       <c r="A348" s="3">
         <v>365</v>
       </c>
@@ -7838,11 +7902,11 @@
       <c r="D348" t="s">
         <v>63</v>
       </c>
-      <c r="E348" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="349" spans="1:6">
+      <c r="F348" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" hidden="1">
       <c r="A349" s="3">
         <v>366</v>
       </c>
@@ -7852,31 +7916,31 @@
       <c r="D349" t="s">
         <v>63</v>
       </c>
-      <c r="E349" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="350" spans="1:6">
+      <c r="F349" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7">
       <c r="A350" s="3">
-        <v>367</v>
+        <v>488</v>
       </c>
       <c r="B350" t="s">
-        <v>274</v>
+        <v>385</v>
       </c>
       <c r="C350" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D350">
-        <v>0.375</v>
-      </c>
-      <c r="E350" t="s">
-        <v>466</v>
+        <v>0.625</v>
       </c>
       <c r="F350" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="351" spans="1:6">
+        <v>481</v>
+      </c>
+      <c r="G350" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" hidden="1">
       <c r="A351" s="3">
         <v>368</v>
       </c>
@@ -7889,11 +7953,11 @@
       <c r="D351" t="s">
         <v>63</v>
       </c>
-      <c r="E351" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="352" spans="1:6">
+      <c r="F351" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" hidden="1">
       <c r="A352" s="3">
         <v>369</v>
       </c>
@@ -7906,11 +7970,11 @@
       <c r="D352" t="s">
         <v>63</v>
       </c>
-      <c r="E352" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="353" spans="1:5">
+      <c r="F352" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" hidden="1">
       <c r="A353" s="3">
         <v>371</v>
       </c>
@@ -7923,11 +7987,11 @@
       <c r="D353" t="s">
         <v>63</v>
       </c>
-      <c r="E353" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="354" spans="1:5">
+      <c r="F353" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" hidden="1">
       <c r="A354" s="3">
         <v>372</v>
       </c>
@@ -7940,11 +8004,11 @@
       <c r="D354" t="s">
         <v>63</v>
       </c>
-      <c r="E354" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="355" spans="1:5">
+      <c r="F354" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" hidden="1">
       <c r="A355" s="3">
         <v>373</v>
       </c>
@@ -7957,11 +8021,11 @@
       <c r="D355" t="s">
         <v>63</v>
       </c>
-      <c r="E355" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="356" spans="1:5">
+      <c r="F355" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" hidden="1">
       <c r="A356" s="3">
         <v>375</v>
       </c>
@@ -7974,11 +8038,11 @@
       <c r="D356" t="s">
         <v>63</v>
       </c>
-      <c r="E356" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="357" spans="1:5">
+      <c r="F356" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" hidden="1">
       <c r="A357" s="3">
         <v>376</v>
       </c>
@@ -7991,11 +8055,11 @@
       <c r="D357" t="s">
         <v>63</v>
       </c>
-      <c r="E357" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="358" spans="1:5">
+      <c r="F357" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" hidden="1">
       <c r="A358" s="3">
         <v>377</v>
       </c>
@@ -8008,11 +8072,11 @@
       <c r="D358" t="s">
         <v>63</v>
       </c>
-      <c r="E358" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="359" spans="1:5">
+      <c r="F358" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" hidden="1">
       <c r="A359" s="3">
         <v>378</v>
       </c>
@@ -8022,11 +8086,11 @@
       <c r="D359" t="s">
         <v>63</v>
       </c>
-      <c r="E359" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="360" spans="1:5">
+      <c r="F359" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" hidden="1">
       <c r="A360" s="3">
         <v>379</v>
       </c>
@@ -8037,11 +8101,11 @@
       <c r="D360" t="s">
         <v>63</v>
       </c>
-      <c r="E360" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="361" spans="1:5">
+      <c r="F360" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" hidden="1">
       <c r="A361" s="3">
         <v>380</v>
       </c>
@@ -8054,11 +8118,11 @@
       <c r="D361" t="s">
         <v>63</v>
       </c>
-      <c r="E361" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="362" spans="1:5">
+      <c r="F361" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" hidden="1">
       <c r="A362" s="3">
         <v>381</v>
       </c>
@@ -8071,11 +8135,11 @@
       <c r="D362" t="s">
         <v>63</v>
       </c>
-      <c r="E362" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="363" spans="1:5">
+      <c r="F362" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" hidden="1">
       <c r="A363" s="3">
         <v>382</v>
       </c>
@@ -8088,11 +8152,11 @@
       <c r="D363" t="s">
         <v>63</v>
       </c>
-      <c r="E363" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="364" spans="1:5">
+      <c r="F363" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" hidden="1">
       <c r="A364" s="3">
         <v>383</v>
       </c>
@@ -8105,11 +8169,11 @@
       <c r="D364" t="s">
         <v>63</v>
       </c>
-      <c r="E364" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="365" spans="1:5">
+      <c r="F364" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" hidden="1">
       <c r="A365" s="3">
         <v>384</v>
       </c>
@@ -8122,11 +8186,11 @@
       <c r="D365" t="s">
         <v>63</v>
       </c>
-      <c r="E365" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="366" spans="1:5">
+      <c r="F365" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" hidden="1">
       <c r="A366" s="3">
         <v>386</v>
       </c>
@@ -8139,11 +8203,11 @@
       <c r="D366" t="s">
         <v>63</v>
       </c>
-      <c r="E366" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="367" spans="1:5">
+      <c r="F366" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" hidden="1">
       <c r="A367" s="3">
         <v>387</v>
       </c>
@@ -8156,11 +8220,11 @@
       <c r="D367" t="s">
         <v>63</v>
       </c>
-      <c r="E367" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="368" spans="1:5">
+      <c r="F367" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" hidden="1">
       <c r="A368" s="3">
         <v>388</v>
       </c>
@@ -8173,31 +8237,31 @@
       <c r="D368" t="s">
         <v>63</v>
       </c>
-      <c r="E368" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="369" spans="1:6">
+      <c r="F368" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7">
       <c r="A369" s="3">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="B369" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="C369" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D369">
-        <v>0.375</v>
-      </c>
-      <c r="E369" t="s">
-        <v>488</v>
+        <v>0.625</v>
       </c>
       <c r="F369" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="370" spans="1:6">
+        <v>467</v>
+      </c>
+      <c r="G369" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" hidden="1">
       <c r="A370" s="3">
         <v>391</v>
       </c>
@@ -8207,11 +8271,11 @@
       <c r="D370" t="s">
         <v>63</v>
       </c>
-      <c r="E370" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="371" spans="1:6">
+      <c r="F370" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" hidden="1">
       <c r="A371" s="3">
         <v>392</v>
       </c>
@@ -8221,11 +8285,11 @@
       <c r="D371" t="s">
         <v>63</v>
       </c>
-      <c r="E371" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="372" spans="1:6">
+      <c r="F371" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" hidden="1">
       <c r="A372" s="3">
         <v>393</v>
       </c>
@@ -8235,11 +8299,11 @@
       <c r="D372" t="s">
         <v>63</v>
       </c>
-      <c r="E372" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="373" spans="1:6">
+      <c r="F372" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" hidden="1">
       <c r="A373" s="3">
         <v>394</v>
       </c>
@@ -8252,31 +8316,31 @@
       <c r="D373" t="s">
         <v>63</v>
       </c>
-      <c r="E373" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="374" spans="1:6">
+      <c r="F373" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7">
       <c r="A374" s="3">
-        <v>395</v>
+        <v>205</v>
       </c>
       <c r="B374" t="s">
-        <v>301</v>
+        <v>117</v>
       </c>
       <c r="C374" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D374">
         <v>0.375</v>
       </c>
-      <c r="E374" t="s">
-        <v>488</v>
-      </c>
       <c r="F374" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="375" spans="1:6">
+        <v>462</v>
+      </c>
+      <c r="G374" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" hidden="1">
       <c r="A375" s="3">
         <v>396</v>
       </c>
@@ -8289,31 +8353,31 @@
       <c r="D375" t="s">
         <v>63</v>
       </c>
-      <c r="E375" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="376" spans="1:6">
+      <c r="F375" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7">
       <c r="A376" s="3">
-        <v>397</v>
+        <v>114</v>
       </c>
       <c r="B376" t="s">
-        <v>303</v>
+        <v>19</v>
       </c>
       <c r="C376" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D376">
-        <v>0.375</v>
-      </c>
-      <c r="E376" t="s">
-        <v>467</v>
+        <v>0.625</v>
       </c>
       <c r="F376" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="377" spans="1:6">
+        <v>461</v>
+      </c>
+      <c r="G376" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" hidden="1">
       <c r="A377" s="3">
         <v>398</v>
       </c>
@@ -8323,11 +8387,11 @@
       <c r="D377" t="s">
         <v>63</v>
       </c>
-      <c r="E377" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="378" spans="1:6">
+      <c r="F377" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" hidden="1">
       <c r="A378" s="3">
         <v>399</v>
       </c>
@@ -8340,11 +8404,11 @@
       <c r="D378" t="s">
         <v>63</v>
       </c>
-      <c r="E378" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="379" spans="1:6">
+      <c r="F378" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" hidden="1">
       <c r="A379" s="3">
         <v>400</v>
       </c>
@@ -8357,11 +8421,11 @@
       <c r="D379" t="s">
         <v>63</v>
       </c>
-      <c r="E379" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="380" spans="1:6">
+      <c r="F379" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" hidden="1">
       <c r="A380" s="3">
         <v>401</v>
       </c>
@@ -8374,11 +8438,11 @@
       <c r="D380" t="s">
         <v>63</v>
       </c>
-      <c r="E380" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="381" spans="1:6">
+      <c r="F380" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" hidden="1">
       <c r="A381" s="3">
         <v>402</v>
       </c>
@@ -8391,11 +8455,11 @@
       <c r="D381" t="s">
         <v>63</v>
       </c>
-      <c r="E381" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="382" spans="1:6">
+      <c r="F381" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" hidden="1">
       <c r="A382" s="3">
         <v>403</v>
       </c>
@@ -8408,11 +8472,11 @@
       <c r="D382" t="s">
         <v>63</v>
       </c>
-      <c r="E382" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="383" spans="1:6">
+      <c r="F382" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" hidden="1">
       <c r="A383" s="3">
         <v>404</v>
       </c>
@@ -8425,11 +8489,11 @@
       <c r="D383" t="s">
         <v>63</v>
       </c>
-      <c r="E383" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="384" spans="1:6">
+      <c r="F383" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" hidden="1">
       <c r="A384" s="3">
         <v>405</v>
       </c>
@@ -8442,11 +8506,11 @@
       <c r="D384" t="s">
         <v>63</v>
       </c>
-      <c r="E384" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="385" spans="1:6">
+      <c r="F384" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7" hidden="1">
       <c r="A385" s="3">
         <v>406</v>
       </c>
@@ -8459,11 +8523,11 @@
       <c r="D385" t="s">
         <v>63</v>
       </c>
-      <c r="E385" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="386" spans="1:6">
+      <c r="F385" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7" hidden="1">
       <c r="A386" s="3">
         <v>407</v>
       </c>
@@ -8476,11 +8540,11 @@
       <c r="D386" t="s">
         <v>63</v>
       </c>
-      <c r="E386" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="387" spans="1:6">
+      <c r="F386" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" hidden="1">
       <c r="A387" s="3">
         <v>409</v>
       </c>
@@ -8493,11 +8557,11 @@
       <c r="D387" t="s">
         <v>63</v>
       </c>
-      <c r="E387" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="388" spans="1:6">
+      <c r="F387" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7" hidden="1">
       <c r="A388" s="3">
         <v>410</v>
       </c>
@@ -8510,11 +8574,11 @@
       <c r="D388" t="s">
         <v>63</v>
       </c>
-      <c r="E388" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="389" spans="1:6">
+      <c r="F388" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" hidden="1">
       <c r="A389" s="3">
         <v>411</v>
       </c>
@@ -8527,11 +8591,11 @@
       <c r="D389" t="s">
         <v>63</v>
       </c>
-      <c r="E389" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="390" spans="1:6">
+      <c r="F389" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" hidden="1">
       <c r="A390" s="3">
         <v>412</v>
       </c>
@@ -8544,31 +8608,31 @@
       <c r="D390" t="s">
         <v>63</v>
       </c>
-      <c r="E390" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="391" spans="1:6">
+      <c r="F390" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7">
       <c r="A391" s="3">
-        <v>413</v>
+        <v>21</v>
       </c>
       <c r="B391" t="s">
-        <v>320</v>
+        <v>121</v>
       </c>
       <c r="C391" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D391">
         <v>0.625</v>
       </c>
-      <c r="E391" t="s">
-        <v>468</v>
-      </c>
       <c r="F391" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="392" spans="1:6">
+        <v>456</v>
+      </c>
+      <c r="G391" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7" hidden="1">
       <c r="A392" s="3">
         <v>414</v>
       </c>
@@ -8581,11 +8645,11 @@
       <c r="D392" t="s">
         <v>63</v>
       </c>
-      <c r="E392" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="393" spans="1:6">
+      <c r="F392" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" hidden="1">
       <c r="A393" s="3">
         <v>415</v>
       </c>
@@ -8598,11 +8662,11 @@
       <c r="D393" t="s">
         <v>63</v>
       </c>
-      <c r="E393" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="394" spans="1:6">
+      <c r="F393" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" hidden="1">
       <c r="A394" s="3">
         <v>416</v>
       </c>
@@ -8613,11 +8677,11 @@
       <c r="D394" t="s">
         <v>63</v>
       </c>
-      <c r="E394" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="395" spans="1:6">
+      <c r="F394" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7" hidden="1">
       <c r="A395" s="3">
         <v>417</v>
       </c>
@@ -8628,11 +8692,11 @@
       <c r="D395" t="s">
         <v>63</v>
       </c>
-      <c r="E395" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="396" spans="1:6">
+      <c r="F395" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" hidden="1">
       <c r="A396" s="3">
         <v>418</v>
       </c>
@@ -8642,11 +8706,11 @@
       <c r="D396" t="s">
         <v>63</v>
       </c>
-      <c r="E396" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="397" spans="1:6">
+      <c r="F396" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7" hidden="1">
       <c r="A397" s="3">
         <v>419</v>
       </c>
@@ -8659,91 +8723,94 @@
       <c r="D397" t="s">
         <v>63</v>
       </c>
-      <c r="E397" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="398" spans="1:6">
+      <c r="F397" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7">
       <c r="A398" s="3">
-        <v>420</v>
+        <v>283</v>
       </c>
       <c r="B398" t="s">
-        <v>327</v>
+        <v>194</v>
       </c>
       <c r="C398" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D398">
-        <v>1</v>
-      </c>
-      <c r="E398" t="s">
-        <v>456</v>
+        <v>0</v>
+      </c>
+      <c r="E398">
+        <v>100</v>
       </c>
       <c r="F398" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="399" spans="1:6">
+        <v>463</v>
+      </c>
+      <c r="G398" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7">
       <c r="A399" s="3">
-        <v>421</v>
+        <v>501</v>
       </c>
       <c r="B399" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="C399" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D399">
         <v>0.375</v>
       </c>
-      <c r="E399" t="s">
-        <v>488</v>
-      </c>
       <c r="F399" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="400" spans="1:6">
+        <v>485</v>
+      </c>
+      <c r="G399" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7">
       <c r="A400" s="3">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B400" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C400" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D400">
-        <v>0.375</v>
-      </c>
-      <c r="E400" t="s">
-        <v>488</v>
+        <v>0.625</v>
       </c>
       <c r="F400" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="401" spans="1:6">
+        <v>455</v>
+      </c>
+      <c r="G400" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7">
       <c r="A401" s="3">
-        <v>423</v>
+        <v>67</v>
       </c>
       <c r="B401" t="s">
-        <v>330</v>
+        <v>419</v>
       </c>
       <c r="C401" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D401">
         <v>0.375</v>
       </c>
-      <c r="E401" t="s">
-        <v>507</v>
-      </c>
       <c r="F401" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="402" spans="1:6">
+        <v>459</v>
+      </c>
+      <c r="G401" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" hidden="1">
       <c r="A402" s="3">
         <v>424</v>
       </c>
@@ -8756,11 +8823,11 @@
       <c r="D402" t="s">
         <v>63</v>
       </c>
-      <c r="E402" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="403" spans="1:6">
+      <c r="F402" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" hidden="1">
       <c r="A403" s="3">
         <v>425</v>
       </c>
@@ -8770,11 +8837,11 @@
       <c r="D403" t="s">
         <v>63</v>
       </c>
-      <c r="E403" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="404" spans="1:6">
+      <c r="F403" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" hidden="1">
       <c r="A404" s="3">
         <v>426</v>
       </c>
@@ -8784,11 +8851,11 @@
       <c r="D404" t="s">
         <v>63</v>
       </c>
-      <c r="E404" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="405" spans="1:6">
+      <c r="F404" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" hidden="1">
       <c r="A405" s="3">
         <v>427</v>
       </c>
@@ -8801,71 +8868,71 @@
       <c r="D405" t="s">
         <v>63</v>
       </c>
-      <c r="E405" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="406" spans="1:6">
+      <c r="F405" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7">
       <c r="A406" s="3">
-        <v>428</v>
+        <v>1</v>
       </c>
       <c r="B406" t="s">
-        <v>334</v>
+        <v>2</v>
       </c>
       <c r="C406" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D406">
         <v>1</v>
       </c>
-      <c r="E406" t="s">
-        <v>469</v>
-      </c>
-      <c r="F406" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="407" spans="1:6">
+      <c r="F406" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="G406" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7">
       <c r="A407" s="3">
-        <v>430</v>
+        <v>308</v>
       </c>
       <c r="B407" t="s">
-        <v>336</v>
+        <v>220</v>
       </c>
       <c r="C407" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D407">
-        <v>0.375</v>
-      </c>
-      <c r="E407" t="s">
-        <v>489</v>
-      </c>
-      <c r="F407" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="408" spans="1:6">
+        <v>0.25</v>
+      </c>
+      <c r="F407" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="G407" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7">
       <c r="A408" s="3">
-        <v>431</v>
+        <v>179</v>
       </c>
       <c r="B408" t="s">
-        <v>337</v>
+        <v>89</v>
       </c>
       <c r="C408" s="1">
         <v>7</v>
       </c>
       <c r="D408">
-        <v>0.375</v>
-      </c>
-      <c r="E408" t="s">
-        <v>490</v>
+        <v>0.25</v>
       </c>
       <c r="F408" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="409" spans="1:6">
+        <v>486</v>
+      </c>
+      <c r="G408" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" hidden="1">
       <c r="A409" s="3">
         <v>434</v>
       </c>
@@ -8878,11 +8945,11 @@
       <c r="D409" t="s">
         <v>63</v>
       </c>
-      <c r="E409" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="410" spans="1:6">
+      <c r="F409" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" hidden="1">
       <c r="A410" s="3">
         <v>437</v>
       </c>
@@ -8893,11 +8960,11 @@
       <c r="D410" t="s">
         <v>63</v>
       </c>
-      <c r="E410" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="411" spans="1:6">
+      <c r="F410" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" hidden="1">
       <c r="A411" s="3">
         <v>438</v>
       </c>
@@ -8908,11 +8975,11 @@
       <c r="D411" t="s">
         <v>63</v>
       </c>
-      <c r="E411" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="412" spans="1:6">
+      <c r="F411" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" hidden="1">
       <c r="A412" s="3">
         <v>439</v>
       </c>
@@ -8923,11 +8990,11 @@
       <c r="D412" t="s">
         <v>63</v>
       </c>
-      <c r="E412" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="413" spans="1:6">
+      <c r="F412" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" hidden="1">
       <c r="A413" s="3">
         <v>440</v>
       </c>
@@ -8938,11 +9005,11 @@
       <c r="D413" t="s">
         <v>63</v>
       </c>
-      <c r="E413" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="414" spans="1:6">
+      <c r="F413" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" hidden="1">
       <c r="A414" s="3">
         <v>441</v>
       </c>
@@ -8953,11 +9020,11 @@
       <c r="D414" t="s">
         <v>63</v>
       </c>
-      <c r="E414" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="415" spans="1:6">
+      <c r="F414" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" hidden="1">
       <c r="A415" s="3">
         <v>442</v>
       </c>
@@ -8970,11 +9037,11 @@
       <c r="D415" t="s">
         <v>63</v>
       </c>
-      <c r="E415" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="416" spans="1:6">
+      <c r="F415" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" hidden="1">
       <c r="A416" s="3">
         <v>443</v>
       </c>
@@ -8987,11 +9054,11 @@
       <c r="D416" t="s">
         <v>63</v>
       </c>
-      <c r="E416" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="417" spans="1:6">
+      <c r="F416" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" hidden="1">
       <c r="A417" s="3">
         <v>444</v>
       </c>
@@ -9004,11 +9071,11 @@
       <c r="D417" t="s">
         <v>63</v>
       </c>
-      <c r="E417" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="418" spans="1:6">
+      <c r="F417" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" hidden="1">
       <c r="A418" s="3">
         <v>445</v>
       </c>
@@ -9021,11 +9088,11 @@
       <c r="D418" t="s">
         <v>63</v>
       </c>
-      <c r="E418" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="419" spans="1:6">
+      <c r="F418" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" hidden="1">
       <c r="A419" s="3">
         <v>446</v>
       </c>
@@ -9038,11 +9105,11 @@
       <c r="D419" t="s">
         <v>63</v>
       </c>
-      <c r="E419" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="420" spans="1:6">
+      <c r="F419" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" hidden="1">
       <c r="A420" s="3">
         <v>447</v>
       </c>
@@ -9055,11 +9122,11 @@
       <c r="D420" t="s">
         <v>63</v>
       </c>
-      <c r="E420" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="421" spans="1:6">
+      <c r="F420" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7" hidden="1">
       <c r="A421" s="3">
         <v>448</v>
       </c>
@@ -9069,11 +9136,11 @@
       <c r="D421" t="s">
         <v>63</v>
       </c>
-      <c r="E421" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="422" spans="1:6">
+      <c r="F421" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" hidden="1">
       <c r="A422" s="3">
         <v>450</v>
       </c>
@@ -9083,11 +9150,11 @@
       <c r="D422" t="s">
         <v>63</v>
       </c>
-      <c r="E422" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="423" spans="1:6">
+      <c r="F422" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" hidden="1">
       <c r="A423" s="3">
         <v>451</v>
       </c>
@@ -9097,11 +9164,11 @@
       <c r="D423" t="s">
         <v>63</v>
       </c>
-      <c r="E423" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="424" spans="1:6">
+      <c r="F423" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" hidden="1">
       <c r="A424" s="3">
         <v>452</v>
       </c>
@@ -9111,11 +9178,11 @@
       <c r="D424" t="s">
         <v>63</v>
       </c>
-      <c r="E424" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="425" spans="1:6">
+      <c r="F424" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" hidden="1">
       <c r="A425" s="3">
         <v>453</v>
       </c>
@@ -9128,311 +9195,317 @@
       <c r="D425" t="s">
         <v>63</v>
       </c>
-      <c r="E425" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="426" spans="1:6">
+      <c r="F425" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7">
       <c r="A426" s="3">
-        <v>455</v>
+        <v>188</v>
       </c>
       <c r="B426" t="s">
-        <v>357</v>
+        <v>98</v>
       </c>
       <c r="C426" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D426">
-        <v>0.625</v>
-      </c>
-      <c r="E426" t="s">
-        <v>456</v>
+        <v>0.375</v>
       </c>
       <c r="F426" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="427" spans="1:6">
+        <v>486</v>
+      </c>
+      <c r="G426" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7">
       <c r="A427" s="3">
-        <v>456</v>
+        <v>367</v>
       </c>
       <c r="B427" t="s">
-        <v>358</v>
+        <v>274</v>
       </c>
       <c r="C427" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D427">
-        <v>1</v>
-      </c>
-      <c r="E427" t="s">
-        <v>470</v>
+        <v>0.375</v>
       </c>
       <c r="F427" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="428" spans="1:6">
+        <v>465</v>
+      </c>
+      <c r="G427" s="8" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7">
       <c r="A428" s="3">
+        <v>30</v>
+      </c>
+      <c r="B428" t="s">
+        <v>212</v>
+      </c>
+      <c r="C428" s="1">
+        <v>5</v>
+      </c>
+      <c r="D428">
+        <v>0.375</v>
+      </c>
+      <c r="F428" t="s">
         <v>457</v>
       </c>
-      <c r="B428" t="s">
-        <v>359</v>
-      </c>
-      <c r="C428" s="1">
-        <v>2</v>
-      </c>
-      <c r="D428">
-        <v>1</v>
-      </c>
-      <c r="E428" t="s">
-        <v>471</v>
-      </c>
-      <c r="F428" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="429" spans="1:6">
+      <c r="G428" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7">
       <c r="A429" s="3">
-        <v>458</v>
+        <v>65</v>
       </c>
       <c r="B429" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="C429" s="1">
         <v>2</v>
       </c>
       <c r="D429">
-        <v>1</v>
-      </c>
-      <c r="E429" t="s">
-        <v>472</v>
+        <v>0.75</v>
       </c>
       <c r="F429" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="430" spans="1:6">
+        <v>458</v>
+      </c>
+      <c r="G429" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7">
       <c r="A430" s="3">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>361</v>
+        <v>334</v>
       </c>
       <c r="C430" s="1">
         <v>2</v>
       </c>
       <c r="D430">
-        <v>1</v>
-      </c>
-      <c r="E430" t="s">
-        <v>473</v>
+        <v>0.625</v>
       </c>
       <c r="F430" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="431" spans="1:6">
+        <v>468</v>
+      </c>
+      <c r="G430" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7">
       <c r="A431" s="3">
+        <v>489</v>
+      </c>
+      <c r="B431" t="s">
+        <v>386</v>
+      </c>
+      <c r="C431" s="1">
+        <v>5</v>
+      </c>
+      <c r="D431">
+        <v>0.375</v>
+      </c>
+      <c r="F431" t="s">
+        <v>482</v>
+      </c>
+      <c r="G431" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7">
+      <c r="A432" s="3">
+        <v>200</v>
+      </c>
+      <c r="B432" t="s">
+        <v>112</v>
+      </c>
+      <c r="C432" s="1">
+        <v>8</v>
+      </c>
+      <c r="D432">
+        <v>0</v>
+      </c>
+      <c r="E432">
+        <v>250</v>
+      </c>
+      <c r="F432" t="s">
+        <v>487</v>
+      </c>
+      <c r="G432" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7">
+      <c r="A433" s="3">
+        <v>395</v>
+      </c>
+      <c r="B433" t="s">
+        <v>301</v>
+      </c>
+      <c r="C433" s="1">
+        <v>8</v>
+      </c>
+      <c r="D433">
+        <v>0</v>
+      </c>
+      <c r="E433">
+        <v>100</v>
+      </c>
+      <c r="F433" t="s">
+        <v>487</v>
+      </c>
+      <c r="G433" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7">
+      <c r="A434" s="3">
+        <v>192</v>
+      </c>
+      <c r="B434" t="s">
+        <v>102</v>
+      </c>
+      <c r="C434" s="1">
+        <v>5</v>
+      </c>
+      <c r="D434">
+        <v>0.375</v>
+      </c>
+      <c r="F434" t="s">
+        <v>486</v>
+      </c>
+      <c r="G434" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7">
+      <c r="A435" s="3">
+        <v>193</v>
+      </c>
+      <c r="B435" t="s">
+        <v>103</v>
+      </c>
+      <c r="C435" s="1">
+        <v>5</v>
+      </c>
+      <c r="D435">
+        <v>0.375</v>
+      </c>
+      <c r="F435" t="s">
+        <v>486</v>
+      </c>
+      <c r="G435" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7">
+      <c r="A436" s="3">
+        <v>83</v>
+      </c>
+      <c r="B436" t="s">
+        <v>437</v>
+      </c>
+      <c r="C436" s="1">
+        <v>2</v>
+      </c>
+      <c r="D436">
+        <v>0.75</v>
+      </c>
+      <c r="F436" t="s">
         <v>460</v>
       </c>
-      <c r="B431" t="s">
-        <v>363</v>
-      </c>
-      <c r="C431" s="1">
-        <v>2</v>
-      </c>
-      <c r="D431">
-        <v>1</v>
-      </c>
-      <c r="E431" t="s">
-        <v>474</v>
-      </c>
-      <c r="F431" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="432" spans="1:6">
-      <c r="A432" s="3">
-        <v>461</v>
-      </c>
-      <c r="B432" t="s">
-        <v>364</v>
-      </c>
-      <c r="C432" s="1">
-        <v>2</v>
-      </c>
-      <c r="D432">
-        <v>1</v>
-      </c>
-      <c r="E432" t="s">
-        <v>475</v>
-      </c>
-      <c r="F432" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="433" spans="1:6">
-      <c r="A433" s="3">
-        <v>462</v>
-      </c>
-      <c r="B433" t="s">
-        <v>365</v>
-      </c>
-      <c r="C433" s="1">
-        <v>2</v>
-      </c>
-      <c r="D433">
-        <v>1</v>
-      </c>
-      <c r="E433" t="s">
-        <v>476</v>
-      </c>
-      <c r="F433" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="434" spans="1:6">
-      <c r="A434" s="3">
-        <v>463</v>
-      </c>
-      <c r="B434" t="s">
-        <v>366</v>
-      </c>
-      <c r="C434" s="1">
-        <v>2</v>
-      </c>
-      <c r="D434">
-        <v>1</v>
-      </c>
-      <c r="E434" t="s">
-        <v>477</v>
-      </c>
-      <c r="F434" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="435" spans="1:6">
-      <c r="A435" s="3">
-        <v>464</v>
-      </c>
-      <c r="B435" t="s">
-        <v>367</v>
-      </c>
-      <c r="C435" s="1">
-        <v>2</v>
-      </c>
-      <c r="D435">
-        <v>1</v>
-      </c>
-      <c r="E435" t="s">
-        <v>478</v>
-      </c>
-      <c r="F435" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="436" spans="1:6">
-      <c r="A436" s="3">
-        <v>466</v>
-      </c>
-      <c r="B436" t="s">
-        <v>368</v>
-      </c>
-      <c r="C436" s="1">
-        <v>3</v>
-      </c>
-      <c r="D436">
-        <v>0.625</v>
-      </c>
-      <c r="E436" t="s">
-        <v>459</v>
-      </c>
-      <c r="F436" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="437" spans="1:6">
+      <c r="G436" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7">
       <c r="A437" s="3">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B437" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C437" s="1">
         <v>3</v>
       </c>
       <c r="D437">
-        <v>1</v>
-      </c>
-      <c r="E437" t="s">
-        <v>471</v>
+        <v>0.625</v>
       </c>
       <c r="F437" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="438" spans="1:6">
+        <v>477</v>
+      </c>
+      <c r="G437" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7">
       <c r="A438" s="3">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B438" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C438" s="1">
         <v>3</v>
       </c>
       <c r="D438">
-        <v>1</v>
-      </c>
-      <c r="E438" t="s">
+        <v>0.625</v>
+      </c>
+      <c r="F438" t="s">
         <v>470</v>
       </c>
-      <c r="F438" t="s">
+      <c r="G438" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="439" spans="1:6">
+    <row r="439" spans="1:7">
       <c r="A439" s="3">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B439" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C439" s="1">
         <v>3</v>
       </c>
       <c r="D439">
-        <v>1</v>
-      </c>
-      <c r="E439" t="s">
-        <v>478</v>
+        <v>0.625</v>
       </c>
       <c r="F439" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="440" spans="1:6">
+        <v>469</v>
+      </c>
+      <c r="G439" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7">
       <c r="A440" s="3">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="B440" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C440" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D440">
-        <v>0.375</v>
-      </c>
-      <c r="E440" t="s">
-        <v>479</v>
+        <v>0.75</v>
       </c>
       <c r="F440" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="441" spans="1:6">
+        <v>476</v>
+      </c>
+      <c r="G440" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" hidden="1">
       <c r="A441" s="3">
         <v>472</v>
       </c>
@@ -9445,11 +9518,11 @@
       <c r="D441" t="s">
         <v>63</v>
       </c>
-      <c r="E441" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="442" spans="1:6">
+      <c r="F441" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" hidden="1">
       <c r="A442" s="3">
         <v>475</v>
       </c>
@@ -9462,11 +9535,11 @@
       <c r="D442" t="s">
         <v>63</v>
       </c>
-      <c r="E442" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="443" spans="1:6">
+      <c r="F442" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7" hidden="1">
       <c r="A443" s="3">
         <v>477</v>
       </c>
@@ -9479,11 +9552,11 @@
       <c r="D443" t="s">
         <v>63</v>
       </c>
-      <c r="E443" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="444" spans="1:6">
+      <c r="F443" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7" hidden="1">
       <c r="A444" s="3">
         <v>478</v>
       </c>
@@ -9496,11 +9569,11 @@
       <c r="D444" t="s">
         <v>63</v>
       </c>
-      <c r="E444" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="445" spans="1:6">
+      <c r="F444" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7" hidden="1">
       <c r="A445" s="3">
         <v>480</v>
       </c>
@@ -9513,11 +9586,11 @@
       <c r="D445" t="s">
         <v>63</v>
       </c>
-      <c r="E445" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="446" spans="1:6">
+      <c r="F445" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7" hidden="1">
       <c r="A446" s="3">
         <v>481</v>
       </c>
@@ -9530,31 +9603,31 @@
       <c r="D446" t="s">
         <v>63</v>
       </c>
-      <c r="E446" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="447" spans="1:6">
+      <c r="F446" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7">
       <c r="A447" s="3">
-        <v>482</v>
+        <v>457</v>
       </c>
       <c r="B447" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="C447" s="1">
         <v>2</v>
       </c>
       <c r="D447">
-        <v>0.625</v>
-      </c>
-      <c r="E447" t="s">
-        <v>480</v>
+        <v>0.75</v>
       </c>
       <c r="F447" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="448" spans="1:6">
+        <v>470</v>
+      </c>
+      <c r="G447" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7" hidden="1">
       <c r="A448" s="3">
         <v>484</v>
       </c>
@@ -9567,31 +9640,31 @@
       <c r="D448" t="s">
         <v>63</v>
       </c>
-      <c r="E448" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="449" spans="1:6">
+      <c r="F448" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7">
       <c r="A449" s="3">
-        <v>485</v>
+        <v>462</v>
       </c>
       <c r="B449" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="C449" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D449">
-        <v>0.375</v>
-      </c>
-      <c r="E449" t="s">
-        <v>481</v>
+        <v>0.75</v>
       </c>
       <c r="F449" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="450" spans="1:6">
+        <v>475</v>
+      </c>
+      <c r="G449" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" hidden="1">
       <c r="A450" s="3">
         <v>486</v>
       </c>
@@ -9601,11 +9674,11 @@
       <c r="D450" t="s">
         <v>63</v>
       </c>
-      <c r="E450" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="451" spans="1:6">
+      <c r="F450" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7" hidden="1">
       <c r="A451" s="3">
         <v>487</v>
       </c>
@@ -9618,71 +9691,71 @@
       <c r="D451" t="s">
         <v>63</v>
       </c>
-      <c r="E451" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="452" spans="1:6">
+      <c r="F451" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7">
       <c r="A452" s="3">
-        <v>488</v>
+        <v>459</v>
       </c>
       <c r="B452" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="C452" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D452">
-        <v>0.375</v>
-      </c>
-      <c r="E452" t="s">
-        <v>482</v>
+        <v>0.75</v>
       </c>
       <c r="F452" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="453" spans="1:6">
+        <v>472</v>
+      </c>
+      <c r="G452" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7">
       <c r="A453" s="3">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="B453" t="s">
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="C453" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D453">
-        <v>0.375</v>
-      </c>
-      <c r="E453" t="s">
-        <v>483</v>
+        <v>0.75</v>
       </c>
       <c r="F453" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="454" spans="1:6">
+        <v>469</v>
+      </c>
+      <c r="G453" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7">
       <c r="A454" s="3">
-        <v>490</v>
+        <v>461</v>
       </c>
       <c r="B454" t="s">
-        <v>388</v>
+        <v>364</v>
       </c>
       <c r="C454" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D454">
-        <v>0.625</v>
-      </c>
-      <c r="E454" t="s">
-        <v>484</v>
+        <v>0.75</v>
       </c>
       <c r="F454" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="455" spans="1:6">
+        <v>474</v>
+      </c>
+      <c r="G454" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7" hidden="1">
       <c r="A455" s="3">
         <v>491</v>
       </c>
@@ -9692,31 +9765,31 @@
       <c r="D455" t="s">
         <v>63</v>
       </c>
-      <c r="E455" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="456" spans="1:6">
+      <c r="F455" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7">
       <c r="A456" s="3">
-        <v>493</v>
+        <v>464</v>
       </c>
       <c r="B456" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="C456" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D456">
-        <v>0.375</v>
-      </c>
-      <c r="E456" t="s">
-        <v>485</v>
+        <v>0.75</v>
       </c>
       <c r="F456" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="457" spans="1:6">
+        <v>477</v>
+      </c>
+      <c r="G456" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7" hidden="1">
       <c r="A457" s="3">
         <v>494</v>
       </c>
@@ -9729,11 +9802,11 @@
       <c r="D457" t="s">
         <v>63</v>
       </c>
-      <c r="E457" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="458" spans="1:6">
+      <c r="F457" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" hidden="1">
       <c r="A458" s="3">
         <v>495</v>
       </c>
@@ -9746,11 +9819,11 @@
       <c r="D458" t="s">
         <v>63</v>
       </c>
-      <c r="E458" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="459" spans="1:6">
+      <c r="F458" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" hidden="1">
       <c r="A459" s="3">
         <v>496</v>
       </c>
@@ -9760,11 +9833,11 @@
       <c r="D459" t="s">
         <v>63</v>
       </c>
-      <c r="E459" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="460" spans="1:6">
+      <c r="F459" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" hidden="1">
       <c r="A460" s="3">
         <v>497</v>
       </c>
@@ -9777,51 +9850,51 @@
       <c r="D460" t="s">
         <v>63</v>
       </c>
-      <c r="E460" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="461" spans="1:6">
+      <c r="F460" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7">
       <c r="A461" s="3">
-        <v>498</v>
+        <v>458</v>
       </c>
       <c r="B461" t="s">
-        <v>395</v>
+        <v>360</v>
       </c>
       <c r="C461" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D461">
-        <v>0.375</v>
-      </c>
-      <c r="E461" t="s">
-        <v>488</v>
+        <v>0.75</v>
       </c>
       <c r="F461" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="462" spans="1:6">
+        <v>471</v>
+      </c>
+      <c r="G461" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7">
       <c r="A462" s="3">
-        <v>499</v>
+        <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="C462" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D462">
-        <v>0.375</v>
-      </c>
-      <c r="E462" t="s">
-        <v>488</v>
+        <v>0.75</v>
       </c>
       <c r="F462" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="463" spans="1:6">
+        <v>473</v>
+      </c>
+      <c r="G462" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" hidden="1">
       <c r="A463" s="3">
         <v>500</v>
       </c>
@@ -9831,16 +9904,16 @@
       <c r="D463" t="s">
         <v>63</v>
       </c>
-      <c r="E463" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="464" spans="1:6">
+      <c r="F463" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7">
       <c r="A464" s="3">
-        <v>501</v>
+        <v>466</v>
       </c>
       <c r="B464" t="s">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="C464" s="1">
         <v>3</v>
@@ -9848,14 +9921,14 @@
       <c r="D464">
         <v>0.625</v>
       </c>
-      <c r="E464" t="s">
-        <v>486</v>
-      </c>
       <c r="F464" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="465" spans="1:5">
+        <v>458</v>
+      </c>
+      <c r="G464" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="465" spans="1:6" hidden="1">
       <c r="A465" s="3">
         <v>502</v>
       </c>
@@ -9868,7 +9941,7 @@
       <c r="D465" t="s">
         <v>63</v>
       </c>
-      <c r="E465" t="s">
+      <c r="F465" t="s">
         <v>63</v>
       </c>
     </row>

--- a/data/entrada/nóminas/cargos.xlsx
+++ b/data/entrada/nóminas/cargos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amarzal/_Activo/eco/CoAna/data/entrada/nóminas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BB8514-DA1E-7247-8802-2C98BC2613A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD26005-9DE8-6543-857A-B75457E6C7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="524">
   <si>
     <t>cargo</t>
   </si>
@@ -1602,6 +1602,9 @@
   </si>
   <si>
     <t>dedicación_horaria</t>
+  </si>
+  <si>
+    <t>facultades-escuelas</t>
   </si>
 </sst>
 </file>
@@ -1678,17 +1681,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1737,16 +1738,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9D2F6B4F-52C3-6B46-B201-F77B94AF0593}" name="Table1" displayName="Table1" ref="A1:G465" totalsRowShown="0">
-  <autoFilter ref="A1:G465" xr:uid="{9D2F6B4F-52C3-6B46-B201-F77B94AF0593}">
-    <filterColumn colId="3">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G464">
-    <sortCondition ref="B1:B465"/>
-  </sortState>
+  <autoFilter ref="A1:G465" xr:uid="{9D2F6B4F-52C3-6B46-B201-F77B94AF0593}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{3203C3A6-50D8-DD4C-80B4-06BC4BEB47B2}" name="cargo" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{33160495-9720-6A40-B7C2-1BBB379EE15A}" name="nombre"/>
@@ -2111,25 +2103,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3">
-        <v>490</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>388</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>483</v>
+        <v>455</v>
       </c>
       <c r="G2" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" hidden="1">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2146,7 +2138,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1">
+    <row r="4" spans="1:7">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2163,7 +2155,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1">
+    <row r="5" spans="1:7">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2180,7 +2172,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1">
+    <row r="6" spans="1:7">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2197,7 +2189,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1">
+    <row r="7" spans="1:7">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2214,7 +2206,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1">
+    <row r="8" spans="1:7">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2231,7 +2223,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1">
+    <row r="9" spans="1:7">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2248,7 +2240,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1">
+    <row r="10" spans="1:7">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2266,7 +2258,7 @@
       </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" hidden="1">
+    <row r="11" spans="1:7">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2283,7 +2275,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1">
+    <row r="12" spans="1:7">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -2300,7 +2292,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1">
+    <row r="13" spans="1:7">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2317,7 +2309,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1">
+    <row r="14" spans="1:7">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -2334,7 +2326,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1">
+    <row r="15" spans="1:7">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -2351,7 +2343,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1">
+    <row r="16" spans="1:7">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -2368,7 +2360,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1">
+    <row r="17" spans="1:7">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -2385,7 +2377,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1">
+    <row r="18" spans="1:7">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -2404,10 +2396,10 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="3">
-        <v>421</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>328</v>
+        <v>90</v>
       </c>
       <c r="C19" s="1">
         <v>7</v>
@@ -2416,16 +2408,16 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="F19" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="G19" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1">
+    <row r="20" spans="1:7">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -2442,7 +2434,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1">
+    <row r="21" spans="1:7">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -2459,28 +2451,25 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="C22" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>250</v>
+        <v>0.625</v>
       </c>
       <c r="F22" t="s">
-        <v>495</v>
+        <v>456</v>
       </c>
       <c r="G22" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" hidden="1">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -2495,7 +2484,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1">
+    <row r="24" spans="1:7">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -2512,7 +2501,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1">
+    <row r="25" spans="1:7">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -2529,7 +2518,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1">
+    <row r="26" spans="1:7">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -2546,7 +2535,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1">
+    <row r="27" spans="1:7">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -2563,7 +2552,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1">
+    <row r="28" spans="1:7">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -2580,7 +2569,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1">
+    <row r="29" spans="1:7">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -2597,7 +2586,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1">
+    <row r="30" spans="1:7">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -2616,28 +2605,25 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="3">
-        <v>198</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>212</v>
       </c>
       <c r="C31" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>250</v>
+        <v>0.375</v>
       </c>
       <c r="F31" t="s">
-        <v>487</v>
+        <v>457</v>
       </c>
       <c r="G31" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" hidden="1">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -2654,7 +2640,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1">
+    <row r="33" spans="1:7">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -2673,28 +2659,25 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="3">
-        <v>360</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="C34" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34">
-        <v>250</v>
+        <v>0.625</v>
       </c>
       <c r="F34" t="s">
-        <v>487</v>
+        <v>457</v>
       </c>
       <c r="G34" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" hidden="1">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -2711,7 +2694,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1">
+    <row r="36" spans="1:7">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -2728,7 +2711,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1">
+    <row r="37" spans="1:7">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -2745,7 +2728,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1">
+    <row r="38" spans="1:7">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -2762,7 +2745,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1">
+    <row r="39" spans="1:7">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -2779,7 +2762,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1">
+    <row r="40" spans="1:7">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -2796,7 +2779,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -2813,7 +2796,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1">
+    <row r="42" spans="1:7">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -2830,7 +2813,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1">
+    <row r="43" spans="1:7">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -2847,7 +2830,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1">
+    <row r="44" spans="1:7">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -2864,7 +2847,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1">
+    <row r="45" spans="1:7">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -2881,7 +2864,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1">
+    <row r="46" spans="1:7">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -2898,7 +2881,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1">
+    <row r="47" spans="1:7">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -2915,7 +2898,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1">
+    <row r="48" spans="1:7">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -2932,7 +2915,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1">
+    <row r="49" spans="1:6">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -2949,7 +2932,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1">
+    <row r="50" spans="1:6">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -2966,7 +2949,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1">
+    <row r="51" spans="1:6">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -2983,7 +2966,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1">
+    <row r="52" spans="1:6">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -3000,7 +2983,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1">
+    <row r="53" spans="1:6">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -3017,7 +3000,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1">
+    <row r="54" spans="1:6">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -3034,7 +3017,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1">
+    <row r="55" spans="1:6">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -3051,7 +3034,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1">
+    <row r="56" spans="1:6">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -3068,7 +3051,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1">
+    <row r="57" spans="1:6">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -3085,7 +3068,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1">
+    <row r="58" spans="1:6">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -3102,7 +3085,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1">
+    <row r="59" spans="1:6">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -3119,7 +3102,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1">
+    <row r="60" spans="1:6">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -3136,7 +3119,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1">
+    <row r="61" spans="1:6">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -3153,7 +3136,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1">
+    <row r="62" spans="1:6">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -3170,7 +3153,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1">
+    <row r="63" spans="1:6">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -3187,7 +3170,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1">
+    <row r="64" spans="1:6">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -3204,7 +3187,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1">
+    <row r="65" spans="1:7">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -3223,28 +3206,25 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="3">
-        <v>361</v>
+        <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>268</v>
+        <v>417</v>
       </c>
       <c r="C66" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D66">
-        <v>0</v>
-      </c>
-      <c r="E66">
-        <v>250</v>
+        <v>0.75</v>
       </c>
       <c r="F66" t="s">
-        <v>487</v>
+        <v>458</v>
       </c>
       <c r="G66" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -3263,25 +3243,25 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="3">
-        <v>397</v>
+        <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>303</v>
+        <v>419</v>
       </c>
       <c r="C68" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D68">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="F68" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="G68" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" hidden="1">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -3298,7 +3278,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1">
+    <row r="70" spans="1:7">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -3315,7 +3295,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1">
+    <row r="71" spans="1:7">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -3332,7 +3312,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1">
+    <row r="72" spans="1:7">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -3349,7 +3329,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1">
+    <row r="73" spans="1:7">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -3366,7 +3346,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1">
+    <row r="74" spans="1:7">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -3383,7 +3363,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1">
+    <row r="75" spans="1:7">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -3400,7 +3380,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1">
+    <row r="76" spans="1:7">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -3417,7 +3397,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1">
+    <row r="77" spans="1:7">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -3434,7 +3414,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1">
+    <row r="78" spans="1:7">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -3451,7 +3431,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1">
+    <row r="79" spans="1:7">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -3468,7 +3448,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1">
+    <row r="80" spans="1:7">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -3485,7 +3465,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1">
+    <row r="81" spans="1:7">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -3502,7 +3482,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1">
+    <row r="82" spans="1:7">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -3519,7 +3499,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1">
+    <row r="83" spans="1:7">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -3538,28 +3518,25 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="3">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>219</v>
+        <v>437</v>
       </c>
       <c r="C84" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D84">
-        <v>0</v>
-      </c>
-      <c r="E84">
-        <v>250</v>
+        <v>0.75</v>
       </c>
       <c r="F84" t="s">
-        <v>489</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" hidden="1">
+        <v>460</v>
+      </c>
+      <c r="G84" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -3576,7 +3553,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1">
+    <row r="86" spans="1:7">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -3593,7 +3570,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1">
+    <row r="87" spans="1:7">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -3610,7 +3587,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1">
+    <row r="88" spans="1:7">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -3627,7 +3604,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1">
+    <row r="89" spans="1:7">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -3644,7 +3621,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1">
+    <row r="90" spans="1:7">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -3661,7 +3638,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1">
+    <row r="91" spans="1:7">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -3678,7 +3655,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1">
+    <row r="92" spans="1:7">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -3695,7 +3672,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1">
+    <row r="93" spans="1:7">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -3712,7 +3689,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1">
+    <row r="94" spans="1:7">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -3729,7 +3706,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1">
+    <row r="95" spans="1:7">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -3746,7 +3723,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1">
+    <row r="96" spans="1:7">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -3763,7 +3740,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="97" spans="1:6" hidden="1">
+    <row r="97" spans="1:6">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -3780,7 +3757,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="98" spans="1:6" hidden="1">
+    <row r="98" spans="1:6">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -3797,7 +3774,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="99" spans="1:6" hidden="1">
+    <row r="99" spans="1:6">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -3814,7 +3791,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="100" spans="1:6" hidden="1">
+    <row r="100" spans="1:6">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -3831,7 +3808,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="101" spans="1:6" hidden="1">
+    <row r="101" spans="1:6">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -3848,7 +3825,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:6" hidden="1">
+    <row r="102" spans="1:6">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -3865,7 +3842,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="103" spans="1:6" hidden="1">
+    <row r="103" spans="1:6">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -3882,7 +3859,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="104" spans="1:6" hidden="1">
+    <row r="104" spans="1:6">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -3899,7 +3876,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="105" spans="1:6" hidden="1">
+    <row r="105" spans="1:6">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -3916,7 +3893,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="106" spans="1:6" hidden="1">
+    <row r="106" spans="1:6">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -3933,7 +3910,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="107" spans="1:6" hidden="1">
+    <row r="107" spans="1:6">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -3950,7 +3927,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="108" spans="1:6" hidden="1">
+    <row r="108" spans="1:6">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -3967,7 +3944,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="109" spans="1:6" hidden="1">
+    <row r="109" spans="1:6">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -3984,7 +3961,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="110" spans="1:6" hidden="1">
+    <row r="110" spans="1:6">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -4001,7 +3978,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="111" spans="1:6" hidden="1">
+    <row r="111" spans="1:6">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -4018,7 +3995,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="112" spans="1:6" hidden="1">
+    <row r="112" spans="1:6">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -4035,7 +4012,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1">
+    <row r="113" spans="1:7">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -4052,7 +4029,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1">
+    <row r="114" spans="1:7">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -4071,28 +4048,25 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="3">
-        <v>292</v>
+        <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>203</v>
+        <v>19</v>
       </c>
       <c r="C115" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D115">
-        <v>0</v>
-      </c>
-      <c r="E115">
-        <v>400</v>
+        <v>0.625</v>
       </c>
       <c r="F115" t="s">
-        <v>487</v>
+        <v>461</v>
       </c>
       <c r="G115" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -4107,7 +4081,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1">
+    <row r="117" spans="1:7">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -4122,7 +4096,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1">
+    <row r="118" spans="1:7">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -4139,7 +4113,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1">
+    <row r="119" spans="1:7">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -4156,7 +4130,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1">
+    <row r="120" spans="1:7">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -4171,7 +4145,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1">
+    <row r="121" spans="1:7">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -4188,7 +4162,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1">
+    <row r="122" spans="1:7">
       <c r="A122" s="3">
         <v>121</v>
       </c>
@@ -4205,7 +4179,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1">
+    <row r="123" spans="1:7">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -4222,7 +4196,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1">
+    <row r="124" spans="1:7">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -4239,7 +4213,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1">
+    <row r="125" spans="1:7">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -4256,7 +4230,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1">
+    <row r="126" spans="1:7">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -4273,7 +4247,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1">
+    <row r="127" spans="1:7">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -4290,7 +4264,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1">
+    <row r="128" spans="1:7">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -4307,7 +4281,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="129" spans="1:6" hidden="1">
+    <row r="129" spans="1:6">
       <c r="A129" s="3">
         <v>128</v>
       </c>
@@ -4324,7 +4298,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="130" spans="1:6" hidden="1">
+    <row r="130" spans="1:6">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -4341,7 +4315,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="131" spans="1:6" hidden="1">
+    <row r="131" spans="1:6">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -4358,7 +4332,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="132" spans="1:6" hidden="1">
+    <row r="132" spans="1:6">
       <c r="A132" s="3">
         <v>131</v>
       </c>
@@ -4373,7 +4347,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="133" spans="1:6" hidden="1">
+    <row r="133" spans="1:6">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -4390,7 +4364,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="134" spans="1:6" hidden="1">
+    <row r="134" spans="1:6">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -4407,7 +4381,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="135" spans="1:6" hidden="1">
+    <row r="135" spans="1:6">
       <c r="A135" s="3">
         <v>134</v>
       </c>
@@ -4424,7 +4398,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="136" spans="1:6" hidden="1">
+    <row r="136" spans="1:6">
       <c r="A136" s="3">
         <v>135</v>
       </c>
@@ -4441,7 +4415,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="137" spans="1:6" hidden="1">
+    <row r="137" spans="1:6">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -4456,7 +4430,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="138" spans="1:6" hidden="1">
+    <row r="138" spans="1:6">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -4471,7 +4445,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="139" spans="1:6" hidden="1">
+    <row r="139" spans="1:6">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -4488,7 +4462,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="140" spans="1:6" hidden="1">
+    <row r="140" spans="1:6">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -4505,7 +4479,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="141" spans="1:6" hidden="1">
+    <row r="141" spans="1:6">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -4522,7 +4496,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="142" spans="1:6" hidden="1">
+    <row r="142" spans="1:6">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -4539,7 +4513,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="143" spans="1:6" hidden="1">
+    <row r="143" spans="1:6">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -4556,7 +4530,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="144" spans="1:6" hidden="1">
+    <row r="144" spans="1:6">
       <c r="A144" s="3">
         <v>143</v>
       </c>
@@ -4573,7 +4547,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="145" spans="1:6" hidden="1">
+    <row r="145" spans="1:6">
       <c r="A145" s="3">
         <v>144</v>
       </c>
@@ -4590,7 +4564,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="146" spans="1:6" hidden="1">
+    <row r="146" spans="1:6">
       <c r="A146" s="3">
         <v>145</v>
       </c>
@@ -4607,7 +4581,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="147" spans="1:6" hidden="1">
+    <row r="147" spans="1:6">
       <c r="A147" s="3">
         <v>146</v>
       </c>
@@ -4624,7 +4598,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="148" spans="1:6" hidden="1">
+    <row r="148" spans="1:6">
       <c r="A148" s="3">
         <v>147</v>
       </c>
@@ -4641,7 +4615,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="149" spans="1:6" hidden="1">
+    <row r="149" spans="1:6">
       <c r="A149" s="3">
         <v>148</v>
       </c>
@@ -4658,7 +4632,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="150" spans="1:6" hidden="1">
+    <row r="150" spans="1:6">
       <c r="A150" s="3">
         <v>149</v>
       </c>
@@ -4675,7 +4649,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="151" spans="1:6" hidden="1">
+    <row r="151" spans="1:6">
       <c r="A151" s="3">
         <v>150</v>
       </c>
@@ -4692,7 +4666,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="152" spans="1:6" hidden="1">
+    <row r="152" spans="1:6">
       <c r="A152" s="3">
         <v>151</v>
       </c>
@@ -4709,7 +4683,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="153" spans="1:6" hidden="1">
+    <row r="153" spans="1:6">
       <c r="A153" s="3">
         <v>152</v>
       </c>
@@ -4726,7 +4700,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="154" spans="1:6" hidden="1">
+    <row r="154" spans="1:6">
       <c r="A154" s="3">
         <v>153</v>
       </c>
@@ -4743,7 +4717,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="155" spans="1:6" hidden="1">
+    <row r="155" spans="1:6">
       <c r="A155" s="3">
         <v>154</v>
       </c>
@@ -4757,7 +4731,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="156" spans="1:6" hidden="1">
+    <row r="156" spans="1:6">
       <c r="A156" s="3">
         <v>155</v>
       </c>
@@ -4771,7 +4745,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="157" spans="1:6" hidden="1">
+    <row r="157" spans="1:6">
       <c r="A157" s="3">
         <v>156</v>
       </c>
@@ -4785,7 +4759,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="158" spans="1:6" hidden="1">
+    <row r="158" spans="1:6">
       <c r="A158" s="3">
         <v>157</v>
       </c>
@@ -4799,7 +4773,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="159" spans="1:6" hidden="1">
+    <row r="159" spans="1:6">
       <c r="A159" s="3">
         <v>158</v>
       </c>
@@ -4813,7 +4787,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="160" spans="1:6" hidden="1">
+    <row r="160" spans="1:6">
       <c r="A160" s="3">
         <v>159</v>
       </c>
@@ -4827,7 +4801,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="161" spans="1:6" hidden="1">
+    <row r="161" spans="1:6">
       <c r="A161" s="3">
         <v>160</v>
       </c>
@@ -4841,7 +4815,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="162" spans="1:6" hidden="1">
+    <row r="162" spans="1:6">
       <c r="A162" s="3">
         <v>161</v>
       </c>
@@ -4855,7 +4829,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="163" spans="1:6" hidden="1">
+    <row r="163" spans="1:6">
       <c r="A163" s="3">
         <v>162</v>
       </c>
@@ -4872,7 +4846,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="164" spans="1:6" hidden="1">
+    <row r="164" spans="1:6">
       <c r="A164" s="3">
         <v>163</v>
       </c>
@@ -4889,7 +4863,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="165" spans="1:6" hidden="1">
+    <row r="165" spans="1:6">
       <c r="A165" s="3">
         <v>164</v>
       </c>
@@ -4904,7 +4878,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="166" spans="1:6" hidden="1">
+    <row r="166" spans="1:6">
       <c r="A166" s="3">
         <v>165</v>
       </c>
@@ -4921,7 +4895,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="167" spans="1:6" hidden="1">
+    <row r="167" spans="1:6">
       <c r="A167" s="3">
         <v>166</v>
       </c>
@@ -4936,7 +4910,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="168" spans="1:6" hidden="1">
+    <row r="168" spans="1:6">
       <c r="A168" s="3">
         <v>167</v>
       </c>
@@ -4951,7 +4925,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="169" spans="1:6" hidden="1">
+    <row r="169" spans="1:6">
       <c r="A169" s="3">
         <v>168</v>
       </c>
@@ -4966,7 +4940,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="170" spans="1:6" hidden="1">
+    <row r="170" spans="1:6">
       <c r="A170" s="3">
         <v>169</v>
       </c>
@@ -4980,7 +4954,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="171" spans="1:6" hidden="1">
+    <row r="171" spans="1:6">
       <c r="A171" s="3">
         <v>170</v>
       </c>
@@ -4995,7 +4969,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="172" spans="1:6" hidden="1">
+    <row r="172" spans="1:6">
       <c r="A172" s="3">
         <v>171</v>
       </c>
@@ -5010,7 +4984,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="173" spans="1:6" hidden="1">
+    <row r="173" spans="1:6">
       <c r="A173" s="3">
         <v>172</v>
       </c>
@@ -5025,7 +4999,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="174" spans="1:6" hidden="1">
+    <row r="174" spans="1:6">
       <c r="A174" s="3">
         <v>173</v>
       </c>
@@ -5040,7 +5014,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="175" spans="1:6" hidden="1">
+    <row r="175" spans="1:6">
       <c r="A175" s="3">
         <v>174</v>
       </c>
@@ -5055,7 +5029,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="176" spans="1:6" hidden="1">
+    <row r="176" spans="1:6">
       <c r="A176" s="3">
         <v>176</v>
       </c>
@@ -5070,7 +5044,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="177" spans="1:7" hidden="1">
+    <row r="177" spans="1:7">
       <c r="A177" s="3">
         <v>177</v>
       </c>
@@ -5087,51 +5061,45 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="3">
-        <v>293</v>
+        <v>178</v>
       </c>
       <c r="B178" t="s">
-        <v>204</v>
+        <v>88</v>
       </c>
       <c r="C178" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D178">
-        <v>0</v>
-      </c>
-      <c r="E178">
-        <v>400</v>
+        <v>0.375</v>
       </c>
       <c r="F178" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G178" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="3">
-        <v>431</v>
+        <v>179</v>
       </c>
       <c r="B179" t="s">
-        <v>337</v>
+        <v>89</v>
       </c>
       <c r="C179" s="1">
         <v>7</v>
       </c>
       <c r="D179">
-        <v>0</v>
-      </c>
-      <c r="E179">
-        <v>250</v>
+        <v>0.25</v>
       </c>
       <c r="F179" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="G179" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" hidden="1">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
       <c r="A180" s="3">
         <v>180</v>
       </c>
@@ -5146,7 +5114,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="181" spans="1:7" hidden="1">
+    <row r="181" spans="1:7">
       <c r="A181" s="3">
         <v>182</v>
       </c>
@@ -5161,7 +5129,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="182" spans="1:7" hidden="1">
+    <row r="182" spans="1:7">
       <c r="A182" s="3">
         <v>183</v>
       </c>
@@ -5176,7 +5144,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="183" spans="1:7" hidden="1">
+    <row r="183" spans="1:7">
       <c r="A183" s="3">
         <v>184</v>
       </c>
@@ -5191,7 +5159,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="184" spans="1:7" hidden="1">
+    <row r="184" spans="1:7">
       <c r="A184" s="3">
         <v>185</v>
       </c>
@@ -5206,7 +5174,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="185" spans="1:7" hidden="1">
+    <row r="185" spans="1:7">
       <c r="A185" s="3">
         <v>186</v>
       </c>
@@ -5221,7 +5189,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="186" spans="1:7" hidden="1">
+    <row r="186" spans="1:7">
       <c r="A186" s="3">
         <v>187</v>
       </c>
@@ -5238,120 +5206,105 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="3">
-        <v>389</v>
+        <v>188</v>
       </c>
       <c r="B187" t="s">
-        <v>295</v>
+        <v>98</v>
       </c>
       <c r="C187" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D187">
-        <v>0</v>
-      </c>
-      <c r="E187">
-        <v>250</v>
+        <v>0.375</v>
       </c>
       <c r="F187" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G187" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="3">
-        <v>314</v>
+        <v>189</v>
       </c>
       <c r="B188" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="C188" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D188">
-        <v>0</v>
-      </c>
-      <c r="E188">
-        <v>150</v>
+        <v>0.625</v>
       </c>
       <c r="F188" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G188" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="3">
-        <v>430</v>
+        <v>191</v>
       </c>
       <c r="B189" t="s">
-        <v>336</v>
+        <v>101</v>
       </c>
       <c r="C189" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D189">
-        <v>0</v>
-      </c>
-      <c r="E189">
-        <v>100</v>
+        <v>0.375</v>
       </c>
       <c r="F189" t="s">
-        <v>488</v>
-      </c>
-      <c r="G189" t="s">
-        <v>508</v>
+        <v>486</v>
+      </c>
+      <c r="G189" s="6" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="3">
+        <v>192</v>
+      </c>
+      <c r="B190" t="s">
+        <v>102</v>
+      </c>
+      <c r="C190" s="1">
+        <v>5</v>
+      </c>
+      <c r="D190">
+        <v>0.375</v>
+      </c>
+      <c r="F190" t="s">
+        <v>486</v>
+      </c>
+      <c r="G190" t="s">
         <v>499</v>
-      </c>
-      <c r="B190" t="s">
-        <v>396</v>
-      </c>
-      <c r="C190" s="1">
-        <v>8</v>
-      </c>
-      <c r="D190">
-        <v>0</v>
-      </c>
-      <c r="E190">
-        <v>100</v>
-      </c>
-      <c r="F190" t="s">
-        <v>487</v>
-      </c>
-      <c r="G190" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="3">
-        <v>498</v>
+        <v>193</v>
       </c>
       <c r="B191" t="s">
-        <v>395</v>
+        <v>103</v>
       </c>
       <c r="C191" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D191">
-        <v>0</v>
-      </c>
-      <c r="E191">
-        <v>100</v>
+        <v>0.375</v>
       </c>
       <c r="F191" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G191" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" hidden="1">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
       <c r="A192" s="3">
         <v>194</v>
       </c>
@@ -5368,7 +5321,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="193" spans="1:7" hidden="1">
+    <row r="193" spans="1:7">
       <c r="A193" s="3">
         <v>195</v>
       </c>
@@ -5385,7 +5338,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="194" spans="1:7" hidden="1">
+    <row r="194" spans="1:7">
       <c r="A194" s="3">
         <v>196</v>
       </c>
@@ -5400,7 +5353,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="195" spans="1:7" hidden="1">
+    <row r="195" spans="1:7">
       <c r="A195" s="3">
         <v>197</v>
       </c>
@@ -5419,10 +5372,10 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="3">
-        <v>422</v>
+        <v>198</v>
       </c>
       <c r="B196" t="s">
-        <v>329</v>
+        <v>108</v>
       </c>
       <c r="C196" s="1">
         <v>7</v>
@@ -5431,7 +5384,7 @@
         <v>0</v>
       </c>
       <c r="E196">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F196" t="s">
         <v>487</v>
@@ -5440,7 +5393,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="197" spans="1:7" hidden="1">
+    <row r="197" spans="1:7">
       <c r="A197" s="3">
         <v>199</v>
       </c>
@@ -5459,28 +5412,28 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="3">
-        <v>423</v>
+        <v>200</v>
       </c>
       <c r="B198" t="s">
-        <v>330</v>
+        <v>112</v>
       </c>
       <c r="C198" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D198">
         <v>0</v>
       </c>
       <c r="E198">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="F198" t="s">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="G198" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
       <c r="A199" s="3">
         <v>201</v>
       </c>
@@ -5494,7 +5447,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="200" spans="1:7" hidden="1">
+    <row r="200" spans="1:7">
       <c r="A200" s="3">
         <v>202</v>
       </c>
@@ -5511,7 +5464,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="201" spans="1:7" hidden="1">
+    <row r="201" spans="1:7">
       <c r="A201" s="3">
         <v>203</v>
       </c>
@@ -5528,7 +5481,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="202" spans="1:7" hidden="1">
+    <row r="202" spans="1:7">
       <c r="A202" s="3">
         <v>204</v>
       </c>
@@ -5547,25 +5500,25 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203" s="3">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="B203" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C203" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D203">
-        <v>0.625</v>
+        <v>0.375</v>
       </c>
       <c r="F203" t="s">
-        <v>486</v>
+        <v>462</v>
       </c>
       <c r="G203" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" hidden="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
       <c r="A204" s="3">
         <v>207</v>
       </c>
@@ -5580,7 +5533,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="205" spans="1:7" hidden="1">
+    <row r="205" spans="1:7">
       <c r="A205" s="3">
         <v>208</v>
       </c>
@@ -5595,7 +5548,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="206" spans="1:7" hidden="1">
+    <row r="206" spans="1:7">
       <c r="A206" s="3">
         <v>209</v>
       </c>
@@ -5610,7 +5563,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="207" spans="1:7" hidden="1">
+    <row r="207" spans="1:7">
       <c r="A207" s="3">
         <v>210</v>
       </c>
@@ -5625,7 +5578,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="208" spans="1:7" hidden="1">
+    <row r="208" spans="1:7">
       <c r="A208" s="3">
         <v>211</v>
       </c>
@@ -5640,7 +5593,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="209" spans="1:6" hidden="1">
+    <row r="209" spans="1:6">
       <c r="A209" s="3">
         <v>212</v>
       </c>
@@ -5655,7 +5608,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="210" spans="1:6" hidden="1">
+    <row r="210" spans="1:6">
       <c r="A210" s="3">
         <v>213</v>
       </c>
@@ -5670,7 +5623,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="211" spans="1:6" hidden="1">
+    <row r="211" spans="1:6">
       <c r="A211" s="3">
         <v>214</v>
       </c>
@@ -5685,7 +5638,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="212" spans="1:6" hidden="1">
+    <row r="212" spans="1:6">
       <c r="A212" s="3">
         <v>215</v>
       </c>
@@ -5700,7 +5653,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="213" spans="1:6" hidden="1">
+    <row r="213" spans="1:6">
       <c r="A213" s="3">
         <v>216</v>
       </c>
@@ -5715,7 +5668,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="214" spans="1:6" hidden="1">
+    <row r="214" spans="1:6">
       <c r="A214" s="3">
         <v>217</v>
       </c>
@@ -5730,7 +5683,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="215" spans="1:6" hidden="1">
+    <row r="215" spans="1:6">
       <c r="A215" s="3">
         <v>218</v>
       </c>
@@ -5745,7 +5698,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="216" spans="1:6" hidden="1">
+    <row r="216" spans="1:6">
       <c r="A216" s="3">
         <v>219</v>
       </c>
@@ -5760,7 +5713,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="217" spans="1:6" hidden="1">
+    <row r="217" spans="1:6">
       <c r="A217" s="3">
         <v>220</v>
       </c>
@@ -5775,7 +5728,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="218" spans="1:6" hidden="1">
+    <row r="218" spans="1:6">
       <c r="A218" s="3">
         <v>221</v>
       </c>
@@ -5790,7 +5743,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="219" spans="1:6" hidden="1">
+    <row r="219" spans="1:6">
       <c r="A219" s="3">
         <v>222</v>
       </c>
@@ -5805,7 +5758,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="220" spans="1:6" hidden="1">
+    <row r="220" spans="1:6">
       <c r="A220" s="3">
         <v>223</v>
       </c>
@@ -5820,7 +5773,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="221" spans="1:6" hidden="1">
+    <row r="221" spans="1:6">
       <c r="A221" s="3">
         <v>224</v>
       </c>
@@ -5835,7 +5788,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="222" spans="1:6" hidden="1">
+    <row r="222" spans="1:6">
       <c r="A222" s="3">
         <v>225</v>
       </c>
@@ -5850,7 +5803,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="223" spans="1:6" hidden="1">
+    <row r="223" spans="1:6">
       <c r="A223" s="3">
         <v>226</v>
       </c>
@@ -5865,7 +5818,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="224" spans="1:6" hidden="1">
+    <row r="224" spans="1:6">
       <c r="A224" s="3">
         <v>227</v>
       </c>
@@ -5880,7 +5833,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="225" spans="1:6" hidden="1">
+    <row r="225" spans="1:6">
       <c r="A225" s="3">
         <v>228</v>
       </c>
@@ -5895,7 +5848,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="226" spans="1:6" hidden="1">
+    <row r="226" spans="1:6">
       <c r="A226" s="3">
         <v>229</v>
       </c>
@@ -5910,7 +5863,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="227" spans="1:6" hidden="1">
+    <row r="227" spans="1:6">
       <c r="A227" s="3">
         <v>230</v>
       </c>
@@ -5925,7 +5878,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="228" spans="1:6" hidden="1">
+    <row r="228" spans="1:6">
       <c r="A228" s="3">
         <v>231</v>
       </c>
@@ -5940,7 +5893,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="229" spans="1:6" hidden="1">
+    <row r="229" spans="1:6">
       <c r="A229" s="3">
         <v>232</v>
       </c>
@@ -5955,7 +5908,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="230" spans="1:6" hidden="1">
+    <row r="230" spans="1:6">
       <c r="A230" s="3">
         <v>233</v>
       </c>
@@ -5970,7 +5923,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="231" spans="1:6" hidden="1">
+    <row r="231" spans="1:6">
       <c r="A231" s="3">
         <v>234</v>
       </c>
@@ -5985,7 +5938,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="232" spans="1:6" hidden="1">
+    <row r="232" spans="1:6">
       <c r="A232" s="3">
         <v>237</v>
       </c>
@@ -6002,7 +5955,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="233" spans="1:6" hidden="1">
+    <row r="233" spans="1:6">
       <c r="A233" s="3">
         <v>238</v>
       </c>
@@ -6016,7 +5969,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="234" spans="1:6" hidden="1">
+    <row r="234" spans="1:6">
       <c r="A234" s="3">
         <v>239</v>
       </c>
@@ -6033,7 +5986,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="235" spans="1:6" hidden="1">
+    <row r="235" spans="1:6">
       <c r="A235" s="3">
         <v>240</v>
       </c>
@@ -6047,7 +6000,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="236" spans="1:6" hidden="1">
+    <row r="236" spans="1:6">
       <c r="A236" s="3">
         <v>241</v>
       </c>
@@ -6062,7 +6015,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="237" spans="1:6" hidden="1">
+    <row r="237" spans="1:6">
       <c r="A237" s="3">
         <v>243</v>
       </c>
@@ -6077,7 +6030,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="238" spans="1:6" hidden="1">
+    <row r="238" spans="1:6">
       <c r="A238" s="3">
         <v>244</v>
       </c>
@@ -6092,7 +6045,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="239" spans="1:6" hidden="1">
+    <row r="239" spans="1:6">
       <c r="A239" s="3">
         <v>245</v>
       </c>
@@ -6109,7 +6062,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="240" spans="1:6" hidden="1">
+    <row r="240" spans="1:6">
       <c r="A240" s="3">
         <v>246</v>
       </c>
@@ -6126,7 +6079,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="241" spans="1:6" hidden="1">
+    <row r="241" spans="1:6">
       <c r="A241" s="3">
         <v>248</v>
       </c>
@@ -6140,7 +6093,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="242" spans="1:6" hidden="1">
+    <row r="242" spans="1:6">
       <c r="A242" s="3">
         <v>249</v>
       </c>
@@ -6154,7 +6107,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="243" spans="1:6" hidden="1">
+    <row r="243" spans="1:6">
       <c r="A243" s="3">
         <v>250</v>
       </c>
@@ -6168,7 +6121,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="244" spans="1:6" hidden="1">
+    <row r="244" spans="1:6">
       <c r="A244" s="3">
         <v>251</v>
       </c>
@@ -6185,7 +6138,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="245" spans="1:6" hidden="1">
+    <row r="245" spans="1:6">
       <c r="A245" s="3">
         <v>252</v>
       </c>
@@ -6202,7 +6155,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="246" spans="1:6" hidden="1">
+    <row r="246" spans="1:6">
       <c r="A246" s="3">
         <v>253</v>
       </c>
@@ -6219,7 +6172,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="247" spans="1:6" hidden="1">
+    <row r="247" spans="1:6">
       <c r="A247" s="3">
         <v>254</v>
       </c>
@@ -6236,7 +6189,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="248" spans="1:6" hidden="1">
+    <row r="248" spans="1:6">
       <c r="A248" s="3">
         <v>255</v>
       </c>
@@ -6253,7 +6206,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="249" spans="1:6" hidden="1">
+    <row r="249" spans="1:6">
       <c r="A249" s="3">
         <v>256</v>
       </c>
@@ -6267,7 +6220,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="250" spans="1:6" hidden="1">
+    <row r="250" spans="1:6">
       <c r="A250" s="3">
         <v>257</v>
       </c>
@@ -6284,7 +6237,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="251" spans="1:6" hidden="1">
+    <row r="251" spans="1:6">
       <c r="A251" s="3">
         <v>258</v>
       </c>
@@ -6301,7 +6254,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="252" spans="1:6" hidden="1">
+    <row r="252" spans="1:6">
       <c r="A252" s="3">
         <v>259</v>
       </c>
@@ -6318,7 +6271,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="253" spans="1:6" hidden="1">
+    <row r="253" spans="1:6">
       <c r="A253" s="3">
         <v>260</v>
       </c>
@@ -6332,7 +6285,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="254" spans="1:6" hidden="1">
+    <row r="254" spans="1:6">
       <c r="A254" s="3">
         <v>261</v>
       </c>
@@ -6347,7 +6300,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="255" spans="1:6" hidden="1">
+    <row r="255" spans="1:6">
       <c r="A255" s="3">
         <v>262</v>
       </c>
@@ -6364,7 +6317,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="256" spans="1:6" hidden="1">
+    <row r="256" spans="1:6">
       <c r="A256" s="3">
         <v>263</v>
       </c>
@@ -6378,7 +6331,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="257" spans="1:6" hidden="1">
+    <row r="257" spans="1:6">
       <c r="A257" s="3">
         <v>264</v>
       </c>
@@ -6393,7 +6346,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="258" spans="1:6" hidden="1">
+    <row r="258" spans="1:6">
       <c r="A258" s="3">
         <v>265</v>
       </c>
@@ -6407,7 +6360,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="259" spans="1:6" hidden="1">
+    <row r="259" spans="1:6">
       <c r="A259" s="3">
         <v>266</v>
       </c>
@@ -6424,7 +6377,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="260" spans="1:6" hidden="1">
+    <row r="260" spans="1:6">
       <c r="A260" s="3">
         <v>267</v>
       </c>
@@ -6441,7 +6394,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="261" spans="1:6" hidden="1">
+    <row r="261" spans="1:6">
       <c r="A261" s="3">
         <v>268</v>
       </c>
@@ -6458,7 +6411,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="262" spans="1:6" hidden="1">
+    <row r="262" spans="1:6">
       <c r="A262" s="3">
         <v>269</v>
       </c>
@@ -6475,7 +6428,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="263" spans="1:6" hidden="1">
+    <row r="263" spans="1:6">
       <c r="A263" s="3">
         <v>270</v>
       </c>
@@ -6492,7 +6445,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="264" spans="1:6" hidden="1">
+    <row r="264" spans="1:6">
       <c r="A264" s="3">
         <v>272</v>
       </c>
@@ -6509,7 +6462,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="265" spans="1:6" hidden="1">
+    <row r="265" spans="1:6">
       <c r="A265" s="3">
         <v>273</v>
       </c>
@@ -6526,7 +6479,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="266" spans="1:6" hidden="1">
+    <row r="266" spans="1:6">
       <c r="A266" s="3">
         <v>274</v>
       </c>
@@ -6543,7 +6496,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="267" spans="1:6" hidden="1">
+    <row r="267" spans="1:6">
       <c r="A267" s="3">
         <v>275</v>
       </c>
@@ -6560,7 +6513,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="268" spans="1:6" hidden="1">
+    <row r="268" spans="1:6">
       <c r="A268" s="3">
         <v>276</v>
       </c>
@@ -6577,7 +6530,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="269" spans="1:6" hidden="1">
+    <row r="269" spans="1:6">
       <c r="A269" s="3">
         <v>277</v>
       </c>
@@ -6594,7 +6547,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="270" spans="1:6" hidden="1">
+    <row r="270" spans="1:6">
       <c r="A270" s="3">
         <v>278</v>
       </c>
@@ -6611,7 +6564,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="271" spans="1:6" hidden="1">
+    <row r="271" spans="1:6">
       <c r="A271" s="3">
         <v>279</v>
       </c>
@@ -6628,7 +6581,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="272" spans="1:6" hidden="1">
+    <row r="272" spans="1:6">
       <c r="A272" s="3">
         <v>280</v>
       </c>
@@ -6642,7 +6595,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="273" spans="1:7" hidden="1">
+    <row r="273" spans="1:7">
       <c r="A273" s="3">
         <v>281</v>
       </c>
@@ -6659,7 +6612,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="274" spans="1:7" hidden="1">
+    <row r="274" spans="1:7">
       <c r="A274" s="3">
         <v>282</v>
       </c>
@@ -6678,25 +6631,28 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275" s="3">
-        <v>482</v>
+        <v>283</v>
       </c>
       <c r="B275" t="s">
-        <v>381</v>
+        <v>194</v>
       </c>
       <c r="C275" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D275">
-        <v>0.75</v>
+        <v>0</v>
+      </c>
+      <c r="E275">
+        <v>100</v>
       </c>
       <c r="F275" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="G275" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" hidden="1">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
       <c r="A276" s="3">
         <v>284</v>
       </c>
@@ -6713,7 +6669,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="277" spans="1:7" hidden="1">
+    <row r="277" spans="1:7">
       <c r="A277" s="3">
         <v>285</v>
       </c>
@@ -6727,7 +6683,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="278" spans="1:7" hidden="1">
+    <row r="278" spans="1:7">
       <c r="A278" s="3">
         <v>286</v>
       </c>
@@ -6741,7 +6697,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="279" spans="1:7" hidden="1">
+    <row r="279" spans="1:7">
       <c r="A279" s="3">
         <v>287</v>
       </c>
@@ -6758,7 +6714,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="280" spans="1:7" hidden="1">
+    <row r="280" spans="1:7">
       <c r="A280" s="3">
         <v>288</v>
       </c>
@@ -6775,7 +6731,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="281" spans="1:7" hidden="1">
+    <row r="281" spans="1:7">
       <c r="A281" s="3">
         <v>289</v>
       </c>
@@ -6790,7 +6746,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="282" spans="1:7" hidden="1">
+    <row r="282" spans="1:7">
       <c r="A282" s="3">
         <v>291</v>
       </c>
@@ -6807,45 +6763,51 @@
     </row>
     <row r="283" spans="1:7">
       <c r="A283" s="3">
-        <v>455</v>
+        <v>292</v>
       </c>
       <c r="B283" t="s">
-        <v>357</v>
+        <v>203</v>
       </c>
       <c r="C283" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D283">
-        <v>0.625</v>
+        <v>0</v>
+      </c>
+      <c r="E283">
+        <v>400</v>
       </c>
       <c r="F283" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="G283" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="284" spans="1:7">
       <c r="A284" s="3">
-        <v>471</v>
+        <v>293</v>
       </c>
       <c r="B284" t="s">
-        <v>373</v>
+        <v>204</v>
       </c>
       <c r="C284" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D284">
-        <v>0.625</v>
+        <v>0</v>
+      </c>
+      <c r="E284">
+        <v>400</v>
       </c>
       <c r="F284" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="G284" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
       <c r="A285" s="3">
         <v>294</v>
       </c>
@@ -6862,7 +6824,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="286" spans="1:7" hidden="1">
+    <row r="286" spans="1:7">
       <c r="A286" s="3">
         <v>295</v>
       </c>
@@ -6879,7 +6841,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="287" spans="1:7" hidden="1">
+    <row r="287" spans="1:7">
       <c r="A287" s="3">
         <v>296</v>
       </c>
@@ -6893,7 +6855,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="288" spans="1:7" hidden="1">
+    <row r="288" spans="1:7">
       <c r="A288" s="3">
         <v>297</v>
       </c>
@@ -6910,7 +6872,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="289" spans="1:7" hidden="1">
+    <row r="289" spans="1:7">
       <c r="A289" s="3">
         <v>298</v>
       </c>
@@ -6927,7 +6889,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="290" spans="1:7" hidden="1">
+    <row r="290" spans="1:7">
       <c r="A290" s="3">
         <v>299</v>
       </c>
@@ -6944,7 +6906,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="291" spans="1:7" hidden="1">
+    <row r="291" spans="1:7">
       <c r="A291" s="3">
         <v>300</v>
       </c>
@@ -6958,7 +6920,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="292" spans="1:7" hidden="1">
+    <row r="292" spans="1:7">
       <c r="A292" s="3">
         <v>301</v>
       </c>
@@ -6992,7 +6954,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="294" spans="1:7" hidden="1">
+    <row r="294" spans="1:7">
       <c r="A294" s="3">
         <v>303</v>
       </c>
@@ -7009,7 +6971,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="295" spans="1:7" hidden="1">
+    <row r="295" spans="1:7">
       <c r="A295" s="3">
         <v>304</v>
       </c>
@@ -7023,7 +6985,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="296" spans="1:7" hidden="1">
+    <row r="296" spans="1:7">
       <c r="A296" s="3">
         <v>305</v>
       </c>
@@ -7042,45 +7004,48 @@
     </row>
     <row r="297" spans="1:7">
       <c r="A297" s="3">
-        <v>191</v>
+        <v>307</v>
       </c>
       <c r="B297" t="s">
-        <v>101</v>
+        <v>219</v>
       </c>
       <c r="C297" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D297">
-        <v>0.375</v>
+        <v>0</v>
+      </c>
+      <c r="E297">
+        <v>250</v>
       </c>
       <c r="F297" t="s">
-        <v>486</v>
-      </c>
-      <c r="G297" s="7" t="s">
-        <v>499</v>
+        <v>489</v>
+      </c>
+      <c r="G297" s="5" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="298" spans="1:7">
       <c r="A298" s="3">
-        <v>178</v>
+        <v>308</v>
       </c>
       <c r="B298" t="s">
-        <v>88</v>
+        <v>220</v>
       </c>
       <c r="C298" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D298">
-        <v>0.375</v>
-      </c>
-      <c r="F298" t="s">
+        <v>0.25</v>
+      </c>
+      <c r="F298" s="6" t="s">
         <v>486</v>
       </c>
       <c r="G298" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="299" spans="1:7" hidden="1">
+    <row r="299" spans="1:7">
       <c r="A299" s="3">
         <v>309</v>
       </c>
@@ -7094,7 +7059,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="300" spans="1:7" hidden="1">
+    <row r="300" spans="1:7">
       <c r="A300" s="3">
         <v>310</v>
       </c>
@@ -7108,7 +7073,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="301" spans="1:7" hidden="1">
+    <row r="301" spans="1:7">
       <c r="A301" s="3">
         <v>311</v>
       </c>
@@ -7122,7 +7087,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="302" spans="1:7" hidden="1">
+    <row r="302" spans="1:7">
       <c r="A302" s="3">
         <v>312</v>
       </c>
@@ -7136,7 +7101,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="303" spans="1:7" hidden="1">
+    <row r="303" spans="1:7">
       <c r="A303" s="3">
         <v>313</v>
       </c>
@@ -7153,25 +7118,28 @@
     </row>
     <row r="304" spans="1:7">
       <c r="A304" s="3">
-        <v>364</v>
+        <v>314</v>
       </c>
       <c r="B304" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="C304" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D304">
-        <v>0.625</v>
+        <v>0</v>
+      </c>
+      <c r="E304">
+        <v>150</v>
       </c>
       <c r="F304" t="s">
-        <v>465</v>
+        <v>487</v>
       </c>
       <c r="G304" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
       <c r="A305" s="3">
         <v>315</v>
       </c>
@@ -7188,7 +7156,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="306" spans="1:7" hidden="1">
+    <row r="306" spans="1:7">
       <c r="A306" s="3">
         <v>316</v>
       </c>
@@ -7205,7 +7173,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="307" spans="1:7" hidden="1">
+    <row r="307" spans="1:7">
       <c r="A307" s="3">
         <v>317</v>
       </c>
@@ -7222,7 +7190,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="308" spans="1:7" hidden="1">
+    <row r="308" spans="1:7">
       <c r="A308" s="3">
         <v>318</v>
       </c>
@@ -7239,7 +7207,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="309" spans="1:7" hidden="1">
+    <row r="309" spans="1:7">
       <c r="A309" s="3">
         <v>319</v>
       </c>
@@ -7256,7 +7224,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="310" spans="1:7" hidden="1">
+    <row r="310" spans="1:7">
       <c r="A310" s="3">
         <v>320</v>
       </c>
@@ -7273,7 +7241,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="311" spans="1:7" hidden="1">
+    <row r="311" spans="1:7">
       <c r="A311" s="3">
         <v>321</v>
       </c>
@@ -7290,7 +7258,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="312" spans="1:7" hidden="1">
+    <row r="312" spans="1:7">
       <c r="A312" s="3">
         <v>322</v>
       </c>
@@ -7307,7 +7275,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="313" spans="1:7" hidden="1">
+    <row r="313" spans="1:7">
       <c r="A313" s="3">
         <v>323</v>
       </c>
@@ -7324,7 +7292,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="314" spans="1:7" hidden="1">
+    <row r="314" spans="1:7">
       <c r="A314" s="3">
         <v>324</v>
       </c>
@@ -7341,7 +7309,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="315" spans="1:7" hidden="1">
+    <row r="315" spans="1:7">
       <c r="A315" s="3">
         <v>325</v>
       </c>
@@ -7358,7 +7326,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="316" spans="1:7" hidden="1">
+    <row r="316" spans="1:7">
       <c r="A316" s="3">
         <v>326</v>
       </c>
@@ -7375,7 +7343,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="317" spans="1:7" hidden="1">
+    <row r="317" spans="1:7">
       <c r="A317" s="3">
         <v>327</v>
       </c>
@@ -7394,10 +7362,10 @@
     </row>
     <row r="318" spans="1:7">
       <c r="A318" s="3">
-        <v>33</v>
+        <v>328</v>
       </c>
       <c r="B318" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C318" s="1">
         <v>3</v>
@@ -7406,13 +7374,13 @@
         <v>0.625</v>
       </c>
       <c r="F318" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="G318" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="319" spans="1:7" hidden="1">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7">
       <c r="A319" s="3">
         <v>329</v>
       </c>
@@ -7427,7 +7395,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="320" spans="1:7" hidden="1">
+    <row r="320" spans="1:7">
       <c r="A320" s="3">
         <v>331</v>
       </c>
@@ -7441,7 +7409,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="321" spans="1:6" hidden="1">
+    <row r="321" spans="1:6">
       <c r="A321" s="3">
         <v>332</v>
       </c>
@@ -7458,7 +7426,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="322" spans="1:6" hidden="1">
+    <row r="322" spans="1:6">
       <c r="A322" s="3">
         <v>333</v>
       </c>
@@ -7475,7 +7443,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="323" spans="1:6" hidden="1">
+    <row r="323" spans="1:6">
       <c r="A323" s="3">
         <v>334</v>
       </c>
@@ -7489,7 +7457,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="324" spans="1:6" hidden="1">
+    <row r="324" spans="1:6">
       <c r="A324" s="3">
         <v>336</v>
       </c>
@@ -7503,7 +7471,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="325" spans="1:6" hidden="1">
+    <row r="325" spans="1:6">
       <c r="A325" s="3">
         <v>338</v>
       </c>
@@ -7520,7 +7488,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="326" spans="1:6" hidden="1">
+    <row r="326" spans="1:6">
       <c r="A326" s="3">
         <v>339</v>
       </c>
@@ -7537,7 +7505,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="327" spans="1:6" hidden="1">
+    <row r="327" spans="1:6">
       <c r="A327" s="3">
         <v>340</v>
       </c>
@@ -7552,7 +7520,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="328" spans="1:6" hidden="1">
+    <row r="328" spans="1:6">
       <c r="A328" s="3">
         <v>341</v>
       </c>
@@ -7569,7 +7537,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="329" spans="1:6" hidden="1">
+    <row r="329" spans="1:6">
       <c r="A329" s="3">
         <v>342</v>
       </c>
@@ -7586,7 +7554,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="330" spans="1:6" hidden="1">
+    <row r="330" spans="1:6">
       <c r="A330" s="3">
         <v>344</v>
       </c>
@@ -7600,7 +7568,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="331" spans="1:6" hidden="1">
+    <row r="331" spans="1:6">
       <c r="A331" s="3">
         <v>345</v>
       </c>
@@ -7617,7 +7585,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="332" spans="1:6" hidden="1">
+    <row r="332" spans="1:6">
       <c r="A332" s="3">
         <v>347</v>
       </c>
@@ -7634,7 +7602,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="333" spans="1:6" hidden="1">
+    <row r="333" spans="1:6">
       <c r="A333" s="3">
         <v>348</v>
       </c>
@@ -7651,7 +7619,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="334" spans="1:6" hidden="1">
+    <row r="334" spans="1:6">
       <c r="A334" s="3">
         <v>349</v>
       </c>
@@ -7668,7 +7636,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="335" spans="1:6" hidden="1">
+    <row r="335" spans="1:6">
       <c r="A335" s="3">
         <v>350</v>
       </c>
@@ -7685,7 +7653,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="336" spans="1:6" hidden="1">
+    <row r="336" spans="1:6">
       <c r="A336" s="3">
         <v>351</v>
       </c>
@@ -7702,7 +7670,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="337" spans="1:7" hidden="1">
+    <row r="337" spans="1:7">
       <c r="A337" s="3">
         <v>353</v>
       </c>
@@ -7716,7 +7684,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="338" spans="1:7" hidden="1">
+    <row r="338" spans="1:7">
       <c r="A338" s="3">
         <v>354</v>
       </c>
@@ -7733,7 +7701,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="339" spans="1:7" hidden="1">
+    <row r="339" spans="1:7">
       <c r="A339" s="3">
         <v>355</v>
       </c>
@@ -7750,7 +7718,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="340" spans="1:7" hidden="1">
+    <row r="340" spans="1:7">
       <c r="A340" s="3">
         <v>357</v>
       </c>
@@ -7767,21 +7735,27 @@
         <v>63</v>
       </c>
     </row>
-    <row r="341" spans="1:7" hidden="1">
+    <row r="341" spans="1:7">
       <c r="A341" s="3">
         <v>358</v>
       </c>
       <c r="B341" t="s">
         <v>264</v>
       </c>
+      <c r="C341">
+        <v>8</v>
+      </c>
       <c r="D341" t="s">
         <v>63</v>
       </c>
       <c r="F341" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="342" spans="1:7" hidden="1">
+        <v>487</v>
+      </c>
+      <c r="G341" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7">
       <c r="A342" s="3">
         <v>359</v>
       </c>
@@ -7800,48 +7774,51 @@
     </row>
     <row r="343" spans="1:7">
       <c r="A343" s="3">
-        <v>485</v>
+        <v>360</v>
       </c>
       <c r="B343" t="s">
-        <v>382</v>
+        <v>267</v>
       </c>
       <c r="C343" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D343">
-        <v>0.625</v>
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>250</v>
       </c>
       <c r="F343" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="G343" t="s">
-        <v>518</v>
+        <v>504</v>
       </c>
     </row>
     <row r="344" spans="1:7">
       <c r="A344" s="3">
-        <v>493</v>
+        <v>361</v>
       </c>
       <c r="B344" t="s">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="C344" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D344">
         <v>0</v>
       </c>
       <c r="E344">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F344" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="G344" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="345" spans="1:7" hidden="1">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7">
       <c r="A345" s="3">
         <v>362</v>
       </c>
@@ -7858,7 +7835,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="346" spans="1:7" hidden="1">
+    <row r="346" spans="1:7">
       <c r="A346" s="3">
         <v>363</v>
       </c>
@@ -7874,10 +7851,10 @@
     </row>
     <row r="347" spans="1:7">
       <c r="A347" s="3">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="B347" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="C347" s="1">
         <v>3</v>
@@ -7886,13 +7863,13 @@
         <v>0.625</v>
       </c>
       <c r="F347" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G347" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="348" spans="1:7" hidden="1">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7">
       <c r="A348" s="3">
         <v>365</v>
       </c>
@@ -7906,7 +7883,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="349" spans="1:7" hidden="1">
+    <row r="349" spans="1:7">
       <c r="A349" s="3">
         <v>366</v>
       </c>
@@ -7922,25 +7899,25 @@
     </row>
     <row r="350" spans="1:7">
       <c r="A350" s="3">
-        <v>488</v>
+        <v>367</v>
       </c>
       <c r="B350" t="s">
-        <v>385</v>
+        <v>274</v>
       </c>
       <c r="C350" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D350">
-        <v>0.625</v>
+        <v>0.375</v>
       </c>
       <c r="F350" t="s">
-        <v>481</v>
-      </c>
-      <c r="G350" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="351" spans="1:7" hidden="1">
+        <v>465</v>
+      </c>
+      <c r="G350" s="6" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7">
       <c r="A351" s="3">
         <v>368</v>
       </c>
@@ -7957,7 +7934,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="352" spans="1:7" hidden="1">
+    <row r="352" spans="1:7">
       <c r="A352" s="3">
         <v>369</v>
       </c>
@@ -7974,7 +7951,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="353" spans="1:6" hidden="1">
+    <row r="353" spans="1:6">
       <c r="A353" s="3">
         <v>371</v>
       </c>
@@ -7991,7 +7968,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="354" spans="1:6" hidden="1">
+    <row r="354" spans="1:6">
       <c r="A354" s="3">
         <v>372</v>
       </c>
@@ -8008,7 +7985,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="355" spans="1:6" hidden="1">
+    <row r="355" spans="1:6">
       <c r="A355" s="3">
         <v>373</v>
       </c>
@@ -8025,7 +8002,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="356" spans="1:6" hidden="1">
+    <row r="356" spans="1:6">
       <c r="A356" s="3">
         <v>375</v>
       </c>
@@ -8042,7 +8019,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="357" spans="1:6" hidden="1">
+    <row r="357" spans="1:6">
       <c r="A357" s="3">
         <v>376</v>
       </c>
@@ -8059,7 +8036,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="358" spans="1:6" hidden="1">
+    <row r="358" spans="1:6">
       <c r="A358" s="3">
         <v>377</v>
       </c>
@@ -8076,7 +8053,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="359" spans="1:6" hidden="1">
+    <row r="359" spans="1:6">
       <c r="A359" s="3">
         <v>378</v>
       </c>
@@ -8090,7 +8067,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="360" spans="1:6" hidden="1">
+    <row r="360" spans="1:6">
       <c r="A360" s="3">
         <v>379</v>
       </c>
@@ -8105,7 +8082,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="361" spans="1:6" hidden="1">
+    <row r="361" spans="1:6">
       <c r="A361" s="3">
         <v>380</v>
       </c>
@@ -8122,7 +8099,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="362" spans="1:6" hidden="1">
+    <row r="362" spans="1:6">
       <c r="A362" s="3">
         <v>381</v>
       </c>
@@ -8139,7 +8116,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="363" spans="1:6" hidden="1">
+    <row r="363" spans="1:6">
       <c r="A363" s="3">
         <v>382</v>
       </c>
@@ -8156,7 +8133,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="364" spans="1:6" hidden="1">
+    <row r="364" spans="1:6">
       <c r="A364" s="3">
         <v>383</v>
       </c>
@@ -8173,7 +8150,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="365" spans="1:6" hidden="1">
+    <row r="365" spans="1:6">
       <c r="A365" s="3">
         <v>384</v>
       </c>
@@ -8190,7 +8167,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="366" spans="1:6" hidden="1">
+    <row r="366" spans="1:6">
       <c r="A366" s="3">
         <v>386</v>
       </c>
@@ -8207,7 +8184,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="367" spans="1:6" hidden="1">
+    <row r="367" spans="1:6">
       <c r="A367" s="3">
         <v>387</v>
       </c>
@@ -8224,7 +8201,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="368" spans="1:6" hidden="1">
+    <row r="368" spans="1:6">
       <c r="A368" s="3">
         <v>388</v>
       </c>
@@ -8243,25 +8220,28 @@
     </row>
     <row r="369" spans="1:7">
       <c r="A369" s="3">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="B369" t="s">
-        <v>320</v>
+        <v>295</v>
       </c>
       <c r="C369" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D369">
-        <v>0.625</v>
+        <v>0</v>
+      </c>
+      <c r="E369">
+        <v>250</v>
       </c>
       <c r="F369" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="G369" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="370" spans="1:7" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7">
       <c r="A370" s="3">
         <v>391</v>
       </c>
@@ -8275,7 +8255,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="371" spans="1:7" hidden="1">
+    <row r="371" spans="1:7">
       <c r="A371" s="3">
         <v>392</v>
       </c>
@@ -8289,7 +8269,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="372" spans="1:7" hidden="1">
+    <row r="372" spans="1:7">
       <c r="A372" s="3">
         <v>393</v>
       </c>
@@ -8303,7 +8283,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="373" spans="1:7" hidden="1">
+    <row r="373" spans="1:7">
       <c r="A373" s="3">
         <v>394</v>
       </c>
@@ -8322,25 +8302,28 @@
     </row>
     <row r="374" spans="1:7">
       <c r="A374" s="3">
-        <v>205</v>
+        <v>395</v>
       </c>
       <c r="B374" t="s">
-        <v>117</v>
+        <v>301</v>
       </c>
       <c r="C374" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D374">
-        <v>0.375</v>
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>100</v>
       </c>
       <c r="F374" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="G374" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="375" spans="1:7" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7">
       <c r="A375" s="3">
         <v>396</v>
       </c>
@@ -8359,25 +8342,25 @@
     </row>
     <row r="376" spans="1:7">
       <c r="A376" s="3">
-        <v>114</v>
+        <v>397</v>
       </c>
       <c r="B376" t="s">
-        <v>19</v>
+        <v>303</v>
       </c>
       <c r="C376" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D376">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="F376" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="G376" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="377" spans="1:7" hidden="1">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7">
       <c r="A377" s="3">
         <v>398</v>
       </c>
@@ -8391,7 +8374,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="378" spans="1:7" hidden="1">
+    <row r="378" spans="1:7">
       <c r="A378" s="3">
         <v>399</v>
       </c>
@@ -8408,7 +8391,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="379" spans="1:7" hidden="1">
+    <row r="379" spans="1:7">
       <c r="A379" s="3">
         <v>400</v>
       </c>
@@ -8425,7 +8408,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="380" spans="1:7" hidden="1">
+    <row r="380" spans="1:7">
       <c r="A380" s="3">
         <v>401</v>
       </c>
@@ -8442,7 +8425,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="381" spans="1:7" hidden="1">
+    <row r="381" spans="1:7">
       <c r="A381" s="3">
         <v>402</v>
       </c>
@@ -8459,7 +8442,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="382" spans="1:7" hidden="1">
+    <row r="382" spans="1:7">
       <c r="A382" s="3">
         <v>403</v>
       </c>
@@ -8476,7 +8459,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="383" spans="1:7" hidden="1">
+    <row r="383" spans="1:7">
       <c r="A383" s="3">
         <v>404</v>
       </c>
@@ -8493,7 +8476,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="384" spans="1:7" hidden="1">
+    <row r="384" spans="1:7">
       <c r="A384" s="3">
         <v>405</v>
       </c>
@@ -8510,7 +8493,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="385" spans="1:7" hidden="1">
+    <row r="385" spans="1:7">
       <c r="A385" s="3">
         <v>406</v>
       </c>
@@ -8527,7 +8510,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="386" spans="1:7" hidden="1">
+    <row r="386" spans="1:7">
       <c r="A386" s="3">
         <v>407</v>
       </c>
@@ -8544,7 +8527,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="387" spans="1:7" hidden="1">
+    <row r="387" spans="1:7">
       <c r="A387" s="3">
         <v>409</v>
       </c>
@@ -8561,7 +8544,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="388" spans="1:7" hidden="1">
+    <row r="388" spans="1:7">
       <c r="A388" s="3">
         <v>410</v>
       </c>
@@ -8578,7 +8561,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="389" spans="1:7" hidden="1">
+    <row r="389" spans="1:7">
       <c r="A389" s="3">
         <v>411</v>
       </c>
@@ -8595,7 +8578,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="390" spans="1:7" hidden="1">
+    <row r="390" spans="1:7">
       <c r="A390" s="3">
         <v>412</v>
       </c>
@@ -8614,25 +8597,25 @@
     </row>
     <row r="391" spans="1:7">
       <c r="A391" s="3">
-        <v>21</v>
+        <v>413</v>
       </c>
       <c r="B391" t="s">
-        <v>121</v>
+        <v>320</v>
       </c>
       <c r="C391" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D391">
         <v>0.625</v>
       </c>
       <c r="F391" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="G391" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="392" spans="1:7" hidden="1">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7">
       <c r="A392" s="3">
         <v>414</v>
       </c>
@@ -8649,7 +8632,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="393" spans="1:7" hidden="1">
+    <row r="393" spans="1:7">
       <c r="A393" s="3">
         <v>415</v>
       </c>
@@ -8666,7 +8649,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="394" spans="1:7" hidden="1">
+    <row r="394" spans="1:7">
       <c r="A394" s="3">
         <v>416</v>
       </c>
@@ -8681,7 +8664,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="395" spans="1:7" hidden="1">
+    <row r="395" spans="1:7">
       <c r="A395" s="3">
         <v>417</v>
       </c>
@@ -8696,7 +8679,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="396" spans="1:7" hidden="1">
+    <row r="396" spans="1:7">
       <c r="A396" s="3">
         <v>418</v>
       </c>
@@ -8710,7 +8693,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="397" spans="1:7" hidden="1">
+    <row r="397" spans="1:7">
       <c r="A397" s="3">
         <v>419</v>
       </c>
@@ -8729,88 +8712,94 @@
     </row>
     <row r="398" spans="1:7">
       <c r="A398" s="3">
-        <v>283</v>
+        <v>420</v>
       </c>
       <c r="B398" t="s">
-        <v>194</v>
+        <v>327</v>
       </c>
       <c r="C398" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D398">
-        <v>0</v>
-      </c>
-      <c r="E398">
-        <v>100</v>
+        <v>0.625</v>
       </c>
       <c r="F398" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="G398" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
     </row>
     <row r="399" spans="1:7">
       <c r="A399" s="3">
-        <v>501</v>
+        <v>421</v>
       </c>
       <c r="B399" t="s">
+        <v>328</v>
+      </c>
+      <c r="C399" s="1">
+        <v>7</v>
+      </c>
+      <c r="D399">
+        <v>0</v>
+      </c>
+      <c r="E399">
         <v>400</v>
       </c>
-      <c r="C399" s="1">
-        <v>3</v>
-      </c>
-      <c r="D399">
-        <v>0.375</v>
-      </c>
       <c r="F399" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G399" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="400" spans="1:7">
       <c r="A400" s="3">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B400" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C400" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D400">
-        <v>0.625</v>
+        <v>0</v>
+      </c>
+      <c r="E400">
+        <v>200</v>
       </c>
       <c r="F400" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="G400" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="401" spans="1:7">
       <c r="A401" s="3">
-        <v>67</v>
+        <v>423</v>
       </c>
       <c r="B401" t="s">
-        <v>419</v>
+        <v>330</v>
       </c>
       <c r="C401" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D401">
-        <v>0.375</v>
+        <v>0</v>
+      </c>
+      <c r="E401">
+        <v>150</v>
       </c>
       <c r="F401" t="s">
-        <v>459</v>
+        <v>506</v>
       </c>
       <c r="G401" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="402" spans="1:7" hidden="1">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7">
       <c r="A402" s="3">
         <v>424</v>
       </c>
@@ -8827,7 +8816,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="403" spans="1:7" hidden="1">
+    <row r="403" spans="1:7">
       <c r="A403" s="3">
         <v>425</v>
       </c>
@@ -8841,7 +8830,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="404" spans="1:7" hidden="1">
+    <row r="404" spans="1:7">
       <c r="A404" s="3">
         <v>426</v>
       </c>
@@ -8855,7 +8844,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="405" spans="1:7" hidden="1">
+    <row r="405" spans="1:7">
       <c r="A405" s="3">
         <v>427</v>
       </c>
@@ -8874,65 +8863,71 @@
     </row>
     <row r="406" spans="1:7">
       <c r="A406" s="3">
-        <v>1</v>
+        <v>428</v>
       </c>
       <c r="B406" t="s">
+        <v>334</v>
+      </c>
+      <c r="C406" s="1">
         <v>2</v>
       </c>
-      <c r="C406" s="1">
-        <v>1</v>
-      </c>
       <c r="D406">
-        <v>1</v>
-      </c>
-      <c r="F406" s="5" t="s">
-        <v>455</v>
+        <v>0.625</v>
+      </c>
+      <c r="F406" t="s">
+        <v>468</v>
       </c>
       <c r="G406" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
     </row>
     <row r="407" spans="1:7">
       <c r="A407" s="3">
-        <v>308</v>
+        <v>430</v>
       </c>
       <c r="B407" t="s">
-        <v>220</v>
+        <v>336</v>
       </c>
       <c r="C407" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D407">
-        <v>0.25</v>
-      </c>
-      <c r="F407" s="8" t="s">
-        <v>486</v>
+        <v>0</v>
+      </c>
+      <c r="E407">
+        <v>100</v>
+      </c>
+      <c r="F407" t="s">
+        <v>488</v>
       </c>
       <c r="G407" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
     </row>
     <row r="408" spans="1:7">
       <c r="A408" s="3">
-        <v>179</v>
+        <v>431</v>
       </c>
       <c r="B408" t="s">
-        <v>89</v>
+        <v>337</v>
       </c>
       <c r="C408" s="1">
         <v>7</v>
       </c>
       <c r="D408">
-        <v>0.25</v>
+        <v>0</v>
+      </c>
+      <c r="E408">
+        <v>250</v>
       </c>
       <c r="F408" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="G408" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="409" spans="1:7" hidden="1">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7">
       <c r="A409" s="3">
         <v>434</v>
       </c>
@@ -8949,7 +8944,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="410" spans="1:7" hidden="1">
+    <row r="410" spans="1:7">
       <c r="A410" s="3">
         <v>437</v>
       </c>
@@ -8964,7 +8959,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="411" spans="1:7" hidden="1">
+    <row r="411" spans="1:7">
       <c r="A411" s="3">
         <v>438</v>
       </c>
@@ -8979,7 +8974,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="412" spans="1:7" hidden="1">
+    <row r="412" spans="1:7">
       <c r="A412" s="3">
         <v>439</v>
       </c>
@@ -8994,22 +8989,24 @@
         <v>63</v>
       </c>
     </row>
-    <row r="413" spans="1:7" hidden="1">
+    <row r="413" spans="1:7">
       <c r="A413" s="3">
         <v>440</v>
       </c>
       <c r="B413" t="s">
         <v>343</v>
       </c>
-      <c r="C413" s="1"/>
-      <c r="D413" t="s">
-        <v>63</v>
+      <c r="C413" s="1">
+        <v>8</v>
       </c>
       <c r="F413" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="414" spans="1:7" hidden="1">
+        <v>463</v>
+      </c>
+      <c r="G413" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7">
       <c r="A414" s="3">
         <v>441</v>
       </c>
@@ -9024,7 +9021,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="415" spans="1:7" hidden="1">
+    <row r="415" spans="1:7">
       <c r="A415" s="3">
         <v>442</v>
       </c>
@@ -9041,7 +9038,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="416" spans="1:7" hidden="1">
+    <row r="416" spans="1:7">
       <c r="A416" s="3">
         <v>443</v>
       </c>
@@ -9058,7 +9055,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="417" spans="1:7" hidden="1">
+    <row r="417" spans="1:7">
       <c r="A417" s="3">
         <v>444</v>
       </c>
@@ -9075,7 +9072,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="418" spans="1:7" hidden="1">
+    <row r="418" spans="1:7">
       <c r="A418" s="3">
         <v>445</v>
       </c>
@@ -9092,7 +9089,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="419" spans="1:7" hidden="1">
+    <row r="419" spans="1:7">
       <c r="A419" s="3">
         <v>446</v>
       </c>
@@ -9109,7 +9106,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="420" spans="1:7" hidden="1">
+    <row r="420" spans="1:7">
       <c r="A420" s="3">
         <v>447</v>
       </c>
@@ -9126,7 +9123,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="421" spans="1:7" hidden="1">
+    <row r="421" spans="1:7">
       <c r="A421" s="3">
         <v>448</v>
       </c>
@@ -9140,7 +9137,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="422" spans="1:7" hidden="1">
+    <row r="422" spans="1:7">
       <c r="A422" s="3">
         <v>450</v>
       </c>
@@ -9154,7 +9151,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="423" spans="1:7" hidden="1">
+    <row r="423" spans="1:7">
       <c r="A423" s="3">
         <v>451</v>
       </c>
@@ -9168,7 +9165,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="424" spans="1:7" hidden="1">
+    <row r="424" spans="1:7">
       <c r="A424" s="3">
         <v>452</v>
       </c>
@@ -9182,7 +9179,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="425" spans="1:7" hidden="1">
+    <row r="425" spans="1:7">
       <c r="A425" s="3">
         <v>453</v>
       </c>
@@ -9201,70 +9198,70 @@
     </row>
     <row r="426" spans="1:7">
       <c r="A426" s="3">
-        <v>188</v>
+        <v>455</v>
       </c>
       <c r="B426" t="s">
-        <v>98</v>
+        <v>357</v>
       </c>
       <c r="C426" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D426">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="F426" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="G426" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
     </row>
     <row r="427" spans="1:7">
       <c r="A427" s="3">
-        <v>367</v>
+        <v>456</v>
       </c>
       <c r="B427" t="s">
-        <v>274</v>
+        <v>358</v>
       </c>
       <c r="C427" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D427">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="F427" t="s">
-        <v>465</v>
-      </c>
-      <c r="G427" s="8" t="s">
-        <v>504</v>
+        <v>469</v>
+      </c>
+      <c r="G427" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="428" spans="1:7">
       <c r="A428" s="3">
-        <v>30</v>
+        <v>457</v>
       </c>
       <c r="B428" t="s">
-        <v>212</v>
+        <v>359</v>
       </c>
       <c r="C428" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D428">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="F428" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="G428" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
     </row>
     <row r="429" spans="1:7">
       <c r="A429" s="3">
-        <v>65</v>
+        <v>458</v>
       </c>
       <c r="B429" t="s">
-        <v>417</v>
+        <v>360</v>
       </c>
       <c r="C429" s="1">
         <v>2</v>
@@ -9273,164 +9270,158 @@
         <v>0.75</v>
       </c>
       <c r="F429" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="G429" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
     </row>
     <row r="430" spans="1:7">
       <c r="A430" s="3">
-        <v>428</v>
+        <v>459</v>
       </c>
       <c r="B430" t="s">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="C430" s="1">
         <v>2</v>
       </c>
       <c r="D430">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="F430" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="G430" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="431" spans="1:7">
       <c r="A431" s="3">
-        <v>489</v>
+        <v>460</v>
       </c>
       <c r="B431" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="C431" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D431">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="F431" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="G431" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
     </row>
     <row r="432" spans="1:7">
       <c r="A432" s="3">
-        <v>200</v>
+        <v>461</v>
       </c>
       <c r="B432" t="s">
-        <v>112</v>
+        <v>364</v>
       </c>
       <c r="C432" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D432">
-        <v>0</v>
-      </c>
-      <c r="E432">
-        <v>250</v>
+        <v>0.75</v>
       </c>
       <c r="F432" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="G432" t="s">
-        <v>492</v>
+        <v>514</v>
       </c>
     </row>
     <row r="433" spans="1:7">
       <c r="A433" s="3">
-        <v>395</v>
+        <v>462</v>
       </c>
       <c r="B433" t="s">
-        <v>301</v>
+        <v>365</v>
       </c>
       <c r="C433" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D433">
-        <v>0</v>
-      </c>
-      <c r="E433">
-        <v>100</v>
+        <v>0.75</v>
       </c>
       <c r="F433" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="G433" t="s">
-        <v>492</v>
+        <v>515</v>
       </c>
     </row>
     <row r="434" spans="1:7">
       <c r="A434" s="3">
-        <v>192</v>
+        <v>463</v>
       </c>
       <c r="B434" t="s">
-        <v>102</v>
+        <v>366</v>
       </c>
       <c r="C434" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D434">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="F434" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="G434" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
     </row>
     <row r="435" spans="1:7">
       <c r="A435" s="3">
-        <v>193</v>
+        <v>464</v>
       </c>
       <c r="B435" t="s">
-        <v>103</v>
+        <v>367</v>
       </c>
       <c r="C435" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D435">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="F435" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="G435" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
     </row>
     <row r="436" spans="1:7">
       <c r="A436" s="3">
-        <v>83</v>
+        <v>466</v>
       </c>
       <c r="B436" t="s">
-        <v>437</v>
+        <v>368</v>
       </c>
       <c r="C436" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D436">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="F436" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G436" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="437" spans="1:7">
       <c r="A437" s="3">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B437" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C437" s="1">
         <v>3</v>
@@ -9439,18 +9430,18 @@
         <v>0.625</v>
       </c>
       <c r="F437" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="G437" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
     </row>
     <row r="438" spans="1:7">
       <c r="A438" s="3">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B438" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C438" s="1">
         <v>3</v>
@@ -9459,18 +9450,18 @@
         <v>0.625</v>
       </c>
       <c r="F438" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G438" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="439" spans="1:7">
       <c r="A439" s="3">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B439" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C439" s="1">
         <v>3</v>
@@ -9479,33 +9470,33 @@
         <v>0.625</v>
       </c>
       <c r="F439" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="G439" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="440" spans="1:7">
       <c r="A440" s="3">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B440" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C440" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D440">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="F440" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G440" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="441" spans="1:7" hidden="1">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7">
       <c r="A441" s="3">
         <v>472</v>
       </c>
@@ -9522,7 +9513,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="442" spans="1:7" hidden="1">
+    <row r="442" spans="1:7">
       <c r="A442" s="3">
         <v>475</v>
       </c>
@@ -9539,7 +9530,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="443" spans="1:7" hidden="1">
+    <row r="443" spans="1:7">
       <c r="A443" s="3">
         <v>477</v>
       </c>
@@ -9556,7 +9547,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="444" spans="1:7" hidden="1">
+    <row r="444" spans="1:7">
       <c r="A444" s="3">
         <v>478</v>
       </c>
@@ -9573,7 +9564,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="445" spans="1:7" hidden="1">
+    <row r="445" spans="1:7">
       <c r="A445" s="3">
         <v>480</v>
       </c>
@@ -9590,7 +9581,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="446" spans="1:7" hidden="1">
+    <row r="446" spans="1:7">
       <c r="A446" s="3">
         <v>481</v>
       </c>
@@ -9609,10 +9600,10 @@
     </row>
     <row r="447" spans="1:7">
       <c r="A447" s="3">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="B447" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="C447" s="1">
         <v>2</v>
@@ -9621,13 +9612,13 @@
         <v>0.75</v>
       </c>
       <c r="F447" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="G447" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="448" spans="1:7" hidden="1">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7">
       <c r="A448" s="3">
         <v>484</v>
       </c>
@@ -9646,25 +9637,25 @@
     </row>
     <row r="449" spans="1:7">
       <c r="A449" s="3">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="B449" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="C449" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D449">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="F449" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="G449" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="450" spans="1:7" hidden="1">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7">
       <c r="A450" s="3">
         <v>486</v>
       </c>
@@ -9678,7 +9669,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="451" spans="1:7" hidden="1">
+    <row r="451" spans="1:7">
       <c r="A451" s="3">
         <v>487</v>
       </c>
@@ -9697,65 +9688,65 @@
     </row>
     <row r="452" spans="1:7">
       <c r="A452" s="3">
-        <v>459</v>
+        <v>488</v>
       </c>
       <c r="B452" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="C452" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D452">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="F452" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="G452" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
     </row>
     <row r="453" spans="1:7">
       <c r="A453" s="3">
-        <v>456</v>
+        <v>489</v>
       </c>
       <c r="B453" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="C453" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D453">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="F453" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="G453" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="454" spans="1:7">
       <c r="A454" s="3">
-        <v>461</v>
+        <v>490</v>
       </c>
       <c r="B454" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="C454" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D454">
-        <v>0.75</v>
-      </c>
-      <c r="F454" t="s">
-        <v>474</v>
+        <v>0.375</v>
+      </c>
+      <c r="F454" s="6" t="s">
+        <v>483</v>
       </c>
       <c r="G454" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="455" spans="1:7" hidden="1">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7">
       <c r="A455" s="3">
         <v>491</v>
       </c>
@@ -9771,25 +9762,28 @@
     </row>
     <row r="456" spans="1:7">
       <c r="A456" s="3">
-        <v>464</v>
+        <v>493</v>
       </c>
       <c r="B456" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="C456" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D456">
-        <v>0.75</v>
+        <v>0</v>
+      </c>
+      <c r="E456">
+        <v>0</v>
       </c>
       <c r="F456" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="G456" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="457" spans="1:7" hidden="1">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7">
       <c r="A457" s="3">
         <v>494</v>
       </c>
@@ -9806,7 +9800,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="458" spans="1:7" hidden="1">
+    <row r="458" spans="1:7">
       <c r="A458" s="3">
         <v>495</v>
       </c>
@@ -9823,7 +9817,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="459" spans="1:7" hidden="1">
+    <row r="459" spans="1:7">
       <c r="A459" s="3">
         <v>496</v>
       </c>
@@ -9837,7 +9831,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="460" spans="1:7" hidden="1">
+    <row r="460" spans="1:7">
       <c r="A460" s="3">
         <v>497</v>
       </c>
@@ -9856,45 +9850,51 @@
     </row>
     <row r="461" spans="1:7">
       <c r="A461" s="3">
-        <v>458</v>
+        <v>498</v>
       </c>
       <c r="B461" t="s">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="C461" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D461">
-        <v>0.75</v>
+        <v>0</v>
+      </c>
+      <c r="E461">
+        <v>100</v>
       </c>
       <c r="F461" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="G461" t="s">
-        <v>511</v>
+        <v>492</v>
       </c>
     </row>
     <row r="462" spans="1:7">
       <c r="A462" s="3">
-        <v>460</v>
+        <v>499</v>
       </c>
       <c r="B462" t="s">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="C462" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D462">
-        <v>0.75</v>
+        <v>0</v>
+      </c>
+      <c r="E462">
+        <v>100</v>
       </c>
       <c r="F462" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="G462" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="463" spans="1:7" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7">
       <c r="A463" s="3">
         <v>500</v>
       </c>
@@ -9910,25 +9910,25 @@
     </row>
     <row r="464" spans="1:7">
       <c r="A464" s="3">
-        <v>466</v>
+        <v>501</v>
       </c>
       <c r="B464" t="s">
-        <v>368</v>
+        <v>400</v>
       </c>
       <c r="C464" s="1">
         <v>3</v>
       </c>
       <c r="D464">
-        <v>0.625</v>
+        <v>0.375</v>
       </c>
       <c r="F464" t="s">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="G464" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="465" spans="1:6" hidden="1">
+    <row r="465" spans="1:6">
       <c r="A465" s="3">
         <v>502</v>
       </c>

--- a/data/entrada/nóminas/cargos.xlsx
+++ b/data/entrada/nóminas/cargos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amarzal/_Activo/eco/CoAna/data/entrada/nóminas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD26005-9DE8-6543-857A-B75457E6C7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5D287A-823B-F941-82EB-D3760DF21BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="525">
   <si>
     <t>cargo</t>
   </si>
@@ -1605,6 +1605,9 @@
   </si>
   <si>
     <t>facultades-escuelas</t>
+  </si>
+  <si>
+    <t>dag-CENTROTITULACION</t>
   </si>
 </sst>
 </file>
@@ -1681,7 +1684,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1690,7 +1693,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2411,7 +2413,7 @@
         <v>250</v>
       </c>
       <c r="F19" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="G19" t="s">
         <v>492</v>
@@ -5260,7 +5262,7 @@
       <c r="F189" t="s">
         <v>486</v>
       </c>
-      <c r="G189" s="6" t="s">
+      <c r="G189" t="s">
         <v>499</v>
       </c>
     </row>
@@ -5278,10 +5280,10 @@
         <v>0.375</v>
       </c>
       <c r="F190" t="s">
-        <v>486</v>
+        <v>524</v>
       </c>
       <c r="G190" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5298,10 +5300,10 @@
         <v>0.375</v>
       </c>
       <c r="F191" t="s">
-        <v>486</v>
+        <v>524</v>
       </c>
       <c r="G191" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -7038,7 +7040,7 @@
       <c r="D298">
         <v>0.25</v>
       </c>
-      <c r="F298" s="6" t="s">
+      <c r="F298" t="s">
         <v>486</v>
       </c>
       <c r="G298" t="s">
@@ -7913,7 +7915,7 @@
       <c r="F350" t="s">
         <v>465</v>
       </c>
-      <c r="G350" s="6" t="s">
+      <c r="G350" t="s">
         <v>504</v>
       </c>
     </row>
@@ -9739,7 +9741,7 @@
       <c r="D454">
         <v>0.375</v>
       </c>
-      <c r="F454" s="6" t="s">
+      <c r="F454" t="s">
         <v>483</v>
       </c>
       <c r="G454" t="s">

--- a/data/entrada/nóminas/cargos.xlsx
+++ b/data/entrada/nóminas/cargos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amarzal/_Activo/eco/CoAna/data/entrada/nóminas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5D287A-823B-F941-82EB-D3760DF21BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81607A4-AAB4-CD48-BBEA-C8F04C3CFD54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="529">
   <si>
     <t>cargo</t>
   </si>
@@ -1608,6 +1608,18 @@
   </si>
   <si>
     <t>dag-CENTROTITULACION</t>
+  </si>
+  <si>
+    <t>cátedras-investigación</t>
+  </si>
+  <si>
+    <t>cátedras-aulas-empresa</t>
+  </si>
+  <si>
+    <t>cát-unesco-filosofia-pau</t>
+  </si>
+  <si>
+    <t>cát-unesco-esclavitudes-afrodescendencia</t>
   </si>
 </sst>
 </file>
@@ -6901,11 +6913,14 @@
       <c r="C290" s="1">
         <v>4</v>
       </c>
-      <c r="D290" t="s">
-        <v>63</v>
+      <c r="D290">
+        <v>0</v>
       </c>
       <c r="F290" t="s">
-        <v>63</v>
+        <v>527</v>
+      </c>
+      <c r="G290" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -7411,7 +7426,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="321" spans="1:6">
+    <row r="321" spans="1:7">
       <c r="A321" s="3">
         <v>332</v>
       </c>
@@ -7428,7 +7443,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="322" spans="1:6">
+    <row r="322" spans="1:7">
       <c r="A322" s="3">
         <v>333</v>
       </c>
@@ -7445,7 +7460,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="323" spans="1:6">
+    <row r="323" spans="1:7">
       <c r="A323" s="3">
         <v>334</v>
       </c>
@@ -7459,7 +7474,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="324" spans="1:6">
+    <row r="324" spans="1:7">
       <c r="A324" s="3">
         <v>336</v>
       </c>
@@ -7473,7 +7488,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="325" spans="1:6">
+    <row r="325" spans="1:7">
       <c r="A325" s="3">
         <v>338</v>
       </c>
@@ -7490,7 +7505,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="326" spans="1:6">
+    <row r="326" spans="1:7">
       <c r="A326" s="3">
         <v>339</v>
       </c>
@@ -7507,7 +7522,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="327" spans="1:6">
+    <row r="327" spans="1:7">
       <c r="A327" s="3">
         <v>340</v>
       </c>
@@ -7522,7 +7537,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="328" spans="1:6">
+    <row r="328" spans="1:7">
       <c r="A328" s="3">
         <v>341</v>
       </c>
@@ -7539,7 +7554,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="329" spans="1:6">
+    <row r="329" spans="1:7">
       <c r="A329" s="3">
         <v>342</v>
       </c>
@@ -7549,14 +7564,17 @@
       <c r="C329" s="1">
         <v>5</v>
       </c>
-      <c r="D329" t="s">
-        <v>63</v>
+      <c r="D329">
+        <v>0</v>
       </c>
       <c r="F329" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="330" spans="1:6">
+        <v>526</v>
+      </c>
+      <c r="G329" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7">
       <c r="A330" s="3">
         <v>344</v>
       </c>
@@ -7570,7 +7588,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="331" spans="1:6">
+    <row r="331" spans="1:7">
       <c r="A331" s="3">
         <v>345</v>
       </c>
@@ -7587,7 +7605,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="332" spans="1:6">
+    <row r="332" spans="1:7">
       <c r="A332" s="3">
         <v>347</v>
       </c>
@@ -7604,7 +7622,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="333" spans="1:6">
+    <row r="333" spans="1:7">
       <c r="A333" s="3">
         <v>348</v>
       </c>
@@ -7621,7 +7639,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="334" spans="1:6">
+    <row r="334" spans="1:7">
       <c r="A334" s="3">
         <v>349</v>
       </c>
@@ -7638,7 +7656,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="335" spans="1:6">
+    <row r="335" spans="1:7">
       <c r="A335" s="3">
         <v>350</v>
       </c>
@@ -7655,7 +7673,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="336" spans="1:6">
+    <row r="336" spans="1:7">
       <c r="A336" s="3">
         <v>351</v>
       </c>
@@ -7953,7 +7971,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="353" spans="1:6">
+    <row r="353" spans="1:7">
       <c r="A353" s="3">
         <v>371</v>
       </c>
@@ -7970,7 +7988,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="354" spans="1:6">
+    <row r="354" spans="1:7">
       <c r="A354" s="3">
         <v>372</v>
       </c>
@@ -7987,7 +8005,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="355" spans="1:6">
+    <row r="355" spans="1:7">
       <c r="A355" s="3">
         <v>373</v>
       </c>
@@ -8004,7 +8022,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="356" spans="1:6">
+    <row r="356" spans="1:7">
       <c r="A356" s="3">
         <v>375</v>
       </c>
@@ -8021,7 +8039,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="357" spans="1:6">
+    <row r="357" spans="1:7">
       <c r="A357" s="3">
         <v>376</v>
       </c>
@@ -8038,7 +8056,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="358" spans="1:6">
+    <row r="358" spans="1:7">
       <c r="A358" s="3">
         <v>377</v>
       </c>
@@ -8055,7 +8073,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="359" spans="1:6">
+    <row r="359" spans="1:7">
       <c r="A359" s="3">
         <v>378</v>
       </c>
@@ -8069,7 +8087,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="360" spans="1:6">
+    <row r="360" spans="1:7">
       <c r="A360" s="3">
         <v>379</v>
       </c>
@@ -8084,7 +8102,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="361" spans="1:6">
+    <row r="361" spans="1:7">
       <c r="A361" s="3">
         <v>380</v>
       </c>
@@ -8101,7 +8119,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="362" spans="1:6">
+    <row r="362" spans="1:7">
       <c r="A362" s="3">
         <v>381</v>
       </c>
@@ -8118,7 +8136,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="363" spans="1:6">
+    <row r="363" spans="1:7">
       <c r="A363" s="3">
         <v>382</v>
       </c>
@@ -8135,7 +8153,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="364" spans="1:6">
+    <row r="364" spans="1:7">
       <c r="A364" s="3">
         <v>383</v>
       </c>
@@ -8152,7 +8170,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="365" spans="1:6">
+    <row r="365" spans="1:7">
       <c r="A365" s="3">
         <v>384</v>
       </c>
@@ -8162,14 +8180,17 @@
       <c r="C365" s="1">
         <v>7</v>
       </c>
-      <c r="D365" t="s">
-        <v>63</v>
+      <c r="D365">
+        <v>0</v>
       </c>
       <c r="F365" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="366" spans="1:6">
+        <v>526</v>
+      </c>
+      <c r="G365" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7">
       <c r="A366" s="3">
         <v>386</v>
       </c>
@@ -8186,7 +8207,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="367" spans="1:6">
+    <row r="367" spans="1:7">
       <c r="A367" s="3">
         <v>387</v>
       </c>
@@ -8203,7 +8224,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="368" spans="1:6">
+    <row r="368" spans="1:7">
       <c r="A368" s="3">
         <v>388</v>
       </c>
@@ -8644,11 +8665,14 @@
       <c r="C393" s="1">
         <v>4</v>
       </c>
-      <c r="D393" t="s">
-        <v>63</v>
+      <c r="D393">
+        <v>0.625</v>
       </c>
       <c r="F393" t="s">
-        <v>63</v>
+        <v>456</v>
+      </c>
+      <c r="G393" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="394" spans="1:7">
@@ -8856,11 +8880,14 @@
       <c r="C405" s="1">
         <v>4</v>
       </c>
-      <c r="D405" t="s">
-        <v>63</v>
+      <c r="D405">
+        <v>0</v>
       </c>
       <c r="F405" t="s">
-        <v>63</v>
+        <v>527</v>
+      </c>
+      <c r="G405" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="406" spans="1:7">
@@ -9630,11 +9657,14 @@
       <c r="C448" s="1">
         <v>3</v>
       </c>
-      <c r="D448" t="s">
-        <v>63</v>
+      <c r="D448">
+        <v>0.625</v>
       </c>
       <c r="F448" t="s">
-        <v>63</v>
+        <v>464</v>
+      </c>
+      <c r="G448" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="449" spans="1:7">
@@ -9779,7 +9809,7 @@
         <v>0</v>
       </c>
       <c r="F456" t="s">
-        <v>484</v>
+        <v>528</v>
       </c>
       <c r="G456" t="s">
         <v>484</v>
@@ -9795,11 +9825,14 @@
       <c r="C457" s="1">
         <v>8</v>
       </c>
-      <c r="D457" t="s">
-        <v>63</v>
+      <c r="D457">
+        <v>0</v>
       </c>
       <c r="F457" t="s">
-        <v>63</v>
+        <v>526</v>
+      </c>
+      <c r="G457" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="458" spans="1:7">
@@ -9812,11 +9845,14 @@
       <c r="C458" s="1">
         <v>8</v>
       </c>
-      <c r="D458" t="s">
-        <v>63</v>
+      <c r="D458">
+        <v>9</v>
       </c>
       <c r="F458" t="s">
-        <v>63</v>
+        <v>526</v>
+      </c>
+      <c r="G458" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="459" spans="1:7">
